--- a/automation/reports/Excel/Load_Testing_Report.xlsx
+++ b/automation/reports/Excel/Load_Testing_Report.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:40:01</t>
+          <t>2026-10-05 21:16:34</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>2072.06s</t>
+          <t>2139.57s</t>
         </is>
       </c>
     </row>
@@ -853,11 +853,11 @@
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>p95 = 514ms, 0% errors</t>
+          <t>p95 = 590ms, 0% errors</t>
         </is>
       </c>
       <c r="H2" s="11" t="n">
-        <v>5.73</v>
+        <v>4.5</v>
       </c>
       <c r="I2" s="11" t="inlineStr">
         <is>
@@ -903,11 +903,11 @@
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>p95 = 842ms, 0% errors</t>
+          <t>p95 = 562ms, 0% errors</t>
         </is>
       </c>
       <c r="H3" s="14" t="n">
-        <v>4.19</v>
+        <v>7.04</v>
       </c>
       <c r="I3" s="14" t="inlineStr">
         <is>
@@ -953,11 +953,11 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>p95 = 222ms, 0% errors</t>
+          <t>p95 = 343ms, 0% errors</t>
         </is>
       </c>
       <c r="H4" s="11" t="n">
-        <v>3.01</v>
+        <v>8.02</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>p95 = 837ms, 0% errors</t>
+          <t>p95 = 331ms, 0% errors</t>
         </is>
       </c>
       <c r="H5" s="14" t="n">
-        <v>9.539999999999999</v>
+        <v>5.78</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -1053,11 +1053,11 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>p95 = 872ms, 0% errors</t>
+          <t>p95 = 694ms, 0% errors</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>3.87</v>
+        <v>6.1</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>p95 = 632ms, 0% errors</t>
+          <t>p95 = 266ms, 0% errors</t>
         </is>
       </c>
       <c r="H7" s="14" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
@@ -1153,11 +1153,11 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>p95 = 462ms, 0% errors</t>
+          <t>p95 = 329ms, 0% errors</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>5.76</v>
+        <v>5.44</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -1203,11 +1203,11 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>p95 = 403ms, 0% errors</t>
+          <t>p95 = 561ms, 0% errors</t>
         </is>
       </c>
       <c r="H9" s="14" t="n">
-        <v>7.88</v>
+        <v>9.24</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -1253,11 +1253,11 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>p95 = 209ms, 0% errors</t>
+          <t>p95 = 428ms, 0% errors</t>
         </is>
       </c>
       <c r="H10" s="11" t="n">
-        <v>11.42</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1303,11 +1303,11 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>p95 = 572ms, 0% errors</t>
+          <t>p95 = 756ms, 0% errors</t>
         </is>
       </c>
       <c r="H11" s="14" t="n">
-        <v>10.37</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
@@ -1353,11 +1353,11 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>p95 = 340ms, 0% errors</t>
+          <t>p95 = 545ms, 0% errors</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
-        <v>3.93</v>
+        <v>5.64</v>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>p95 = 338ms, 0% errors</t>
+          <t>p95 = 817ms, 0% errors</t>
         </is>
       </c>
       <c r="H13" s="14" t="n">
-        <v>3.96</v>
+        <v>10.47</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -1453,11 +1453,11 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>p95 = 523ms, 0% errors</t>
+          <t>p95 = 511ms, 0% errors</t>
         </is>
       </c>
       <c r="H14" s="11" t="n">
-        <v>1.81</v>
+        <v>5.69</v>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
@@ -1503,11 +1503,11 @@
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>p95 = 182ms, 0% errors</t>
+          <t>p95 = 271ms, 0% errors</t>
         </is>
       </c>
       <c r="H15" s="14" t="n">
-        <v>7.18</v>
+        <v>1.61</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1553,11 +1553,11 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>p95 = 441ms, 0% errors</t>
+          <t>p95 = 234ms, 0% errors</t>
         </is>
       </c>
       <c r="H16" s="11" t="n">
-        <v>11.54</v>
+        <v>6.24</v>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
@@ -1603,11 +1603,11 @@
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>p95 = 213ms, 0% errors</t>
+          <t>p95 = 722ms, 0% errors</t>
         </is>
       </c>
       <c r="H17" s="14" t="n">
-        <v>10.74</v>
+        <v>1.8</v>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
@@ -1653,11 +1653,11 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>p95 = 754ms, 0% errors</t>
+          <t>p95 = 599ms, 0% errors</t>
         </is>
       </c>
       <c r="H18" s="11" t="n">
-        <v>5.4</v>
+        <v>7.72</v>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
@@ -1703,11 +1703,11 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>p95 = 235ms, 0% errors</t>
+          <t>p95 = 340ms, 0% errors</t>
         </is>
       </c>
       <c r="H19" s="14" t="n">
-        <v>10.23</v>
+        <v>4.49</v>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
@@ -1753,11 +1753,11 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>p95 = 527ms, 0% errors</t>
+          <t>p95 = 721ms, 0% errors</t>
         </is>
       </c>
       <c r="H20" s="11" t="n">
-        <v>6.5</v>
+        <v>5.36</v>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
@@ -1803,11 +1803,11 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>p95 = 469ms, 0% errors</t>
+          <t>p95 = 214ms, 0% errors</t>
         </is>
       </c>
       <c r="H21" s="14" t="n">
-        <v>8.779999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
@@ -1853,11 +1853,11 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>p95 = 402ms, 0% errors</t>
+          <t>p95 = 246ms, 0% errors</t>
         </is>
       </c>
       <c r="H22" s="11" t="n">
-        <v>4.51</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
@@ -1903,11 +1903,11 @@
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>p95 = 514ms, 0% errors</t>
+          <t>p95 = 429ms, 0% errors</t>
         </is>
       </c>
       <c r="H23" s="14" t="n">
-        <v>6.16</v>
+        <v>1.98</v>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
@@ -1953,11 +1953,11 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>p95 = 192ms, 0% errors</t>
+          <t>p95 = 258ms, 0% errors</t>
         </is>
       </c>
       <c r="H24" s="11" t="n">
-        <v>4.9</v>
+        <v>5.95</v>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
@@ -2003,11 +2003,11 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>p95 = 194ms, 0% errors</t>
+          <t>p95 = 489ms, 0% errors</t>
         </is>
       </c>
       <c r="H25" s="14" t="n">
-        <v>10.93</v>
+        <v>3.15</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
@@ -2053,11 +2053,11 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>p95 = 340ms, 0% errors</t>
+          <t>p95 = 655ms, 0% errors</t>
         </is>
       </c>
       <c r="H26" s="11" t="n">
-        <v>1.65</v>
+        <v>8.68</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
@@ -2103,11 +2103,11 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>p95 = 548ms, 0% errors</t>
+          <t>p95 = 865ms, 0% errors</t>
         </is>
       </c>
       <c r="H27" s="14" t="n">
-        <v>6.52</v>
+        <v>10.74</v>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
@@ -2153,11 +2153,11 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>p95 = 421ms, 0% errors</t>
+          <t>p95 = 435ms, 0% errors</t>
         </is>
       </c>
       <c r="H28" s="11" t="n">
-        <v>8.74</v>
+        <v>9.07</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
@@ -2203,11 +2203,11 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>p95 = 558ms, 0% errors</t>
+          <t>p95 = 410ms, 0% errors</t>
         </is>
       </c>
       <c r="H29" s="14" t="n">
-        <v>10.71</v>
+        <v>2.03</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
@@ -2253,11 +2253,11 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>p95 = 774ms, 0% errors</t>
+          <t>p95 = 429ms, 0% errors</t>
         </is>
       </c>
       <c r="H30" s="11" t="n">
-        <v>8.369999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
@@ -2303,11 +2303,11 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>p95 = 645ms, 0% errors</t>
+          <t>p95 = 643ms, 0% errors</t>
         </is>
       </c>
       <c r="H31" s="14" t="n">
-        <v>4.18</v>
+        <v>6.92</v>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
@@ -2353,11 +2353,11 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>p95 = 534ms, 0% errors</t>
+          <t>p95 = 809ms, 0% errors</t>
         </is>
       </c>
       <c r="H32" s="11" t="n">
-        <v>2.66</v>
+        <v>10.11</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -2403,11 +2403,11 @@
       </c>
       <c r="G33" s="15" t="inlineStr">
         <is>
-          <t>p95 = 436ms, 0% errors</t>
+          <t>p95 = 763ms, 0% errors</t>
         </is>
       </c>
       <c r="H33" s="14" t="n">
-        <v>10.82</v>
+        <v>7.82</v>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
@@ -2453,11 +2453,11 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>p95 = 293ms, 0% errors</t>
+          <t>p95 = 549ms, 0% errors</t>
         </is>
       </c>
       <c r="H34" s="11" t="n">
-        <v>1.88</v>
+        <v>2.82</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
@@ -2503,11 +2503,11 @@
       </c>
       <c r="G35" s="15" t="inlineStr">
         <is>
-          <t>p95 = 784ms, 0% errors</t>
+          <t>p95 = 620ms, 0% errors</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
-        <v>6.54</v>
+        <v>8.56</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
@@ -2553,11 +2553,11 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>p95 = 822ms, 0% errors</t>
+          <t>p95 = 542ms, 0% errors</t>
         </is>
       </c>
       <c r="H36" s="11" t="n">
-        <v>8.68</v>
+        <v>6.59</v>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
@@ -2603,11 +2603,11 @@
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>p95 = 196ms, 0% errors</t>
+          <t>p95 = 466ms, 0% errors</t>
         </is>
       </c>
       <c r="H37" s="14" t="n">
-        <v>4.82</v>
+        <v>8.75</v>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
@@ -2653,11 +2653,11 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>p95 = 656ms, 0% errors</t>
+          <t>p95 = 837ms, 0% errors</t>
         </is>
       </c>
       <c r="H38" s="11" t="n">
-        <v>11.69</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
@@ -2703,11 +2703,11 @@
       </c>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>p95 = 297ms, 0% errors</t>
+          <t>p95 = 346ms, 0% errors</t>
         </is>
       </c>
       <c r="H39" s="14" t="n">
-        <v>7.63</v>
+        <v>6.82</v>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
@@ -2753,11 +2753,11 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>p95 = 639ms, 0% errors</t>
+          <t>p95 = 598ms, 0% errors</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
-        <v>8.44</v>
+        <v>1.54</v>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
@@ -2803,11 +2803,11 @@
       </c>
       <c r="G41" s="15" t="inlineStr">
         <is>
-          <t>p95 = 883ms, 0% errors</t>
+          <t>p95 = 709ms, 0% errors</t>
         </is>
       </c>
       <c r="H41" s="14" t="n">
-        <v>4.09</v>
+        <v>10.97</v>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
@@ -2853,11 +2853,11 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>p95 = 775ms, 0% errors</t>
+          <t>p95 = 185ms, 0% errors</t>
         </is>
       </c>
       <c r="H42" s="11" t="n">
-        <v>9.26</v>
+        <v>10.69</v>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
@@ -2903,11 +2903,11 @@
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>p95 = 571ms, 0% errors</t>
+          <t>p95 = 764ms, 0% errors</t>
         </is>
       </c>
       <c r="H43" s="14" t="n">
-        <v>4.73</v>
+        <v>3.9</v>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
@@ -2953,11 +2953,11 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>p95 = 807ms, 0% errors</t>
+          <t>p95 = 214ms, 0% errors</t>
         </is>
       </c>
       <c r="H44" s="11" t="n">
-        <v>3.65</v>
+        <v>5.76</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
@@ -3003,11 +3003,11 @@
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>p95 = 207ms, 0% errors</t>
+          <t>p95 = 613ms, 0% errors</t>
         </is>
       </c>
       <c r="H45" s="14" t="n">
-        <v>3.96</v>
+        <v>4.43</v>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
@@ -3053,11 +3053,11 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>p95 = 858ms, 0% errors</t>
+          <t>p95 = 798ms, 0% errors</t>
         </is>
       </c>
       <c r="H46" s="11" t="n">
-        <v>4.43</v>
+        <v>6.11</v>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
@@ -3103,11 +3103,11 @@
       </c>
       <c r="G47" s="15" t="inlineStr">
         <is>
-          <t>p95 = 805ms, 0% errors</t>
+          <t>p95 = 729ms, 0% errors</t>
         </is>
       </c>
       <c r="H47" s="14" t="n">
-        <v>5.52</v>
+        <v>8.1</v>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
@@ -3153,11 +3153,11 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>p95 = 702ms, 0% errors</t>
+          <t>p95 = 458ms, 0% errors</t>
         </is>
       </c>
       <c r="H48" s="11" t="n">
-        <v>4.77</v>
+        <v>9.77</v>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
@@ -3203,11 +3203,11 @@
       </c>
       <c r="G49" s="15" t="inlineStr">
         <is>
-          <t>p95 = 357ms, 0% errors</t>
+          <t>p95 = 294ms, 0% errors</t>
         </is>
       </c>
       <c r="H49" s="14" t="n">
-        <v>10.7</v>
+        <v>5.71</v>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
@@ -3253,11 +3253,11 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>p95 = 321ms, 0% errors</t>
+          <t>p95 = 542ms, 0% errors</t>
         </is>
       </c>
       <c r="H50" s="11" t="n">
-        <v>10.33</v>
+        <v>2.15</v>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
@@ -3303,11 +3303,11 @@
       </c>
       <c r="G51" s="15" t="inlineStr">
         <is>
-          <t>p95 = 346ms, 0% errors</t>
+          <t>p95 = 456ms, 0% errors</t>
         </is>
       </c>
       <c r="H51" s="14" t="n">
-        <v>7.68</v>
+        <v>2.64</v>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
@@ -3353,11 +3353,11 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>p95 = 187ms, 0% errors</t>
+          <t>p95 = 490ms, 0% errors</t>
         </is>
       </c>
       <c r="H52" s="11" t="n">
-        <v>6.84</v>
+        <v>11.68</v>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
@@ -3403,11 +3403,11 @@
       </c>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>p95 = 740ms, 0% errors</t>
+          <t>p95 = 297ms, 0% errors</t>
         </is>
       </c>
       <c r="H53" s="14" t="n">
-        <v>8.16</v>
+        <v>7.34</v>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
@@ -3453,11 +3453,11 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>p95 = 181ms, 0% errors</t>
+          <t>p95 = 356ms, 0% errors</t>
         </is>
       </c>
       <c r="H54" s="11" t="n">
-        <v>1.79</v>
+        <v>6.76</v>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
@@ -3503,11 +3503,11 @@
       </c>
       <c r="G55" s="15" t="inlineStr">
         <is>
-          <t>p95 = 604ms, 0% errors</t>
+          <t>p95 = 879ms, 0% errors</t>
         </is>
       </c>
       <c r="H55" s="14" t="n">
-        <v>2.88</v>
+        <v>11.46</v>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
@@ -3553,11 +3553,11 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>p95 = 471ms, 0% errors</t>
+          <t>p95 = 622ms, 0% errors</t>
         </is>
       </c>
       <c r="H56" s="11" t="n">
-        <v>10.15</v>
+        <v>7.63</v>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
@@ -3603,11 +3603,11 @@
       </c>
       <c r="G57" s="15" t="inlineStr">
         <is>
-          <t>p95 = 833ms, 0% errors</t>
+          <t>p95 = 265ms, 0% errors</t>
         </is>
       </c>
       <c r="H57" s="14" t="n">
-        <v>11.87</v>
+        <v>4.99</v>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
@@ -3653,11 +3653,11 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>p95 = 207ms, 0% errors</t>
+          <t>p95 = 704ms, 0% errors</t>
         </is>
       </c>
       <c r="H58" s="11" t="n">
-        <v>11.92</v>
+        <v>11.14</v>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
@@ -3703,11 +3703,11 @@
       </c>
       <c r="G59" s="15" t="inlineStr">
         <is>
-          <t>p95 = 285ms, 0% errors</t>
+          <t>p95 = 288ms, 0% errors</t>
         </is>
       </c>
       <c r="H59" s="14" t="n">
-        <v>5.42</v>
+        <v>4.17</v>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
@@ -3753,11 +3753,11 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>p95 = 554ms, 0% errors</t>
+          <t>p95 = 882ms, 0% errors</t>
         </is>
       </c>
       <c r="H60" s="11" t="n">
-        <v>9.08</v>
+        <v>6.4</v>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
@@ -3803,11 +3803,11 @@
       </c>
       <c r="G61" s="15" t="inlineStr">
         <is>
-          <t>p95 = 466ms, 0% errors</t>
+          <t>p95 = 869ms, 0% errors</t>
         </is>
       </c>
       <c r="H61" s="14" t="n">
-        <v>5.73</v>
+        <v>11.16</v>
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
@@ -3853,11 +3853,11 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>p95 = 473ms, 0% errors</t>
+          <t>p95 = 675ms, 0% errors</t>
         </is>
       </c>
       <c r="H62" s="11" t="n">
-        <v>9</v>
+        <v>11.6</v>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
@@ -3903,11 +3903,11 @@
       </c>
       <c r="G63" s="15" t="inlineStr">
         <is>
-          <t>p95 = 312ms, 0% errors</t>
+          <t>p95 = 225ms, 0% errors</t>
         </is>
       </c>
       <c r="H63" s="14" t="n">
-        <v>10.08</v>
+        <v>5.26</v>
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
@@ -3953,11 +3953,11 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>p95 = 321ms, 0% errors</t>
+          <t>p95 = 301ms, 0% errors</t>
         </is>
       </c>
       <c r="H64" s="11" t="n">
-        <v>2.96</v>
+        <v>1.97</v>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
@@ -4003,11 +4003,11 @@
       </c>
       <c r="G65" s="15" t="inlineStr">
         <is>
-          <t>p95 = 341ms, 0% errors</t>
+          <t>p95 = 890ms, 0% errors</t>
         </is>
       </c>
       <c r="H65" s="14" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
@@ -4053,11 +4053,11 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>p95 = 415ms, 0% errors</t>
+          <t>p95 = 766ms, 0% errors</t>
         </is>
       </c>
       <c r="H66" s="11" t="n">
-        <v>8.640000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
@@ -4103,11 +4103,11 @@
       </c>
       <c r="G67" s="15" t="inlineStr">
         <is>
-          <t>p95 = 201ms, 0% errors</t>
+          <t>p95 = 882ms, 0% errors</t>
         </is>
       </c>
       <c r="H67" s="14" t="n">
-        <v>6.87</v>
+        <v>5.1</v>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
@@ -4153,11 +4153,11 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>p95 = 788ms, 0% errors</t>
+          <t>p95 = 314ms, 0% errors</t>
         </is>
       </c>
       <c r="H68" s="11" t="n">
-        <v>4.06</v>
+        <v>5.55</v>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
@@ -4203,11 +4203,11 @@
       </c>
       <c r="G69" s="15" t="inlineStr">
         <is>
-          <t>p95 = 342ms, 0% errors</t>
+          <t>p95 = 517ms, 0% errors</t>
         </is>
       </c>
       <c r="H69" s="14" t="n">
-        <v>6.72</v>
+        <v>10.39</v>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
@@ -4253,11 +4253,11 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>p95 = 329ms, 0% errors</t>
+          <t>p95 = 647ms, 0% errors</t>
         </is>
       </c>
       <c r="H70" s="11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
@@ -4303,11 +4303,11 @@
       </c>
       <c r="G71" s="15" t="inlineStr">
         <is>
-          <t>p95 = 531ms, 0% errors</t>
+          <t>p95 = 556ms, 0% errors</t>
         </is>
       </c>
       <c r="H71" s="14" t="n">
-        <v>10.24</v>
+        <v>2.42</v>
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
@@ -4353,11 +4353,11 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>p95 = 683ms, 0% errors</t>
+          <t>p95 = 466ms, 0% errors</t>
         </is>
       </c>
       <c r="H72" s="11" t="n">
-        <v>8.1</v>
+        <v>7.69</v>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
@@ -4403,11 +4403,11 @@
       </c>
       <c r="G73" s="15" t="inlineStr">
         <is>
-          <t>p95 = 798ms, 0% errors</t>
+          <t>p95 = 396ms, 0% errors</t>
         </is>
       </c>
       <c r="H73" s="14" t="n">
-        <v>5.57</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
@@ -4453,11 +4453,11 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>p95 = 686ms, 0% errors</t>
+          <t>p95 = 312ms, 0% errors</t>
         </is>
       </c>
       <c r="H74" s="11" t="n">
-        <v>3.02</v>
+        <v>11.68</v>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
@@ -4503,11 +4503,11 @@
       </c>
       <c r="G75" s="15" t="inlineStr">
         <is>
-          <t>p95 = 564ms, 0% errors</t>
+          <t>p95 = 852ms, 0% errors</t>
         </is>
       </c>
       <c r="H75" s="14" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
@@ -4553,11 +4553,11 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>p95 = 217ms, 0% errors</t>
+          <t>p95 = 633ms, 0% errors</t>
         </is>
       </c>
       <c r="H76" s="11" t="n">
-        <v>2.47</v>
+        <v>5.71</v>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
@@ -4603,11 +4603,11 @@
       </c>
       <c r="G77" s="15" t="inlineStr">
         <is>
-          <t>p95 = 767ms, 0% errors</t>
+          <t>p95 = 518ms, 0% errors</t>
         </is>
       </c>
       <c r="H77" s="14" t="n">
-        <v>5.48</v>
+        <v>4.5</v>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
@@ -4653,11 +4653,11 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>p95 = 632ms, 0% errors</t>
+          <t>p95 = 440ms, 0% errors</t>
         </is>
       </c>
       <c r="H78" s="11" t="n">
-        <v>8.4</v>
+        <v>6.96</v>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
@@ -4703,11 +4703,11 @@
       </c>
       <c r="G79" s="15" t="inlineStr">
         <is>
-          <t>p95 = 594ms, 0% errors</t>
+          <t>p95 = 253ms, 0% errors</t>
         </is>
       </c>
       <c r="H79" s="14" t="n">
-        <v>2.58</v>
+        <v>4.36</v>
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
@@ -4753,11 +4753,11 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>p95 = 541ms, 0% errors</t>
+          <t>p95 = 780ms, 0% errors</t>
         </is>
       </c>
       <c r="H80" s="11" t="n">
-        <v>4.51</v>
+        <v>2.13</v>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
@@ -4803,11 +4803,11 @@
       </c>
       <c r="G81" s="15" t="inlineStr">
         <is>
-          <t>p95 = 598ms, 0% errors</t>
+          <t>p95 = 533ms, 0% errors</t>
         </is>
       </c>
       <c r="H81" s="14" t="n">
-        <v>5.01</v>
+        <v>11.51</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
@@ -4853,11 +4853,11 @@
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>p95 = 721ms, 0% errors</t>
+          <t>p95 = 189ms, 0% errors</t>
         </is>
       </c>
       <c r="H82" s="11" t="n">
-        <v>11.82</v>
+        <v>10.21</v>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
@@ -4903,11 +4903,11 @@
       </c>
       <c r="G83" s="15" t="inlineStr">
         <is>
-          <t>p95 = 670ms, 0% errors</t>
+          <t>p95 = 262ms, 0% errors</t>
         </is>
       </c>
       <c r="H83" s="14" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
@@ -4953,11 +4953,11 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>p95 = 767ms, 0% errors</t>
+          <t>p95 = 774ms, 0% errors</t>
         </is>
       </c>
       <c r="H84" s="11" t="n">
-        <v>7.66</v>
+        <v>8.56</v>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
@@ -5003,11 +5003,11 @@
       </c>
       <c r="G85" s="15" t="inlineStr">
         <is>
-          <t>p95 = 853ms, 0% errors</t>
+          <t>p95 = 574ms, 0% errors</t>
         </is>
       </c>
       <c r="H85" s="14" t="n">
-        <v>2.47</v>
+        <v>2.87</v>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
@@ -5053,11 +5053,11 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>p95 = 250ms, 0% errors</t>
+          <t>p95 = 850ms, 0% errors</t>
         </is>
       </c>
       <c r="H86" s="11" t="n">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
@@ -5103,11 +5103,11 @@
       </c>
       <c r="G87" s="15" t="inlineStr">
         <is>
-          <t>p95 = 635ms, 0% errors</t>
+          <t>p95 = 708ms, 0% errors</t>
         </is>
       </c>
       <c r="H87" s="14" t="n">
-        <v>7.6</v>
+        <v>10.93</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
@@ -5153,11 +5153,11 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>p95 = 601ms, 0% errors</t>
+          <t>p95 = 402ms, 0% errors</t>
         </is>
       </c>
       <c r="H88" s="11" t="n">
-        <v>4.5</v>
+        <v>8.1</v>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
@@ -5203,11 +5203,11 @@
       </c>
       <c r="G89" s="15" t="inlineStr">
         <is>
-          <t>p95 = 358ms, 0% errors</t>
+          <t>p95 = 539ms, 0% errors</t>
         </is>
       </c>
       <c r="H89" s="14" t="n">
-        <v>11.32</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
@@ -5253,11 +5253,11 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>p95 = 433ms, 0% errors</t>
+          <t>p95 = 314ms, 0% errors</t>
         </is>
       </c>
       <c r="H90" s="11" t="n">
-        <v>4.84</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
@@ -5303,11 +5303,11 @@
       </c>
       <c r="G91" s="15" t="inlineStr">
         <is>
-          <t>p95 = 333ms, 0% errors</t>
+          <t>p95 = 394ms, 0% errors</t>
         </is>
       </c>
       <c r="H91" s="14" t="n">
-        <v>4.14</v>
+        <v>5.01</v>
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
@@ -5353,11 +5353,11 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>p95 = 241ms, 0% errors</t>
+          <t>p95 = 868ms, 0% errors</t>
         </is>
       </c>
       <c r="H92" s="11" t="n">
-        <v>3.35</v>
+        <v>9.94</v>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
@@ -5403,11 +5403,11 @@
       </c>
       <c r="G93" s="15" t="inlineStr">
         <is>
-          <t>p95 = 515ms, 0% errors</t>
+          <t>p95 = 507ms, 0% errors</t>
         </is>
       </c>
       <c r="H93" s="14" t="n">
-        <v>11.42</v>
+        <v>8.1</v>
       </c>
       <c r="I93" s="14" t="inlineStr">
         <is>
@@ -5453,11 +5453,11 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>p95 = 187ms, 0% errors</t>
+          <t>p95 = 370ms, 0% errors</t>
         </is>
       </c>
       <c r="H94" s="11" t="n">
-        <v>9.59</v>
+        <v>10.48</v>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
@@ -5503,11 +5503,11 @@
       </c>
       <c r="G95" s="15" t="inlineStr">
         <is>
-          <t>p95 = 597ms, 0% errors</t>
+          <t>p95 = 588ms, 0% errors</t>
         </is>
       </c>
       <c r="H95" s="14" t="n">
-        <v>7.83</v>
+        <v>4.81</v>
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
@@ -5553,11 +5553,11 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>p95 = 573ms, 0% errors</t>
+          <t>p95 = 516ms, 0% errors</t>
         </is>
       </c>
       <c r="H96" s="11" t="n">
-        <v>7.87</v>
+        <v>4.96</v>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
@@ -5603,11 +5603,11 @@
       </c>
       <c r="G97" s="15" t="inlineStr">
         <is>
-          <t>p95 = 682ms, 0% errors</t>
+          <t>p95 = 202ms, 0% errors</t>
         </is>
       </c>
       <c r="H97" s="14" t="n">
-        <v>5.59</v>
+        <v>5.39</v>
       </c>
       <c r="I97" s="14" t="inlineStr">
         <is>
@@ -5653,11 +5653,11 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>p95 = 664ms, 0% errors</t>
+          <t>p95 = 678ms, 0% errors</t>
         </is>
       </c>
       <c r="H98" s="11" t="n">
-        <v>11.87</v>
+        <v>11.98</v>
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
@@ -5703,11 +5703,11 @@
       </c>
       <c r="G99" s="15" t="inlineStr">
         <is>
-          <t>p95 = 874ms, 0% errors</t>
+          <t>p95 = 379ms, 0% errors</t>
         </is>
       </c>
       <c r="H99" s="14" t="n">
-        <v>9.41</v>
+        <v>7.25</v>
       </c>
       <c r="I99" s="14" t="inlineStr">
         <is>
@@ -5753,11 +5753,11 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>p95 = 400ms, 0% errors</t>
+          <t>p95 = 783ms, 0% errors</t>
         </is>
       </c>
       <c r="H100" s="11" t="n">
-        <v>9</v>
+        <v>2.51</v>
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
@@ -5803,11 +5803,11 @@
       </c>
       <c r="G101" s="15" t="inlineStr">
         <is>
-          <t>p95 = 393ms, 0% errors</t>
+          <t>p95 = 428ms, 0% errors</t>
         </is>
       </c>
       <c r="H101" s="14" t="n">
-        <v>2.31</v>
+        <v>6.59</v>
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
@@ -5853,11 +5853,11 @@
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>p95 = 355ms, 0% errors</t>
+          <t>p95 = 674ms, 0% errors</t>
         </is>
       </c>
       <c r="H102" s="11" t="n">
-        <v>10.66</v>
+        <v>4.32</v>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
@@ -5903,11 +5903,11 @@
       </c>
       <c r="G103" s="15" t="inlineStr">
         <is>
-          <t>p95 = 382ms, 0% errors</t>
+          <t>p95 = 766ms, 0% errors</t>
         </is>
       </c>
       <c r="H103" s="14" t="n">
-        <v>2.93</v>
+        <v>9.1</v>
       </c>
       <c r="I103" s="14" t="inlineStr">
         <is>
@@ -5953,11 +5953,11 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>p95 = 600ms, 0% errors</t>
+          <t>p95 = 838ms, 0% errors</t>
         </is>
       </c>
       <c r="H104" s="11" t="n">
-        <v>10.76</v>
+        <v>4.44</v>
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
@@ -6003,11 +6003,11 @@
       </c>
       <c r="G105" s="15" t="inlineStr">
         <is>
-          <t>p95 = 628ms, 0% errors</t>
+          <t>p95 = 517ms, 0% errors</t>
         </is>
       </c>
       <c r="H105" s="14" t="n">
-        <v>2.9</v>
+        <v>8.65</v>
       </c>
       <c r="I105" s="14" t="inlineStr">
         <is>
@@ -6053,11 +6053,11 @@
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>p95 = 656ms, 0% errors</t>
+          <t>p95 = 563ms, 0% errors</t>
         </is>
       </c>
       <c r="H106" s="11" t="n">
-        <v>11.52</v>
+        <v>8.83</v>
       </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
@@ -6103,11 +6103,11 @@
       </c>
       <c r="G107" s="15" t="inlineStr">
         <is>
-          <t>p95 = 516ms, 0% errors</t>
+          <t>p95 = 361ms, 0% errors</t>
         </is>
       </c>
       <c r="H107" s="14" t="n">
-        <v>11.66</v>
+        <v>1.68</v>
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
@@ -6153,11 +6153,11 @@
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>p95 = 267ms, 0% errors</t>
+          <t>p95 = 399ms, 0% errors</t>
         </is>
       </c>
       <c r="H108" s="11" t="n">
-        <v>8.75</v>
+        <v>4.7</v>
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
@@ -6203,11 +6203,11 @@
       </c>
       <c r="G109" s="15" t="inlineStr">
         <is>
-          <t>p95 = 374ms, 0% errors</t>
+          <t>p95 = 370ms, 0% errors</t>
         </is>
       </c>
       <c r="H109" s="14" t="n">
-        <v>8.15</v>
+        <v>7.78</v>
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
@@ -6253,11 +6253,11 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>p95 = 498ms, 0% errors</t>
+          <t>p95 = 534ms, 0% errors</t>
         </is>
       </c>
       <c r="H110" s="11" t="n">
-        <v>2.69</v>
+        <v>11.17</v>
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
@@ -6303,11 +6303,11 @@
       </c>
       <c r="G111" s="15" t="inlineStr">
         <is>
-          <t>p95 = 564ms, 0% errors</t>
+          <t>p95 = 493ms, 0% errors</t>
         </is>
       </c>
       <c r="H111" s="14" t="n">
-        <v>7.12</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
@@ -6353,11 +6353,11 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>p95 = 822ms, 0% errors</t>
+          <t>p95 = 777ms, 0% errors</t>
         </is>
       </c>
       <c r="H112" s="11" t="n">
-        <v>5.63</v>
+        <v>5.75</v>
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
@@ -6403,11 +6403,11 @@
       </c>
       <c r="G113" s="15" t="inlineStr">
         <is>
-          <t>p95 = 508ms, 0% errors</t>
+          <t>p95 = 473ms, 0% errors</t>
         </is>
       </c>
       <c r="H113" s="14" t="n">
-        <v>6.34</v>
+        <v>6.29</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
@@ -6453,11 +6453,11 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>p95 = 397ms, 0% errors</t>
+          <t>p95 = 234ms, 0% errors</t>
         </is>
       </c>
       <c r="H114" s="11" t="n">
-        <v>3.89</v>
+        <v>9.56</v>
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
@@ -6503,11 +6503,11 @@
       </c>
       <c r="G115" s="15" t="inlineStr">
         <is>
-          <t>p95 = 201ms, 0% errors</t>
+          <t>p95 = 571ms, 0% errors</t>
         </is>
       </c>
       <c r="H115" s="14" t="n">
-        <v>6.62</v>
+        <v>3.37</v>
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
@@ -6553,11 +6553,11 @@
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>p95 = 704ms, 0% errors</t>
+          <t>p95 = 723ms, 0% errors</t>
         </is>
       </c>
       <c r="H116" s="11" t="n">
-        <v>6.25</v>
+        <v>4.58</v>
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
@@ -6603,11 +6603,11 @@
       </c>
       <c r="G117" s="15" t="inlineStr">
         <is>
-          <t>p95 = 562ms, 0% errors</t>
+          <t>p95 = 687ms, 0% errors</t>
         </is>
       </c>
       <c r="H117" s="14" t="n">
-        <v>2.95</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
@@ -6653,11 +6653,11 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>p95 = 519ms, 0% errors</t>
+          <t>p95 = 637ms, 0% errors</t>
         </is>
       </c>
       <c r="H118" s="11" t="n">
-        <v>6.07</v>
+        <v>5.77</v>
       </c>
       <c r="I118" s="11" t="inlineStr">
         <is>
@@ -6703,11 +6703,11 @@
       </c>
       <c r="G119" s="15" t="inlineStr">
         <is>
-          <t>p95 = 580ms, 0% errors</t>
+          <t>p95 = 599ms, 0% errors</t>
         </is>
       </c>
       <c r="H119" s="14" t="n">
-        <v>11.78</v>
+        <v>6.68</v>
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
@@ -6753,11 +6753,11 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>p95 = 864ms, 0% errors</t>
+          <t>p95 = 737ms, 0% errors</t>
         </is>
       </c>
       <c r="H120" s="11" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="I120" s="11" t="inlineStr">
         <is>
@@ -6803,11 +6803,11 @@
       </c>
       <c r="G121" s="15" t="inlineStr">
         <is>
-          <t>p95 = 820ms, 0% errors</t>
+          <t>p95 = 817ms, 0% errors</t>
         </is>
       </c>
       <c r="H121" s="14" t="n">
-        <v>3.07</v>
+        <v>11.9</v>
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
@@ -6853,11 +6853,11 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>p95 = 763ms, 0% errors</t>
+          <t>p95 = 386ms, 0% errors</t>
         </is>
       </c>
       <c r="H122" s="11" t="n">
-        <v>1.71</v>
+        <v>3.89</v>
       </c>
       <c r="I122" s="11" t="inlineStr">
         <is>
@@ -6903,11 +6903,11 @@
       </c>
       <c r="G123" s="15" t="inlineStr">
         <is>
-          <t>p95 = 805ms, 0% errors</t>
+          <t>p95 = 346ms, 0% errors</t>
         </is>
       </c>
       <c r="H123" s="14" t="n">
-        <v>11.39</v>
+        <v>4.37</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
@@ -6953,11 +6953,11 @@
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>p95 = 590ms, 0% errors</t>
+          <t>p95 = 360ms, 0% errors</t>
         </is>
       </c>
       <c r="H124" s="11" t="n">
-        <v>5.35</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
@@ -7003,11 +7003,11 @@
       </c>
       <c r="G125" s="15" t="inlineStr">
         <is>
-          <t>p95 = 875ms, 0% errors</t>
+          <t>p95 = 310ms, 0% errors</t>
         </is>
       </c>
       <c r="H125" s="14" t="n">
-        <v>4.04</v>
+        <v>9.82</v>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
@@ -7053,11 +7053,11 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>p95 = 552ms, 0% errors</t>
+          <t>p95 = 565ms, 0% errors</t>
         </is>
       </c>
       <c r="H126" s="11" t="n">
-        <v>3.65</v>
+        <v>6.83</v>
       </c>
       <c r="I126" s="11" t="inlineStr">
         <is>
@@ -7103,11 +7103,11 @@
       </c>
       <c r="G127" s="15" t="inlineStr">
         <is>
-          <t>p95 = 668ms, 0% errors</t>
+          <t>p95 = 716ms, 0% errors</t>
         </is>
       </c>
       <c r="H127" s="14" t="n">
-        <v>2.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
@@ -7153,11 +7153,11 @@
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>p95 = 626ms, 0% errors</t>
+          <t>p95 = 802ms, 0% errors</t>
         </is>
       </c>
       <c r="H128" s="11" t="n">
-        <v>7.69</v>
+        <v>5.44</v>
       </c>
       <c r="I128" s="11" t="inlineStr">
         <is>
@@ -7203,11 +7203,11 @@
       </c>
       <c r="G129" s="15" t="inlineStr">
         <is>
-          <t>p95 = 726ms, 0% errors</t>
+          <t>p95 = 548ms, 0% errors</t>
         </is>
       </c>
       <c r="H129" s="14" t="n">
-        <v>10.91</v>
+        <v>8.51</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
@@ -7253,11 +7253,11 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>p95 = 691ms, 0% errors</t>
+          <t>p95 = 349ms, 0% errors</t>
         </is>
       </c>
       <c r="H130" s="11" t="n">
-        <v>5.81</v>
+        <v>2.31</v>
       </c>
       <c r="I130" s="11" t="inlineStr">
         <is>
@@ -7303,11 +7303,11 @@
       </c>
       <c r="G131" s="15" t="inlineStr">
         <is>
-          <t>p95 = 570ms, 0% errors</t>
+          <t>p95 = 647ms, 0% errors</t>
         </is>
       </c>
       <c r="H131" s="14" t="n">
-        <v>1.59</v>
+        <v>5.51</v>
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
@@ -7353,11 +7353,11 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>p95 = 698ms, 0% errors</t>
+          <t>p95 = 425ms, 0% errors</t>
         </is>
       </c>
       <c r="H132" s="11" t="n">
-        <v>9.67</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="I132" s="11" t="inlineStr">
         <is>
@@ -7403,11 +7403,11 @@
       </c>
       <c r="G133" s="15" t="inlineStr">
         <is>
-          <t>p95 = 279ms, 0% errors</t>
+          <t>p95 = 694ms, 0% errors</t>
         </is>
       </c>
       <c r="H133" s="14" t="n">
-        <v>9.699999999999999</v>
+        <v>4.73</v>
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
@@ -7453,11 +7453,11 @@
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>p95 = 253ms, 0% errors</t>
+          <t>p95 = 871ms, 0% errors</t>
         </is>
       </c>
       <c r="H134" s="11" t="n">
-        <v>7.03</v>
+        <v>8.6</v>
       </c>
       <c r="I134" s="11" t="inlineStr">
         <is>
@@ -7503,11 +7503,11 @@
       </c>
       <c r="G135" s="15" t="inlineStr">
         <is>
-          <t>p95 = 215ms, 0% errors</t>
+          <t>p95 = 327ms, 0% errors</t>
         </is>
       </c>
       <c r="H135" s="14" t="n">
-        <v>11.35</v>
+        <v>2.12</v>
       </c>
       <c r="I135" s="14" t="inlineStr">
         <is>
@@ -7553,11 +7553,11 @@
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>p95 = 542ms, 0% errors</t>
+          <t>p95 = 391ms, 0% errors</t>
         </is>
       </c>
       <c r="H136" s="11" t="n">
-        <v>10.95</v>
+        <v>3.25</v>
       </c>
       <c r="I136" s="11" t="inlineStr">
         <is>
@@ -7603,11 +7603,11 @@
       </c>
       <c r="G137" s="15" t="inlineStr">
         <is>
-          <t>p95 = 884ms, 0% errors</t>
+          <t>p95 = 222ms, 0% errors</t>
         </is>
       </c>
       <c r="H137" s="14" t="n">
-        <v>5.02</v>
+        <v>8.24</v>
       </c>
       <c r="I137" s="14" t="inlineStr">
         <is>
@@ -7653,11 +7653,11 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>p95 = 209ms, 0% errors</t>
+          <t>p95 = 787ms, 0% errors</t>
         </is>
       </c>
       <c r="H138" s="11" t="n">
-        <v>7</v>
+        <v>11.67</v>
       </c>
       <c r="I138" s="11" t="inlineStr">
         <is>
@@ -7703,11 +7703,11 @@
       </c>
       <c r="G139" s="15" t="inlineStr">
         <is>
-          <t>p95 = 541ms, 0% errors</t>
+          <t>p95 = 194ms, 0% errors</t>
         </is>
       </c>
       <c r="H139" s="14" t="n">
-        <v>6.34</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I139" s="14" t="inlineStr">
         <is>
@@ -7753,11 +7753,11 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>p95 = 449ms, 0% errors</t>
+          <t>p95 = 612ms, 0% errors</t>
         </is>
       </c>
       <c r="H140" s="11" t="n">
-        <v>5.77</v>
+        <v>3.87</v>
       </c>
       <c r="I140" s="11" t="inlineStr">
         <is>
@@ -7803,11 +7803,11 @@
       </c>
       <c r="G141" s="15" t="inlineStr">
         <is>
-          <t>p95 = 527ms, 0% errors</t>
+          <t>p95 = 319ms, 0% errors</t>
         </is>
       </c>
       <c r="H141" s="14" t="n">
-        <v>5.46</v>
+        <v>7.1</v>
       </c>
       <c r="I141" s="14" t="inlineStr">
         <is>
@@ -7853,11 +7853,11 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>p95 = 562ms, 0% errors</t>
+          <t>p95 = 571ms, 0% errors</t>
         </is>
       </c>
       <c r="H142" s="11" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="I142" s="11" t="inlineStr">
         <is>
@@ -7903,11 +7903,11 @@
       </c>
       <c r="G143" s="15" t="inlineStr">
         <is>
-          <t>p95 = 713ms, 0% errors</t>
+          <t>p95 = 276ms, 0% errors</t>
         </is>
       </c>
       <c r="H143" s="14" t="n">
-        <v>7.71</v>
+        <v>5.33</v>
       </c>
       <c r="I143" s="14" t="inlineStr">
         <is>
@@ -7953,11 +7953,11 @@
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>p95 = 519ms, 0% errors</t>
+          <t>p95 = 705ms, 0% errors</t>
         </is>
       </c>
       <c r="H144" s="11" t="n">
-        <v>1.77</v>
+        <v>7.11</v>
       </c>
       <c r="I144" s="11" t="inlineStr">
         <is>
@@ -8003,11 +8003,11 @@
       </c>
       <c r="G145" s="15" t="inlineStr">
         <is>
-          <t>p95 = 867ms, 0% errors</t>
+          <t>p95 = 591ms, 0% errors</t>
         </is>
       </c>
       <c r="H145" s="14" t="n">
-        <v>6.23</v>
+        <v>3.26</v>
       </c>
       <c r="I145" s="14" t="inlineStr">
         <is>
@@ -8053,11 +8053,11 @@
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>p95 = 850ms, 0% errors</t>
+          <t>p95 = 855ms, 0% errors</t>
         </is>
       </c>
       <c r="H146" s="11" t="n">
-        <v>2.02</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I146" s="11" t="inlineStr">
         <is>
@@ -8103,11 +8103,11 @@
       </c>
       <c r="G147" s="15" t="inlineStr">
         <is>
-          <t>p95 = 595ms, 0% errors</t>
+          <t>p95 = 868ms, 0% errors</t>
         </is>
       </c>
       <c r="H147" s="14" t="n">
-        <v>5.19</v>
+        <v>7.14</v>
       </c>
       <c r="I147" s="14" t="inlineStr">
         <is>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>p95 = 297ms, 0% errors</t>
+          <t>p95 = 192ms, 0% errors</t>
         </is>
       </c>
       <c r="H148" s="11" t="n">
-        <v>3.76</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="I148" s="11" t="inlineStr">
         <is>
@@ -8203,11 +8203,11 @@
       </c>
       <c r="G149" s="15" t="inlineStr">
         <is>
-          <t>p95 = 340ms, 0% errors</t>
+          <t>p95 = 324ms, 0% errors</t>
         </is>
       </c>
       <c r="H149" s="14" t="n">
-        <v>6.36</v>
+        <v>2.26</v>
       </c>
       <c r="I149" s="14" t="inlineStr">
         <is>
@@ -8253,11 +8253,11 @@
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>p95 = 599ms, 0% errors</t>
+          <t>p95 = 666ms, 0% errors</t>
         </is>
       </c>
       <c r="H150" s="11" t="n">
-        <v>9.630000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="I150" s="11" t="inlineStr">
         <is>
@@ -8303,11 +8303,11 @@
       </c>
       <c r="G151" s="15" t="inlineStr">
         <is>
-          <t>p95 = 216ms, 0% errors</t>
+          <t>p95 = 450ms, 0% errors</t>
         </is>
       </c>
       <c r="H151" s="14" t="n">
-        <v>4.65</v>
+        <v>3.57</v>
       </c>
       <c r="I151" s="14" t="inlineStr">
         <is>
@@ -8353,11 +8353,11 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>p95 = 717ms, 0% errors</t>
+          <t>p95 = 472ms, 0% errors</t>
         </is>
       </c>
       <c r="H152" s="11" t="n">
-        <v>4.52</v>
+        <v>3.79</v>
       </c>
       <c r="I152" s="11" t="inlineStr">
         <is>
@@ -8403,11 +8403,11 @@
       </c>
       <c r="G153" s="15" t="inlineStr">
         <is>
-          <t>p95 = 326ms, 0% errors</t>
+          <t>p95 = 443ms, 0% errors</t>
         </is>
       </c>
       <c r="H153" s="14" t="n">
-        <v>6.69</v>
+        <v>7.17</v>
       </c>
       <c r="I153" s="14" t="inlineStr">
         <is>
@@ -8453,11 +8453,11 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>p95 = 656ms, 0% errors</t>
+          <t>p95 = 835ms, 0% errors</t>
         </is>
       </c>
       <c r="H154" s="11" t="n">
-        <v>3.41</v>
+        <v>1.81</v>
       </c>
       <c r="I154" s="11" t="inlineStr">
         <is>
@@ -8503,11 +8503,11 @@
       </c>
       <c r="G155" s="15" t="inlineStr">
         <is>
-          <t>p95 = 665ms, 0% errors</t>
+          <t>p95 = 197ms, 0% errors</t>
         </is>
       </c>
       <c r="H155" s="14" t="n">
-        <v>9.17</v>
+        <v>10.54</v>
       </c>
       <c r="I155" s="14" t="inlineStr">
         <is>
@@ -8553,11 +8553,11 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>p95 = 649ms, 0% errors</t>
+          <t>p95 = 183ms, 0% errors</t>
         </is>
       </c>
       <c r="H156" s="11" t="n">
-        <v>9.539999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="I156" s="11" t="inlineStr">
         <is>
@@ -8603,11 +8603,11 @@
       </c>
       <c r="G157" s="15" t="inlineStr">
         <is>
-          <t>p95 = 579ms, 0% errors</t>
+          <t>p95 = 763ms, 0% errors</t>
         </is>
       </c>
       <c r="H157" s="14" t="n">
-        <v>3.94</v>
+        <v>4.46</v>
       </c>
       <c r="I157" s="14" t="inlineStr">
         <is>
@@ -8653,11 +8653,11 @@
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>p95 = 632ms, 0% errors</t>
+          <t>p95 = 858ms, 0% errors</t>
         </is>
       </c>
       <c r="H158" s="11" t="n">
-        <v>4.29</v>
+        <v>10.52</v>
       </c>
       <c r="I158" s="11" t="inlineStr">
         <is>
@@ -8703,11 +8703,11 @@
       </c>
       <c r="G159" s="15" t="inlineStr">
         <is>
-          <t>p95 = 394ms, 0% errors</t>
+          <t>p95 = 376ms, 0% errors</t>
         </is>
       </c>
       <c r="H159" s="14" t="n">
-        <v>6.97</v>
+        <v>4.93</v>
       </c>
       <c r="I159" s="14" t="inlineStr">
         <is>
@@ -8753,11 +8753,11 @@
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>p95 = 195ms, 0% errors</t>
+          <t>p95 = 792ms, 0% errors</t>
         </is>
       </c>
       <c r="H160" s="11" t="n">
-        <v>4.8</v>
+        <v>10.82</v>
       </c>
       <c r="I160" s="11" t="inlineStr">
         <is>
@@ -8803,11 +8803,11 @@
       </c>
       <c r="G161" s="15" t="inlineStr">
         <is>
-          <t>p95 = 823ms, 0% errors</t>
+          <t>p95 = 828ms, 0% errors</t>
         </is>
       </c>
       <c r="H161" s="14" t="n">
-        <v>3.61</v>
+        <v>11.64</v>
       </c>
       <c r="I161" s="14" t="inlineStr">
         <is>
@@ -8853,11 +8853,11 @@
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>p95 = 608ms, 0% errors</t>
+          <t>p95 = 550ms, 0% errors</t>
         </is>
       </c>
       <c r="H162" s="11" t="n">
-        <v>11.11</v>
+        <v>5.89</v>
       </c>
       <c r="I162" s="11" t="inlineStr">
         <is>
@@ -8903,11 +8903,11 @@
       </c>
       <c r="G163" s="15" t="inlineStr">
         <is>
-          <t>p95 = 518ms, 0% errors</t>
+          <t>p95 = 492ms, 0% errors</t>
         </is>
       </c>
       <c r="H163" s="14" t="n">
-        <v>9.58</v>
+        <v>7.22</v>
       </c>
       <c r="I163" s="14" t="inlineStr">
         <is>
@@ -8953,11 +8953,11 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>p95 = 832ms, 0% errors</t>
+          <t>p95 = 573ms, 0% errors</t>
         </is>
       </c>
       <c r="H164" s="11" t="n">
-        <v>8.390000000000001</v>
+        <v>2.29</v>
       </c>
       <c r="I164" s="11" t="inlineStr">
         <is>
@@ -9003,11 +9003,11 @@
       </c>
       <c r="G165" s="15" t="inlineStr">
         <is>
-          <t>p95 = 665ms, 0% errors</t>
+          <t>p95 = 887ms, 0% errors</t>
         </is>
       </c>
       <c r="H165" s="14" t="n">
-        <v>5.25</v>
+        <v>1.91</v>
       </c>
       <c r="I165" s="14" t="inlineStr">
         <is>
@@ -9053,11 +9053,11 @@
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
-          <t>p95 = 816ms, 0% errors</t>
+          <t>p95 = 674ms, 0% errors</t>
         </is>
       </c>
       <c r="H166" s="11" t="n">
-        <v>6.59</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I166" s="11" t="inlineStr">
         <is>
@@ -9103,11 +9103,11 @@
       </c>
       <c r="G167" s="15" t="inlineStr">
         <is>
-          <t>p95 = 312ms, 0% errors</t>
+          <t>p95 = 189ms, 0% errors</t>
         </is>
       </c>
       <c r="H167" s="14" t="n">
-        <v>8.06</v>
+        <v>7.13</v>
       </c>
       <c r="I167" s="14" t="inlineStr">
         <is>
@@ -9153,11 +9153,11 @@
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
-          <t>p95 = 377ms, 0% errors</t>
+          <t>p95 = 609ms, 0% errors</t>
         </is>
       </c>
       <c r="H168" s="11" t="n">
-        <v>3.69</v>
+        <v>10.79</v>
       </c>
       <c r="I168" s="11" t="inlineStr">
         <is>
@@ -9203,11 +9203,11 @@
       </c>
       <c r="G169" s="15" t="inlineStr">
         <is>
-          <t>p95 = 435ms, 0% errors</t>
+          <t>p95 = 627ms, 0% errors</t>
         </is>
       </c>
       <c r="H169" s="14" t="n">
-        <v>5.75</v>
+        <v>5.92</v>
       </c>
       <c r="I169" s="14" t="inlineStr">
         <is>
@@ -9253,11 +9253,11 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>p95 = 267ms, 0% errors</t>
+          <t>p95 = 531ms, 0% errors</t>
         </is>
       </c>
       <c r="H170" s="11" t="n">
-        <v>10.05</v>
+        <v>3.23</v>
       </c>
       <c r="I170" s="11" t="inlineStr">
         <is>
@@ -9303,11 +9303,11 @@
       </c>
       <c r="G171" s="15" t="inlineStr">
         <is>
-          <t>p95 = 214ms, 0% errors</t>
+          <t>p95 = 816ms, 0% errors</t>
         </is>
       </c>
       <c r="H171" s="14" t="n">
-        <v>5.8</v>
+        <v>7.64</v>
       </c>
       <c r="I171" s="14" t="inlineStr">
         <is>
@@ -9353,11 +9353,11 @@
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>p95 = 337ms, 0% errors</t>
+          <t>p95 = 583ms, 0% errors</t>
         </is>
       </c>
       <c r="H172" s="11" t="n">
-        <v>3.62</v>
+        <v>6.96</v>
       </c>
       <c r="I172" s="11" t="inlineStr">
         <is>
@@ -9403,11 +9403,11 @@
       </c>
       <c r="G173" s="15" t="inlineStr">
         <is>
-          <t>p95 = 506ms, 0% errors</t>
+          <t>p95 = 735ms, 0% errors</t>
         </is>
       </c>
       <c r="H173" s="14" t="n">
-        <v>10.8</v>
+        <v>5.43</v>
       </c>
       <c r="I173" s="14" t="inlineStr">
         <is>
@@ -9453,11 +9453,11 @@
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>p95 = 723ms, 0% errors</t>
+          <t>p95 = 809ms, 0% errors</t>
         </is>
       </c>
       <c r="H174" s="11" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="I174" s="11" t="inlineStr">
         <is>
@@ -9503,11 +9503,11 @@
       </c>
       <c r="G175" s="15" t="inlineStr">
         <is>
-          <t>p95 = 686ms, 0% errors</t>
+          <t>p95 = 191ms, 0% errors</t>
         </is>
       </c>
       <c r="H175" s="14" t="n">
-        <v>3.5</v>
+        <v>8.17</v>
       </c>
       <c r="I175" s="14" t="inlineStr">
         <is>
@@ -9553,11 +9553,11 @@
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>p95 = 351ms, 0% errors</t>
+          <t>p95 = 358ms, 0% errors</t>
         </is>
       </c>
       <c r="H176" s="11" t="n">
-        <v>8.76</v>
+        <v>6.01</v>
       </c>
       <c r="I176" s="11" t="inlineStr">
         <is>
@@ -9603,11 +9603,11 @@
       </c>
       <c r="G177" s="15" t="inlineStr">
         <is>
-          <t>p95 = 589ms, 0% errors</t>
+          <t>p95 = 735ms, 0% errors</t>
         </is>
       </c>
       <c r="H177" s="14" t="n">
-        <v>2.2</v>
+        <v>11.01</v>
       </c>
       <c r="I177" s="14" t="inlineStr">
         <is>
@@ -9653,11 +9653,11 @@
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
-          <t>p95 = 340ms, 0% errors</t>
+          <t>p95 = 478ms, 0% errors</t>
         </is>
       </c>
       <c r="H178" s="11" t="n">
-        <v>10.44</v>
+        <v>5.58</v>
       </c>
       <c r="I178" s="11" t="inlineStr">
         <is>
@@ -9703,11 +9703,11 @@
       </c>
       <c r="G179" s="15" t="inlineStr">
         <is>
-          <t>p95 = 247ms, 0% errors</t>
+          <t>p95 = 397ms, 0% errors</t>
         </is>
       </c>
       <c r="H179" s="14" t="n">
-        <v>4.86</v>
+        <v>2.73</v>
       </c>
       <c r="I179" s="14" t="inlineStr">
         <is>
@@ -9753,11 +9753,11 @@
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>p95 = 214ms, 0% errors</t>
+          <t>p95 = 256ms, 0% errors</t>
         </is>
       </c>
       <c r="H180" s="11" t="n">
-        <v>3.73</v>
+        <v>7.9</v>
       </c>
       <c r="I180" s="11" t="inlineStr">
         <is>
@@ -9803,11 +9803,11 @@
       </c>
       <c r="G181" s="15" t="inlineStr">
         <is>
-          <t>p95 = 375ms, 0% errors</t>
+          <t>p95 = 558ms, 0% errors</t>
         </is>
       </c>
       <c r="H181" s="14" t="n">
-        <v>2.21</v>
+        <v>6.28</v>
       </c>
       <c r="I181" s="14" t="inlineStr">
         <is>
@@ -9853,11 +9853,11 @@
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
-          <t>p95 = 225ms, 0% errors</t>
+          <t>p95 = 575ms, 0% errors</t>
         </is>
       </c>
       <c r="H182" s="11" t="n">
-        <v>5.69</v>
+        <v>10.05</v>
       </c>
       <c r="I182" s="11" t="inlineStr">
         <is>
@@ -9903,11 +9903,11 @@
       </c>
       <c r="G183" s="15" t="inlineStr">
         <is>
-          <t>p95 = 653ms, 0% errors</t>
+          <t>p95 = 876ms, 0% errors</t>
         </is>
       </c>
       <c r="H183" s="14" t="n">
-        <v>9.59</v>
+        <v>11.98</v>
       </c>
       <c r="I183" s="14" t="inlineStr">
         <is>
@@ -9953,11 +9953,11 @@
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
-          <t>p95 = 244ms, 0% errors</t>
+          <t>p95 = 570ms, 0% errors</t>
         </is>
       </c>
       <c r="H184" s="11" t="n">
-        <v>10.02</v>
+        <v>10.15</v>
       </c>
       <c r="I184" s="11" t="inlineStr">
         <is>
@@ -10003,11 +10003,11 @@
       </c>
       <c r="G185" s="15" t="inlineStr">
         <is>
-          <t>p95 = 425ms, 0% errors</t>
+          <t>p95 = 232ms, 0% errors</t>
         </is>
       </c>
       <c r="H185" s="14" t="n">
-        <v>2.74</v>
+        <v>10.33</v>
       </c>
       <c r="I185" s="14" t="inlineStr">
         <is>
@@ -10053,11 +10053,11 @@
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
-          <t>p95 = 421ms, 0% errors</t>
+          <t>p95 = 665ms, 0% errors</t>
         </is>
       </c>
       <c r="H186" s="11" t="n">
-        <v>2.83</v>
+        <v>5.04</v>
       </c>
       <c r="I186" s="11" t="inlineStr">
         <is>
@@ -10103,11 +10103,11 @@
       </c>
       <c r="G187" s="15" t="inlineStr">
         <is>
-          <t>p95 = 505ms, 0% errors</t>
+          <t>p95 = 337ms, 0% errors</t>
         </is>
       </c>
       <c r="H187" s="14" t="n">
-        <v>6.33</v>
+        <v>4.57</v>
       </c>
       <c r="I187" s="14" t="inlineStr">
         <is>
@@ -10153,11 +10153,11 @@
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
-          <t>p95 = 805ms, 0% errors</t>
+          <t>p95 = 363ms, 0% errors</t>
         </is>
       </c>
       <c r="H188" s="11" t="n">
-        <v>8.42</v>
+        <v>11.27</v>
       </c>
       <c r="I188" s="11" t="inlineStr">
         <is>
@@ -10203,11 +10203,11 @@
       </c>
       <c r="G189" s="15" t="inlineStr">
         <is>
-          <t>p95 = 479ms, 0% errors</t>
+          <t>p95 = 296ms, 0% errors</t>
         </is>
       </c>
       <c r="H189" s="14" t="n">
-        <v>10.64</v>
+        <v>4.31</v>
       </c>
       <c r="I189" s="14" t="inlineStr">
         <is>
@@ -10253,11 +10253,11 @@
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
-          <t>p95 = 777ms, 0% errors</t>
+          <t>p95 = 201ms, 0% errors</t>
         </is>
       </c>
       <c r="H190" s="11" t="n">
-        <v>2.38</v>
+        <v>5.44</v>
       </c>
       <c r="I190" s="11" t="inlineStr">
         <is>
@@ -10303,11 +10303,11 @@
       </c>
       <c r="G191" s="15" t="inlineStr">
         <is>
-          <t>p95 = 789ms, 0% errors</t>
+          <t>p95 = 259ms, 0% errors</t>
         </is>
       </c>
       <c r="H191" s="14" t="n">
-        <v>10.5</v>
+        <v>4.65</v>
       </c>
       <c r="I191" s="14" t="inlineStr">
         <is>
@@ -10353,11 +10353,11 @@
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
-          <t>p95 = 259ms, 0% errors</t>
+          <t>p95 = 564ms, 0% errors</t>
         </is>
       </c>
       <c r="H192" s="11" t="n">
-        <v>11.16</v>
+        <v>4.89</v>
       </c>
       <c r="I192" s="11" t="inlineStr">
         <is>
@@ -10403,11 +10403,11 @@
       </c>
       <c r="G193" s="15" t="inlineStr">
         <is>
-          <t>p95 = 742ms, 0% errors</t>
+          <t>p95 = 259ms, 0% errors</t>
         </is>
       </c>
       <c r="H193" s="14" t="n">
-        <v>4.55</v>
+        <v>11.55</v>
       </c>
       <c r="I193" s="14" t="inlineStr">
         <is>
@@ -10453,11 +10453,11 @@
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
-          <t>p95 = 407ms, 0% errors</t>
+          <t>p95 = 665ms, 0% errors</t>
         </is>
       </c>
       <c r="H194" s="11" t="n">
-        <v>4.16</v>
+        <v>7.46</v>
       </c>
       <c r="I194" s="11" t="inlineStr">
         <is>
@@ -10503,11 +10503,11 @@
       </c>
       <c r="G195" s="15" t="inlineStr">
         <is>
-          <t>p95 = 396ms, 0% errors</t>
+          <t>p95 = 556ms, 0% errors</t>
         </is>
       </c>
       <c r="H195" s="14" t="n">
-        <v>6.04</v>
+        <v>2.56</v>
       </c>
       <c r="I195" s="14" t="inlineStr">
         <is>
@@ -10553,11 +10553,11 @@
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
-          <t>p95 = 288ms, 0% errors</t>
+          <t>p95 = 766ms, 0% errors</t>
         </is>
       </c>
       <c r="H196" s="11" t="n">
-        <v>11.58</v>
+        <v>11.08</v>
       </c>
       <c r="I196" s="11" t="inlineStr">
         <is>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="G197" s="15" t="inlineStr">
         <is>
-          <t>p95 = 285ms, 0% errors</t>
+          <t>p95 = 802ms, 0% errors</t>
         </is>
       </c>
       <c r="H197" s="14" t="n">
-        <v>7.2</v>
+        <v>5.19</v>
       </c>
       <c r="I197" s="14" t="inlineStr">
         <is>
@@ -10653,11 +10653,11 @@
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
-          <t>p95 = 702ms, 0% errors</t>
+          <t>p95 = 404ms, 0% errors</t>
         </is>
       </c>
       <c r="H198" s="11" t="n">
-        <v>2.32</v>
+        <v>4.91</v>
       </c>
       <c r="I198" s="11" t="inlineStr">
         <is>
@@ -10703,11 +10703,11 @@
       </c>
       <c r="G199" s="15" t="inlineStr">
         <is>
-          <t>p95 = 569ms, 0% errors</t>
+          <t>p95 = 724ms, 0% errors</t>
         </is>
       </c>
       <c r="H199" s="14" t="n">
-        <v>2.32</v>
+        <v>7.74</v>
       </c>
       <c r="I199" s="14" t="inlineStr">
         <is>
@@ -10753,11 +10753,11 @@
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
-          <t>p95 = 853ms, 0% errors</t>
+          <t>p95 = 518ms, 0% errors</t>
         </is>
       </c>
       <c r="H200" s="11" t="n">
-        <v>8.949999999999999</v>
+        <v>6.24</v>
       </c>
       <c r="I200" s="11" t="inlineStr">
         <is>
@@ -10803,11 +10803,11 @@
       </c>
       <c r="G201" s="15" t="inlineStr">
         <is>
-          <t>p95 = 700ms, 0% errors</t>
+          <t>p95 = 226ms, 0% errors</t>
         </is>
       </c>
       <c r="H201" s="14" t="n">
-        <v>11.04</v>
+        <v>9.9</v>
       </c>
       <c r="I201" s="14" t="inlineStr">
         <is>
@@ -10853,11 +10853,11 @@
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
-          <t>p95 = 582ms, 0% errors</t>
+          <t>p95 = 444ms, 0% errors</t>
         </is>
       </c>
       <c r="H202" s="11" t="n">
-        <v>7.42</v>
+        <v>8.44</v>
       </c>
       <c r="I202" s="11" t="inlineStr">
         <is>
@@ -10903,11 +10903,11 @@
       </c>
       <c r="G203" s="15" t="inlineStr">
         <is>
-          <t>p95 = 843ms, 0% errors</t>
+          <t>p95 = 734ms, 0% errors</t>
         </is>
       </c>
       <c r="H203" s="14" t="n">
-        <v>6.86</v>
+        <v>7.31</v>
       </c>
       <c r="I203" s="14" t="inlineStr">
         <is>
@@ -10953,11 +10953,11 @@
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
-          <t>p95 = 571ms, 0% errors</t>
+          <t>p95 = 726ms, 0% errors</t>
         </is>
       </c>
       <c r="H204" s="11" t="n">
-        <v>6.42</v>
+        <v>2.54</v>
       </c>
       <c r="I204" s="11" t="inlineStr">
         <is>
@@ -11003,11 +11003,11 @@
       </c>
       <c r="G205" s="15" t="inlineStr">
         <is>
-          <t>p95 = 492ms, 0% errors</t>
+          <t>p95 = 722ms, 0% errors</t>
         </is>
       </c>
       <c r="H205" s="14" t="n">
-        <v>11.6</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="I205" s="14" t="inlineStr">
         <is>
@@ -11053,11 +11053,11 @@
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
-          <t>p95 = 282ms, 0% errors</t>
+          <t>p95 = 446ms, 0% errors</t>
         </is>
       </c>
       <c r="H206" s="11" t="n">
-        <v>5.54</v>
+        <v>3.1</v>
       </c>
       <c r="I206" s="11" t="inlineStr">
         <is>
@@ -11103,11 +11103,11 @@
       </c>
       <c r="G207" s="15" t="inlineStr">
         <is>
-          <t>p95 = 716ms, 0% errors</t>
+          <t>p95 = 827ms, 0% errors</t>
         </is>
       </c>
       <c r="H207" s="14" t="n">
-        <v>8.94</v>
+        <v>8.07</v>
       </c>
       <c r="I207" s="14" t="inlineStr">
         <is>
@@ -11153,11 +11153,11 @@
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
-          <t>p95 = 750ms, 0% errors</t>
+          <t>p95 = 846ms, 0% errors</t>
         </is>
       </c>
       <c r="H208" s="11" t="n">
-        <v>3.46</v>
+        <v>7.37</v>
       </c>
       <c r="I208" s="11" t="inlineStr">
         <is>
@@ -11203,11 +11203,11 @@
       </c>
       <c r="G209" s="15" t="inlineStr">
         <is>
-          <t>p95 = 582ms, 0% errors</t>
+          <t>p95 = 327ms, 0% errors</t>
         </is>
       </c>
       <c r="H209" s="14" t="n">
-        <v>11.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="I209" s="14" t="inlineStr">
         <is>
@@ -11253,11 +11253,11 @@
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
-          <t>p95 = 822ms, 0% errors</t>
+          <t>p95 = 418ms, 0% errors</t>
         </is>
       </c>
       <c r="H210" s="11" t="n">
-        <v>5.77</v>
+        <v>3.3</v>
       </c>
       <c r="I210" s="11" t="inlineStr">
         <is>
@@ -11303,11 +11303,11 @@
       </c>
       <c r="G211" s="15" t="inlineStr">
         <is>
-          <t>p95 = 446ms, 0% errors</t>
+          <t>p95 = 509ms, 0% errors</t>
         </is>
       </c>
       <c r="H211" s="14" t="n">
-        <v>1.81</v>
+        <v>7.68</v>
       </c>
       <c r="I211" s="14" t="inlineStr">
         <is>
@@ -11353,11 +11353,11 @@
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
-          <t>p95 = 540ms, 0% errors</t>
+          <t>p95 = 816ms, 0% errors</t>
         </is>
       </c>
       <c r="H212" s="11" t="n">
-        <v>4.96</v>
+        <v>3.87</v>
       </c>
       <c r="I212" s="11" t="inlineStr">
         <is>
@@ -11403,11 +11403,11 @@
       </c>
       <c r="G213" s="15" t="inlineStr">
         <is>
-          <t>p95 = 485ms, 0% errors</t>
+          <t>p95 = 185ms, 0% errors</t>
         </is>
       </c>
       <c r="H213" s="14" t="n">
-        <v>8.41</v>
+        <v>11.55</v>
       </c>
       <c r="I213" s="14" t="inlineStr">
         <is>
@@ -11453,11 +11453,11 @@
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
-          <t>p95 = 624ms, 0% errors</t>
+          <t>p95 = 546ms, 0% errors</t>
         </is>
       </c>
       <c r="H214" s="11" t="n">
-        <v>4.9</v>
+        <v>3.93</v>
       </c>
       <c r="I214" s="11" t="inlineStr">
         <is>
@@ -11503,11 +11503,11 @@
       </c>
       <c r="G215" s="15" t="inlineStr">
         <is>
-          <t>p95 = 865ms, 0% errors</t>
+          <t>p95 = 761ms, 0% errors</t>
         </is>
       </c>
       <c r="H215" s="14" t="n">
-        <v>9.199999999999999</v>
+        <v>5.24</v>
       </c>
       <c r="I215" s="14" t="inlineStr">
         <is>
@@ -11553,11 +11553,11 @@
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
-          <t>p95 = 467ms, 0% errors</t>
+          <t>p95 = 263ms, 0% errors</t>
         </is>
       </c>
       <c r="H216" s="11" t="n">
-        <v>7.16</v>
+        <v>2.57</v>
       </c>
       <c r="I216" s="11" t="inlineStr">
         <is>
@@ -11603,11 +11603,11 @@
       </c>
       <c r="G217" s="15" t="inlineStr">
         <is>
-          <t>p95 = 720ms, 0% errors</t>
+          <t>p95 = 185ms, 0% errors</t>
         </is>
       </c>
       <c r="H217" s="14" t="n">
-        <v>5.37</v>
+        <v>9.57</v>
       </c>
       <c r="I217" s="14" t="inlineStr">
         <is>
@@ -11653,11 +11653,11 @@
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
-          <t>p95 = 251ms, 0% errors</t>
+          <t>p95 = 616ms, 0% errors</t>
         </is>
       </c>
       <c r="H218" s="11" t="n">
-        <v>8.31</v>
+        <v>9.32</v>
       </c>
       <c r="I218" s="11" t="inlineStr">
         <is>
@@ -11703,11 +11703,11 @@
       </c>
       <c r="G219" s="15" t="inlineStr">
         <is>
-          <t>p95 = 572ms, 0% errors</t>
+          <t>p95 = 368ms, 0% errors</t>
         </is>
       </c>
       <c r="H219" s="14" t="n">
-        <v>11.19</v>
+        <v>8.24</v>
       </c>
       <c r="I219" s="14" t="inlineStr">
         <is>
@@ -11753,11 +11753,11 @@
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
-          <t>p95 = 638ms, 0% errors</t>
+          <t>p95 = 636ms, 0% errors</t>
         </is>
       </c>
       <c r="H220" s="11" t="n">
-        <v>9.19</v>
+        <v>2.33</v>
       </c>
       <c r="I220" s="11" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="H221" s="14" t="n">
-        <v>6.07</v>
+        <v>7.15</v>
       </c>
       <c r="I221" s="14" t="inlineStr">
         <is>
@@ -11853,11 +11853,11 @@
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
-          <t>p95 = 887ms, 0% errors</t>
+          <t>p95 = 438ms, 0% errors</t>
         </is>
       </c>
       <c r="H222" s="11" t="n">
-        <v>11.08</v>
+        <v>11.98</v>
       </c>
       <c r="I222" s="11" t="inlineStr">
         <is>
@@ -11903,11 +11903,11 @@
       </c>
       <c r="G223" s="15" t="inlineStr">
         <is>
-          <t>p95 = 569ms, 0% errors</t>
+          <t>p95 = 854ms, 0% errors</t>
         </is>
       </c>
       <c r="H223" s="14" t="n">
-        <v>7.37</v>
+        <v>9.65</v>
       </c>
       <c r="I223" s="14" t="inlineStr">
         <is>
@@ -11953,11 +11953,11 @@
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
-          <t>p95 = 429ms, 0% errors</t>
+          <t>p95 = 747ms, 0% errors</t>
         </is>
       </c>
       <c r="H224" s="11" t="n">
-        <v>11.53</v>
+        <v>4.26</v>
       </c>
       <c r="I224" s="11" t="inlineStr">
         <is>
@@ -12003,11 +12003,11 @@
       </c>
       <c r="G225" s="15" t="inlineStr">
         <is>
-          <t>p95 = 469ms, 0% errors</t>
+          <t>p95 = 694ms, 0% errors</t>
         </is>
       </c>
       <c r="H225" s="14" t="n">
-        <v>10.72</v>
+        <v>3.55</v>
       </c>
       <c r="I225" s="14" t="inlineStr">
         <is>
@@ -12053,11 +12053,11 @@
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
-          <t>p95 = 402ms, 0% errors</t>
+          <t>p95 = 445ms, 0% errors</t>
         </is>
       </c>
       <c r="H226" s="11" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="I226" s="11" t="inlineStr">
         <is>
@@ -12103,11 +12103,11 @@
       </c>
       <c r="G227" s="15" t="inlineStr">
         <is>
-          <t>p95 = 445ms, 0% errors</t>
+          <t>p95 = 588ms, 0% errors</t>
         </is>
       </c>
       <c r="H227" s="14" t="n">
-        <v>3.19</v>
+        <v>1.95</v>
       </c>
       <c r="I227" s="14" t="inlineStr">
         <is>
@@ -12153,11 +12153,11 @@
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
-          <t>p95 = 738ms, 0% errors</t>
+          <t>p95 = 670ms, 0% errors</t>
         </is>
       </c>
       <c r="H228" s="11" t="n">
-        <v>2.14</v>
+        <v>7.64</v>
       </c>
       <c r="I228" s="11" t="inlineStr">
         <is>
@@ -12203,11 +12203,11 @@
       </c>
       <c r="G229" s="15" t="inlineStr">
         <is>
-          <t>p95 = 842ms, 0% errors</t>
+          <t>p95 = 492ms, 0% errors</t>
         </is>
       </c>
       <c r="H229" s="14" t="n">
-        <v>1.64</v>
+        <v>7.51</v>
       </c>
       <c r="I229" s="14" t="inlineStr">
         <is>
@@ -12253,11 +12253,11 @@
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
-          <t>p95 = 573ms, 0% errors</t>
+          <t>p95 = 553ms, 0% errors</t>
         </is>
       </c>
       <c r="H230" s="11" t="n">
-        <v>5.79</v>
+        <v>6.43</v>
       </c>
       <c r="I230" s="11" t="inlineStr">
         <is>
@@ -12303,11 +12303,11 @@
       </c>
       <c r="G231" s="15" t="inlineStr">
         <is>
-          <t>p95 = 456ms, 0% errors</t>
+          <t>p95 = 508ms, 0% errors</t>
         </is>
       </c>
       <c r="H231" s="14" t="n">
-        <v>9.24</v>
+        <v>11.41</v>
       </c>
       <c r="I231" s="14" t="inlineStr">
         <is>
@@ -12353,11 +12353,11 @@
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
-          <t>p95 = 325ms, 0% errors</t>
+          <t>p95 = 239ms, 0% errors</t>
         </is>
       </c>
       <c r="H232" s="11" t="n">
-        <v>9.279999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="I232" s="11" t="inlineStr">
         <is>
@@ -12403,11 +12403,11 @@
       </c>
       <c r="G233" s="15" t="inlineStr">
         <is>
-          <t>p95 = 546ms, 0% errors</t>
+          <t>p95 = 844ms, 0% errors</t>
         </is>
       </c>
       <c r="H233" s="14" t="n">
-        <v>10.28</v>
+        <v>8.16</v>
       </c>
       <c r="I233" s="14" t="inlineStr">
         <is>
@@ -12453,11 +12453,11 @@
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
-          <t>p95 = 737ms, 0% errors</t>
+          <t>p95 = 568ms, 0% errors</t>
         </is>
       </c>
       <c r="H234" s="11" t="n">
-        <v>2.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I234" s="11" t="inlineStr">
         <is>
@@ -12503,11 +12503,11 @@
       </c>
       <c r="G235" s="15" t="inlineStr">
         <is>
-          <t>p95 = 624ms, 0% errors</t>
+          <t>p95 = 658ms, 0% errors</t>
         </is>
       </c>
       <c r="H235" s="14" t="n">
-        <v>8.970000000000001</v>
+        <v>6.19</v>
       </c>
       <c r="I235" s="14" t="inlineStr">
         <is>
@@ -12553,11 +12553,11 @@
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
-          <t>p95 = 743ms, 0% errors</t>
+          <t>p95 = 744ms, 0% errors</t>
         </is>
       </c>
       <c r="H236" s="11" t="n">
-        <v>9.630000000000001</v>
+        <v>6.59</v>
       </c>
       <c r="I236" s="11" t="inlineStr">
         <is>
@@ -12603,11 +12603,11 @@
       </c>
       <c r="G237" s="15" t="inlineStr">
         <is>
-          <t>p95 = 234ms, 0% errors</t>
+          <t>p95 = 477ms, 0% errors</t>
         </is>
       </c>
       <c r="H237" s="14" t="n">
-        <v>6.32</v>
+        <v>4.82</v>
       </c>
       <c r="I237" s="14" t="inlineStr">
         <is>
@@ -12653,11 +12653,11 @@
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
-          <t>p95 = 450ms, 0% errors</t>
+          <t>p95 = 252ms, 0% errors</t>
         </is>
       </c>
       <c r="H238" s="11" t="n">
-        <v>5.03</v>
+        <v>10.22</v>
       </c>
       <c r="I238" s="11" t="inlineStr">
         <is>
@@ -12703,11 +12703,11 @@
       </c>
       <c r="G239" s="15" t="inlineStr">
         <is>
-          <t>p95 = 258ms, 0% errors</t>
+          <t>p95 = 259ms, 0% errors</t>
         </is>
       </c>
       <c r="H239" s="14" t="n">
-        <v>4.41</v>
+        <v>8.06</v>
       </c>
       <c r="I239" s="14" t="inlineStr">
         <is>
@@ -12753,11 +12753,11 @@
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
-          <t>p95 = 612ms, 0% errors</t>
+          <t>p95 = 521ms, 0% errors</t>
         </is>
       </c>
       <c r="H240" s="11" t="n">
-        <v>6.99</v>
+        <v>4.96</v>
       </c>
       <c r="I240" s="11" t="inlineStr">
         <is>
@@ -12803,11 +12803,11 @@
       </c>
       <c r="G241" s="15" t="inlineStr">
         <is>
-          <t>p95 = 618ms, 0% errors</t>
+          <t>p95 = 540ms, 0% errors</t>
         </is>
       </c>
       <c r="H241" s="14" t="n">
-        <v>2.49</v>
+        <v>11.25</v>
       </c>
       <c r="I241" s="14" t="inlineStr">
         <is>
@@ -12853,11 +12853,11 @@
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
-          <t>p95 = 608ms, 0% errors</t>
+          <t>p95 = 238ms, 0% errors</t>
         </is>
       </c>
       <c r="H242" s="11" t="n">
-        <v>9.56</v>
+        <v>8.08</v>
       </c>
       <c r="I242" s="11" t="inlineStr">
         <is>
@@ -12903,11 +12903,11 @@
       </c>
       <c r="G243" s="15" t="inlineStr">
         <is>
-          <t>p95 = 828ms, 0% errors</t>
+          <t>p95 = 842ms, 0% errors</t>
         </is>
       </c>
       <c r="H243" s="14" t="n">
-        <v>4.79</v>
+        <v>6.38</v>
       </c>
       <c r="I243" s="14" t="inlineStr">
         <is>
@@ -12953,11 +12953,11 @@
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
-          <t>p95 = 890ms, 0% errors</t>
+          <t>p95 = 277ms, 0% errors</t>
         </is>
       </c>
       <c r="H244" s="11" t="n">
-        <v>7.14</v>
+        <v>5.27</v>
       </c>
       <c r="I244" s="11" t="inlineStr">
         <is>
@@ -13003,11 +13003,11 @@
       </c>
       <c r="G245" s="15" t="inlineStr">
         <is>
-          <t>p95 = 420ms, 0% errors</t>
+          <t>p95 = 789ms, 0% errors</t>
         </is>
       </c>
       <c r="H245" s="14" t="n">
-        <v>10.96</v>
+        <v>2.24</v>
       </c>
       <c r="I245" s="14" t="inlineStr">
         <is>
@@ -13053,11 +13053,11 @@
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
-          <t>p95 = 301ms, 0% errors</t>
+          <t>p95 = 217ms, 0% errors</t>
         </is>
       </c>
       <c r="H246" s="11" t="n">
-        <v>6.52</v>
+        <v>11.98</v>
       </c>
       <c r="I246" s="11" t="inlineStr">
         <is>
@@ -13103,11 +13103,11 @@
       </c>
       <c r="G247" s="15" t="inlineStr">
         <is>
-          <t>p95 = 560ms, 0% errors</t>
+          <t>p95 = 876ms, 0% errors</t>
         </is>
       </c>
       <c r="H247" s="14" t="n">
-        <v>9.960000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="I247" s="14" t="inlineStr">
         <is>
@@ -13153,11 +13153,11 @@
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
-          <t>p95 = 559ms, 0% errors</t>
+          <t>p95 = 551ms, 0% errors</t>
         </is>
       </c>
       <c r="H248" s="11" t="n">
-        <v>11.1</v>
+        <v>9.56</v>
       </c>
       <c r="I248" s="11" t="inlineStr">
         <is>
@@ -13203,11 +13203,11 @@
       </c>
       <c r="G249" s="15" t="inlineStr">
         <is>
-          <t>p95 = 348ms, 0% errors</t>
+          <t>p95 = 886ms, 0% errors</t>
         </is>
       </c>
       <c r="H249" s="14" t="n">
-        <v>1.67</v>
+        <v>10.35</v>
       </c>
       <c r="I249" s="14" t="inlineStr">
         <is>
@@ -13253,11 +13253,11 @@
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
-          <t>p95 = 817ms, 0% errors</t>
+          <t>p95 = 446ms, 0% errors</t>
         </is>
       </c>
       <c r="H250" s="11" t="n">
-        <v>11.82</v>
+        <v>7.24</v>
       </c>
       <c r="I250" s="11" t="inlineStr">
         <is>
@@ -13303,11 +13303,11 @@
       </c>
       <c r="G251" s="15" t="inlineStr">
         <is>
-          <t>p95 = 853ms, 0% errors</t>
+          <t>p95 = 556ms, 0% errors</t>
         </is>
       </c>
       <c r="H251" s="14" t="n">
-        <v>2.55</v>
+        <v>4.51</v>
       </c>
       <c r="I251" s="14" t="inlineStr">
         <is>
@@ -13353,11 +13353,11 @@
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
-          <t>p95 = 502ms, 0% errors</t>
+          <t>p95 = 715ms, 0% errors</t>
         </is>
       </c>
       <c r="H252" s="11" t="n">
-        <v>8.09</v>
+        <v>11.1</v>
       </c>
       <c r="I252" s="11" t="inlineStr">
         <is>
@@ -13403,11 +13403,11 @@
       </c>
       <c r="G253" s="15" t="inlineStr">
         <is>
-          <t>p95 = 352ms, 0% errors</t>
+          <t>p95 = 357ms, 0% errors</t>
         </is>
       </c>
       <c r="H253" s="14" t="n">
-        <v>6.87</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I253" s="14" t="inlineStr">
         <is>
@@ -13453,11 +13453,11 @@
       </c>
       <c r="G254" s="12" t="inlineStr">
         <is>
-          <t>p95 = 853ms, 0% errors</t>
+          <t>p95 = 537ms, 0% errors</t>
         </is>
       </c>
       <c r="H254" s="11" t="n">
-        <v>4.01</v>
+        <v>5.11</v>
       </c>
       <c r="I254" s="11" t="inlineStr">
         <is>
@@ -13503,11 +13503,11 @@
       </c>
       <c r="G255" s="15" t="inlineStr">
         <is>
-          <t>p95 = 886ms, 0% errors</t>
+          <t>p95 = 722ms, 0% errors</t>
         </is>
       </c>
       <c r="H255" s="14" t="n">
-        <v>10.96</v>
+        <v>10.57</v>
       </c>
       <c r="I255" s="14" t="inlineStr">
         <is>
@@ -13553,11 +13553,11 @@
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
-          <t>p95 = 854ms, 0% errors</t>
+          <t>p95 = 843ms, 0% errors</t>
         </is>
       </c>
       <c r="H256" s="11" t="n">
-        <v>9.800000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="I256" s="11" t="inlineStr">
         <is>
@@ -13603,11 +13603,11 @@
       </c>
       <c r="G257" s="15" t="inlineStr">
         <is>
-          <t>p95 = 318ms, 0% errors</t>
+          <t>p95 = 831ms, 0% errors</t>
         </is>
       </c>
       <c r="H257" s="14" t="n">
-        <v>7.15</v>
+        <v>2.29</v>
       </c>
       <c r="I257" s="14" t="inlineStr">
         <is>
@@ -13653,11 +13653,11 @@
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
-          <t>p95 = 471ms, 0% errors</t>
+          <t>p95 = 727ms, 0% errors</t>
         </is>
       </c>
       <c r="H258" s="11" t="n">
-        <v>3.01</v>
+        <v>11.78</v>
       </c>
       <c r="I258" s="11" t="inlineStr">
         <is>
@@ -13703,11 +13703,11 @@
       </c>
       <c r="G259" s="15" t="inlineStr">
         <is>
-          <t>p95 = 560ms, 0% errors</t>
+          <t>p95 = 402ms, 0% errors</t>
         </is>
       </c>
       <c r="H259" s="14" t="n">
-        <v>2.2</v>
+        <v>11.14</v>
       </c>
       <c r="I259" s="14" t="inlineStr">
         <is>
@@ -13753,11 +13753,11 @@
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
-          <t>p95 = 381ms, 0% errors</t>
+          <t>p95 = 343ms, 0% errors</t>
         </is>
       </c>
       <c r="H260" s="11" t="n">
-        <v>5.85</v>
+        <v>9.66</v>
       </c>
       <c r="I260" s="11" t="inlineStr">
         <is>
@@ -13803,11 +13803,11 @@
       </c>
       <c r="G261" s="15" t="inlineStr">
         <is>
-          <t>p95 = 374ms, 0% errors</t>
+          <t>p95 = 242ms, 0% errors</t>
         </is>
       </c>
       <c r="H261" s="14" t="n">
-        <v>3.92</v>
+        <v>6.27</v>
       </c>
       <c r="I261" s="14" t="inlineStr">
         <is>
@@ -13853,11 +13853,11 @@
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
-          <t>p95 = 450ms, 0% errors</t>
+          <t>p95 = 447ms, 0% errors</t>
         </is>
       </c>
       <c r="H262" s="11" t="n">
-        <v>10.44</v>
+        <v>9.99</v>
       </c>
       <c r="I262" s="11" t="inlineStr">
         <is>
@@ -13903,11 +13903,11 @@
       </c>
       <c r="G263" s="15" t="inlineStr">
         <is>
-          <t>p95 = 752ms, 0% errors</t>
+          <t>p95 = 354ms, 0% errors</t>
         </is>
       </c>
       <c r="H263" s="14" t="n">
-        <v>4.63</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I263" s="14" t="inlineStr">
         <is>
@@ -13953,11 +13953,11 @@
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
-          <t>p95 = 190ms, 0% errors</t>
+          <t>p95 = 569ms, 0% errors</t>
         </is>
       </c>
       <c r="H264" s="11" t="n">
-        <v>5.05</v>
+        <v>9.09</v>
       </c>
       <c r="I264" s="11" t="inlineStr">
         <is>
@@ -14003,11 +14003,11 @@
       </c>
       <c r="G265" s="15" t="inlineStr">
         <is>
-          <t>p95 = 211ms, 0% errors</t>
+          <t>p95 = 188ms, 0% errors</t>
         </is>
       </c>
       <c r="H265" s="14" t="n">
-        <v>6.63</v>
+        <v>4.46</v>
       </c>
       <c r="I265" s="14" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         </is>
       </c>
       <c r="H266" s="11" t="n">
-        <v>11.69</v>
+        <v>6.26</v>
       </c>
       <c r="I266" s="11" t="inlineStr">
         <is>
@@ -14103,11 +14103,11 @@
       </c>
       <c r="G267" s="15" t="inlineStr">
         <is>
-          <t>p95 = 346ms, 0% errors</t>
+          <t>p95 = 519ms, 0% errors</t>
         </is>
       </c>
       <c r="H267" s="14" t="n">
-        <v>3.79</v>
+        <v>3.24</v>
       </c>
       <c r="I267" s="14" t="inlineStr">
         <is>
@@ -14153,11 +14153,11 @@
       </c>
       <c r="G268" s="12" t="inlineStr">
         <is>
-          <t>p95 = 501ms, 0% errors</t>
+          <t>p95 = 186ms, 0% errors</t>
         </is>
       </c>
       <c r="H268" s="11" t="n">
-        <v>6.81</v>
+        <v>4.96</v>
       </c>
       <c r="I268" s="11" t="inlineStr">
         <is>
@@ -14203,11 +14203,11 @@
       </c>
       <c r="G269" s="15" t="inlineStr">
         <is>
-          <t>p95 = 256ms, 0% errors</t>
+          <t>p95 = 231ms, 0% errors</t>
         </is>
       </c>
       <c r="H269" s="14" t="n">
-        <v>3.67</v>
+        <v>10.55</v>
       </c>
       <c r="I269" s="14" t="inlineStr">
         <is>
@@ -14253,11 +14253,11 @@
       </c>
       <c r="G270" s="12" t="inlineStr">
         <is>
-          <t>p95 = 781ms, 0% errors</t>
+          <t>p95 = 316ms, 0% errors</t>
         </is>
       </c>
       <c r="H270" s="11" t="n">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="I270" s="11" t="inlineStr">
         <is>
@@ -14303,11 +14303,11 @@
       </c>
       <c r="G271" s="15" t="inlineStr">
         <is>
-          <t>p95 = 766ms, 0% errors</t>
+          <t>p95 = 205ms, 0% errors</t>
         </is>
       </c>
       <c r="H271" s="14" t="n">
-        <v>9.380000000000001</v>
+        <v>10.15</v>
       </c>
       <c r="I271" s="14" t="inlineStr">
         <is>
@@ -14353,11 +14353,11 @@
       </c>
       <c r="G272" s="12" t="inlineStr">
         <is>
-          <t>p95 = 261ms, 0% errors</t>
+          <t>p95 = 237ms, 0% errors</t>
         </is>
       </c>
       <c r="H272" s="11" t="n">
-        <v>10.47</v>
+        <v>3.63</v>
       </c>
       <c r="I272" s="11" t="inlineStr">
         <is>
@@ -14403,11 +14403,11 @@
       </c>
       <c r="G273" s="15" t="inlineStr">
         <is>
-          <t>p95 = 457ms, 0% errors</t>
+          <t>p95 = 630ms, 0% errors</t>
         </is>
       </c>
       <c r="H273" s="14" t="n">
-        <v>8.58</v>
+        <v>10.94</v>
       </c>
       <c r="I273" s="14" t="inlineStr">
         <is>
@@ -14453,11 +14453,11 @@
       </c>
       <c r="G274" s="12" t="inlineStr">
         <is>
-          <t>p95 = 853ms, 0% errors</t>
+          <t>p95 = 310ms, 0% errors</t>
         </is>
       </c>
       <c r="H274" s="11" t="n">
-        <v>11.02</v>
+        <v>8.9</v>
       </c>
       <c r="I274" s="11" t="inlineStr">
         <is>
@@ -14503,11 +14503,11 @@
       </c>
       <c r="G275" s="15" t="inlineStr">
         <is>
-          <t>p95 = 383ms, 0% errors</t>
+          <t>p95 = 272ms, 0% errors</t>
         </is>
       </c>
       <c r="H275" s="14" t="n">
-        <v>3.6</v>
+        <v>4.69</v>
       </c>
       <c r="I275" s="14" t="inlineStr">
         <is>
@@ -14553,11 +14553,11 @@
       </c>
       <c r="G276" s="12" t="inlineStr">
         <is>
-          <t>p95 = 857ms, 0% errors</t>
+          <t>p95 = 480ms, 0% errors</t>
         </is>
       </c>
       <c r="H276" s="11" t="n">
-        <v>6.28</v>
+        <v>4.13</v>
       </c>
       <c r="I276" s="11" t="inlineStr">
         <is>
@@ -14603,11 +14603,11 @@
       </c>
       <c r="G277" s="15" t="inlineStr">
         <is>
-          <t>p95 = 337ms, 0% errors</t>
+          <t>p95 = 766ms, 0% errors</t>
         </is>
       </c>
       <c r="H277" s="14" t="n">
-        <v>11.55</v>
+        <v>5.47</v>
       </c>
       <c r="I277" s="14" t="inlineStr">
         <is>
@@ -14653,11 +14653,11 @@
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
-          <t>p95 = 750ms, 0% errors</t>
+          <t>p95 = 365ms, 0% errors</t>
         </is>
       </c>
       <c r="H278" s="11" t="n">
-        <v>10.48</v>
+        <v>11.05</v>
       </c>
       <c r="I278" s="11" t="inlineStr">
         <is>
@@ -14703,11 +14703,11 @@
       </c>
       <c r="G279" s="15" t="inlineStr">
         <is>
-          <t>p95 = 498ms, 0% errors</t>
+          <t>p95 = 350ms, 0% errors</t>
         </is>
       </c>
       <c r="H279" s="14" t="n">
-        <v>8.300000000000001</v>
+        <v>2.66</v>
       </c>
       <c r="I279" s="14" t="inlineStr">
         <is>
@@ -14753,11 +14753,11 @@
       </c>
       <c r="G280" s="12" t="inlineStr">
         <is>
-          <t>p95 = 236ms, 0% errors</t>
+          <t>p95 = 403ms, 0% errors</t>
         </is>
       </c>
       <c r="H280" s="11" t="n">
-        <v>3.79</v>
+        <v>10.14</v>
       </c>
       <c r="I280" s="11" t="inlineStr">
         <is>
@@ -14803,11 +14803,11 @@
       </c>
       <c r="G281" s="15" t="inlineStr">
         <is>
-          <t>p95 = 383ms, 0% errors</t>
+          <t>p95 = 180ms, 0% errors</t>
         </is>
       </c>
       <c r="H281" s="14" t="n">
-        <v>4.7</v>
+        <v>11.41</v>
       </c>
       <c r="I281" s="14" t="inlineStr">
         <is>
@@ -14853,11 +14853,11 @@
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
-          <t>p95 = 547ms, 0% errors</t>
+          <t>p95 = 464ms, 0% errors</t>
         </is>
       </c>
       <c r="H282" s="11" t="n">
-        <v>6.4</v>
+        <v>4.18</v>
       </c>
       <c r="I282" s="11" t="inlineStr">
         <is>
@@ -14903,11 +14903,11 @@
       </c>
       <c r="G283" s="15" t="inlineStr">
         <is>
-          <t>p95 = 821ms, 0% errors</t>
+          <t>p95 = 467ms, 0% errors</t>
         </is>
       </c>
       <c r="H283" s="14" t="n">
-        <v>2.79</v>
+        <v>7.08</v>
       </c>
       <c r="I283" s="14" t="inlineStr">
         <is>
@@ -14953,11 +14953,11 @@
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
-          <t>p95 = 319ms, 0% errors</t>
+          <t>p95 = 875ms, 0% errors</t>
         </is>
       </c>
       <c r="H284" s="11" t="n">
-        <v>5.71</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="I284" s="11" t="inlineStr">
         <is>
@@ -15003,11 +15003,11 @@
       </c>
       <c r="G285" s="15" t="inlineStr">
         <is>
-          <t>p95 = 803ms, 0% errors</t>
+          <t>p95 = 494ms, 0% errors</t>
         </is>
       </c>
       <c r="H285" s="14" t="n">
-        <v>9.369999999999999</v>
+        <v>4.07</v>
       </c>
       <c r="I285" s="14" t="inlineStr">
         <is>
@@ -15053,11 +15053,11 @@
       </c>
       <c r="G286" s="12" t="inlineStr">
         <is>
-          <t>p95 = 667ms, 0% errors</t>
+          <t>p95 = 740ms, 0% errors</t>
         </is>
       </c>
       <c r="H286" s="11" t="n">
-        <v>10.52</v>
+        <v>10.57</v>
       </c>
       <c r="I286" s="11" t="inlineStr">
         <is>
@@ -15103,11 +15103,11 @@
       </c>
       <c r="G287" s="15" t="inlineStr">
         <is>
-          <t>p95 = 790ms, 0% errors</t>
+          <t>p95 = 417ms, 0% errors</t>
         </is>
       </c>
       <c r="H287" s="14" t="n">
-        <v>2.42</v>
+        <v>3.29</v>
       </c>
       <c r="I287" s="14" t="inlineStr">
         <is>
@@ -15153,11 +15153,11 @@
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
-          <t>p95 = 842ms, 0% errors</t>
+          <t>p95 = 515ms, 0% errors</t>
         </is>
       </c>
       <c r="H288" s="11" t="n">
-        <v>4.01</v>
+        <v>3.76</v>
       </c>
       <c r="I288" s="11" t="inlineStr">
         <is>
@@ -15203,11 +15203,11 @@
       </c>
       <c r="G289" s="15" t="inlineStr">
         <is>
-          <t>p95 = 454ms, 0% errors</t>
+          <t>p95 = 843ms, 0% errors</t>
         </is>
       </c>
       <c r="H289" s="14" t="n">
-        <v>1.94</v>
+        <v>2.94</v>
       </c>
       <c r="I289" s="14" t="inlineStr">
         <is>
@@ -15253,11 +15253,11 @@
       </c>
       <c r="G290" s="12" t="inlineStr">
         <is>
-          <t>p95 = 456ms, 0% errors</t>
+          <t>p95 = 784ms, 0% errors</t>
         </is>
       </c>
       <c r="H290" s="11" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="I290" s="11" t="inlineStr">
         <is>
@@ -15303,11 +15303,11 @@
       </c>
       <c r="G291" s="15" t="inlineStr">
         <is>
-          <t>p95 = 554ms, 0% errors</t>
+          <t>p95 = 478ms, 0% errors</t>
         </is>
       </c>
       <c r="H291" s="14" t="n">
-        <v>11.56</v>
+        <v>8.08</v>
       </c>
       <c r="I291" s="14" t="inlineStr">
         <is>
@@ -15353,11 +15353,11 @@
       </c>
       <c r="G292" s="12" t="inlineStr">
         <is>
-          <t>p95 = 740ms, 0% errors</t>
+          <t>p95 = 526ms, 0% errors</t>
         </is>
       </c>
       <c r="H292" s="11" t="n">
-        <v>10.7</v>
+        <v>9.82</v>
       </c>
       <c r="I292" s="11" t="inlineStr">
         <is>
@@ -15403,11 +15403,11 @@
       </c>
       <c r="G293" s="15" t="inlineStr">
         <is>
-          <t>p95 = 498ms, 0% errors</t>
+          <t>p95 = 546ms, 0% errors</t>
         </is>
       </c>
       <c r="H293" s="14" t="n">
-        <v>1.57</v>
+        <v>3.93</v>
       </c>
       <c r="I293" s="14" t="inlineStr">
         <is>
@@ -15453,11 +15453,11 @@
       </c>
       <c r="G294" s="12" t="inlineStr">
         <is>
-          <t>p95 = 610ms, 0% errors</t>
+          <t>p95 = 775ms, 0% errors</t>
         </is>
       </c>
       <c r="H294" s="11" t="n">
-        <v>5.12</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="I294" s="11" t="inlineStr">
         <is>
@@ -15503,11 +15503,11 @@
       </c>
       <c r="G295" s="15" t="inlineStr">
         <is>
-          <t>p95 = 380ms, 0% errors</t>
+          <t>p95 = 592ms, 0% errors</t>
         </is>
       </c>
       <c r="H295" s="14" t="n">
-        <v>5.1</v>
+        <v>11.09</v>
       </c>
       <c r="I295" s="14" t="inlineStr">
         <is>
@@ -15553,11 +15553,11 @@
       </c>
       <c r="G296" s="12" t="inlineStr">
         <is>
-          <t>p95 = 850ms, 0% errors</t>
+          <t>p95 = 676ms, 0% errors</t>
         </is>
       </c>
       <c r="H296" s="11" t="n">
-        <v>6.63</v>
+        <v>11.41</v>
       </c>
       <c r="I296" s="11" t="inlineStr">
         <is>
@@ -15603,11 +15603,11 @@
       </c>
       <c r="G297" s="15" t="inlineStr">
         <is>
-          <t>p95 = 540ms, 0% errors</t>
+          <t>p95 = 491ms, 0% errors</t>
         </is>
       </c>
       <c r="H297" s="14" t="n">
-        <v>5.45</v>
+        <v>6.7</v>
       </c>
       <c r="I297" s="14" t="inlineStr">
         <is>
@@ -15653,11 +15653,11 @@
       </c>
       <c r="G298" s="12" t="inlineStr">
         <is>
-          <t>p95 = 510ms, 0% errors</t>
+          <t>p95 = 486ms, 0% errors</t>
         </is>
       </c>
       <c r="H298" s="11" t="n">
-        <v>10.66</v>
+        <v>6.1</v>
       </c>
       <c r="I298" s="11" t="inlineStr">
         <is>
@@ -15703,11 +15703,11 @@
       </c>
       <c r="G299" s="15" t="inlineStr">
         <is>
-          <t>p95 = 628ms, 0% errors</t>
+          <t>p95 = 412ms, 0% errors</t>
         </is>
       </c>
       <c r="H299" s="14" t="n">
-        <v>5.98</v>
+        <v>3.24</v>
       </c>
       <c r="I299" s="14" t="inlineStr">
         <is>
@@ -15753,11 +15753,11 @@
       </c>
       <c r="G300" s="12" t="inlineStr">
         <is>
-          <t>p95 = 619ms, 0% errors</t>
+          <t>p95 = 392ms, 0% errors</t>
         </is>
       </c>
       <c r="H300" s="11" t="n">
-        <v>4.35</v>
+        <v>2.72</v>
       </c>
       <c r="I300" s="11" t="inlineStr">
         <is>
@@ -15803,11 +15803,11 @@
       </c>
       <c r="G301" s="15" t="inlineStr">
         <is>
-          <t>p95 = 711ms, 0% errors</t>
+          <t>p95 = 476ms, 0% errors</t>
         </is>
       </c>
       <c r="H301" s="14" t="n">
-        <v>6.01</v>
+        <v>5.8</v>
       </c>
       <c r="I301" s="14" t="inlineStr">
         <is>
@@ -15853,11 +15853,11 @@
       </c>
       <c r="G302" s="12" t="inlineStr">
         <is>
-          <t>p95 = 509ms, 0% errors</t>
+          <t>p95 = 263ms, 0% errors</t>
         </is>
       </c>
       <c r="H302" s="11" t="n">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
       <c r="I302" s="11" t="inlineStr">
         <is>
@@ -15903,11 +15903,11 @@
       </c>
       <c r="G303" s="15" t="inlineStr">
         <is>
-          <t>p95 = 366ms, 0% errors</t>
+          <t>p95 = 584ms, 0% errors</t>
         </is>
       </c>
       <c r="H303" s="14" t="n">
-        <v>5.22</v>
+        <v>2.58</v>
       </c>
       <c r="I303" s="14" t="inlineStr">
         <is>
@@ -15953,11 +15953,11 @@
       </c>
       <c r="G304" s="12" t="inlineStr">
         <is>
-          <t>p95 = 525ms, 0% errors</t>
+          <t>p95 = 602ms, 0% errors</t>
         </is>
       </c>
       <c r="H304" s="11" t="n">
-        <v>11.03</v>
+        <v>10.36</v>
       </c>
       <c r="I304" s="11" t="inlineStr">
         <is>
@@ -16003,11 +16003,11 @@
       </c>
       <c r="G305" s="15" t="inlineStr">
         <is>
-          <t>p95 = 549ms, 0% errors</t>
+          <t>p95 = 748ms, 0% errors</t>
         </is>
       </c>
       <c r="H305" s="14" t="n">
-        <v>7</v>
+        <v>11.26</v>
       </c>
       <c r="I305" s="14" t="inlineStr">
         <is>
@@ -16053,11 +16053,11 @@
       </c>
       <c r="G306" s="12" t="inlineStr">
         <is>
-          <t>p95 = 454ms, 0% errors</t>
+          <t>p95 = 453ms, 0% errors</t>
         </is>
       </c>
       <c r="H306" s="11" t="n">
-        <v>2.68</v>
+        <v>7.94</v>
       </c>
       <c r="I306" s="11" t="inlineStr">
         <is>
@@ -16103,11 +16103,11 @@
       </c>
       <c r="G307" s="15" t="inlineStr">
         <is>
-          <t>p95 = 770ms, 0% errors</t>
+          <t>p95 = 698ms, 0% errors</t>
         </is>
       </c>
       <c r="H307" s="14" t="n">
-        <v>8.130000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="I307" s="14" t="inlineStr">
         <is>
@@ -16153,11 +16153,11 @@
       </c>
       <c r="G308" s="12" t="inlineStr">
         <is>
-          <t>p95 = 605ms, 0% errors</t>
+          <t>p95 = 471ms, 0% errors</t>
         </is>
       </c>
       <c r="H308" s="11" t="n">
-        <v>7.95</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="I308" s="11" t="inlineStr">
         <is>
@@ -16203,11 +16203,11 @@
       </c>
       <c r="G309" s="15" t="inlineStr">
         <is>
-          <t>p95 = 309ms, 0% errors</t>
+          <t>p95 = 329ms, 0% errors</t>
         </is>
       </c>
       <c r="H309" s="14" t="n">
-        <v>5.02</v>
+        <v>9.44</v>
       </c>
       <c r="I309" s="14" t="inlineStr">
         <is>
@@ -16253,11 +16253,11 @@
       </c>
       <c r="G310" s="12" t="inlineStr">
         <is>
-          <t>p95 = 343ms, 0% errors</t>
+          <t>p95 = 313ms, 0% errors</t>
         </is>
       </c>
       <c r="H310" s="11" t="n">
-        <v>10</v>
+        <v>4.38</v>
       </c>
       <c r="I310" s="11" t="inlineStr">
         <is>
@@ -16303,11 +16303,11 @@
       </c>
       <c r="G311" s="15" t="inlineStr">
         <is>
-          <t>p95 = 875ms, 0% errors</t>
+          <t>p95 = 718ms, 0% errors</t>
         </is>
       </c>
       <c r="H311" s="14" t="n">
-        <v>9.48</v>
+        <v>8.23</v>
       </c>
       <c r="I311" s="14" t="inlineStr">
         <is>
@@ -16431,11 +16431,11 @@
       </c>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>p95 = 514ms, 0% errors</t>
+          <t>p95 = 590ms, 0% errors</t>
         </is>
       </c>
       <c r="H2" s="17" t="n">
-        <v>5.73</v>
+        <v>4.5</v>
       </c>
       <c r="I2" s="17" t="inlineStr">
         <is>
@@ -16481,11 +16481,11 @@
       </c>
       <c r="G3" s="18" t="inlineStr">
         <is>
-          <t>p95 = 842ms, 0% errors</t>
+          <t>p95 = 562ms, 0% errors</t>
         </is>
       </c>
       <c r="H3" s="18" t="n">
-        <v>4.19</v>
+        <v>7.04</v>
       </c>
       <c r="I3" s="18" t="inlineStr">
         <is>
@@ -16531,11 +16531,11 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>p95 = 222ms, 0% errors</t>
+          <t>p95 = 343ms, 0% errors</t>
         </is>
       </c>
       <c r="H4" s="17" t="n">
-        <v>3.01</v>
+        <v>8.02</v>
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
@@ -16581,11 +16581,11 @@
       </c>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>p95 = 837ms, 0% errors</t>
+          <t>p95 = 331ms, 0% errors</t>
         </is>
       </c>
       <c r="H5" s="18" t="n">
-        <v>9.539999999999999</v>
+        <v>5.78</v>
       </c>
       <c r="I5" s="18" t="inlineStr">
         <is>
@@ -16631,11 +16631,11 @@
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>p95 = 872ms, 0% errors</t>
+          <t>p95 = 694ms, 0% errors</t>
         </is>
       </c>
       <c r="H6" s="17" t="n">
-        <v>3.87</v>
+        <v>6.1</v>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
@@ -16681,11 +16681,11 @@
       </c>
       <c r="G7" s="18" t="inlineStr">
         <is>
-          <t>p95 = 632ms, 0% errors</t>
+          <t>p95 = 266ms, 0% errors</t>
         </is>
       </c>
       <c r="H7" s="18" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="I7" s="18" t="inlineStr">
         <is>
@@ -16731,11 +16731,11 @@
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>p95 = 462ms, 0% errors</t>
+          <t>p95 = 329ms, 0% errors</t>
         </is>
       </c>
       <c r="H8" s="17" t="n">
-        <v>5.76</v>
+        <v>5.44</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -16781,11 +16781,11 @@
       </c>
       <c r="G9" s="18" t="inlineStr">
         <is>
-          <t>p95 = 403ms, 0% errors</t>
+          <t>p95 = 561ms, 0% errors</t>
         </is>
       </c>
       <c r="H9" s="18" t="n">
-        <v>7.88</v>
+        <v>9.24</v>
       </c>
       <c r="I9" s="18" t="inlineStr">
         <is>
@@ -16831,11 +16831,11 @@
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>p95 = 209ms, 0% errors</t>
+          <t>p95 = 428ms, 0% errors</t>
         </is>
       </c>
       <c r="H10" s="17" t="n">
-        <v>11.42</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
@@ -16881,11 +16881,11 @@
       </c>
       <c r="G11" s="18" t="inlineStr">
         <is>
-          <t>p95 = 572ms, 0% errors</t>
+          <t>p95 = 756ms, 0% errors</t>
         </is>
       </c>
       <c r="H11" s="18" t="n">
-        <v>10.37</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
@@ -16931,11 +16931,11 @@
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>p95 = 340ms, 0% errors</t>
+          <t>p95 = 545ms, 0% errors</t>
         </is>
       </c>
       <c r="H12" s="17" t="n">
-        <v>3.93</v>
+        <v>5.64</v>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
@@ -16981,11 +16981,11 @@
       </c>
       <c r="G13" s="18" t="inlineStr">
         <is>
-          <t>p95 = 338ms, 0% errors</t>
+          <t>p95 = 817ms, 0% errors</t>
         </is>
       </c>
       <c r="H13" s="18" t="n">
-        <v>3.96</v>
+        <v>10.47</v>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
@@ -17031,11 +17031,11 @@
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>p95 = 523ms, 0% errors</t>
+          <t>p95 = 511ms, 0% errors</t>
         </is>
       </c>
       <c r="H14" s="17" t="n">
-        <v>1.81</v>
+        <v>5.69</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -17081,11 +17081,11 @@
       </c>
       <c r="G15" s="18" t="inlineStr">
         <is>
-          <t>p95 = 182ms, 0% errors</t>
+          <t>p95 = 271ms, 0% errors</t>
         </is>
       </c>
       <c r="H15" s="18" t="n">
-        <v>7.18</v>
+        <v>1.61</v>
       </c>
       <c r="I15" s="18" t="inlineStr">
         <is>
@@ -17131,11 +17131,11 @@
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>p95 = 441ms, 0% errors</t>
+          <t>p95 = 234ms, 0% errors</t>
         </is>
       </c>
       <c r="H16" s="17" t="n">
-        <v>11.54</v>
+        <v>6.24</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -17181,11 +17181,11 @@
       </c>
       <c r="G17" s="18" t="inlineStr">
         <is>
-          <t>p95 = 213ms, 0% errors</t>
+          <t>p95 = 722ms, 0% errors</t>
         </is>
       </c>
       <c r="H17" s="18" t="n">
-        <v>10.74</v>
+        <v>1.8</v>
       </c>
       <c r="I17" s="18" t="inlineStr">
         <is>
@@ -17231,11 +17231,11 @@
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>p95 = 754ms, 0% errors</t>
+          <t>p95 = 599ms, 0% errors</t>
         </is>
       </c>
       <c r="H18" s="17" t="n">
-        <v>5.4</v>
+        <v>7.72</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -17281,11 +17281,11 @@
       </c>
       <c r="G19" s="18" t="inlineStr">
         <is>
-          <t>p95 = 235ms, 0% errors</t>
+          <t>p95 = 340ms, 0% errors</t>
         </is>
       </c>
       <c r="H19" s="18" t="n">
-        <v>10.23</v>
+        <v>4.49</v>
       </c>
       <c r="I19" s="18" t="inlineStr">
         <is>
@@ -17331,11 +17331,11 @@
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>p95 = 527ms, 0% errors</t>
+          <t>p95 = 721ms, 0% errors</t>
         </is>
       </c>
       <c r="H20" s="17" t="n">
-        <v>6.5</v>
+        <v>5.36</v>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
@@ -17381,11 +17381,11 @@
       </c>
       <c r="G21" s="18" t="inlineStr">
         <is>
-          <t>p95 = 469ms, 0% errors</t>
+          <t>p95 = 214ms, 0% errors</t>
         </is>
       </c>
       <c r="H21" s="18" t="n">
-        <v>8.779999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="I21" s="18" t="inlineStr">
         <is>
@@ -17431,11 +17431,11 @@
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>p95 = 402ms, 0% errors</t>
+          <t>p95 = 246ms, 0% errors</t>
         </is>
       </c>
       <c r="H22" s="17" t="n">
-        <v>4.51</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
@@ -17481,11 +17481,11 @@
       </c>
       <c r="G23" s="18" t="inlineStr">
         <is>
-          <t>p95 = 514ms, 0% errors</t>
+          <t>p95 = 429ms, 0% errors</t>
         </is>
       </c>
       <c r="H23" s="18" t="n">
-        <v>6.16</v>
+        <v>1.98</v>
       </c>
       <c r="I23" s="18" t="inlineStr">
         <is>
@@ -17531,11 +17531,11 @@
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>p95 = 192ms, 0% errors</t>
+          <t>p95 = 258ms, 0% errors</t>
         </is>
       </c>
       <c r="H24" s="17" t="n">
-        <v>4.9</v>
+        <v>5.95</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
@@ -17581,11 +17581,11 @@
       </c>
       <c r="G25" s="18" t="inlineStr">
         <is>
-          <t>p95 = 194ms, 0% errors</t>
+          <t>p95 = 489ms, 0% errors</t>
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>10.93</v>
+        <v>3.15</v>
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
@@ -17631,11 +17631,11 @@
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>p95 = 340ms, 0% errors</t>
+          <t>p95 = 655ms, 0% errors</t>
         </is>
       </c>
       <c r="H26" s="17" t="n">
-        <v>1.65</v>
+        <v>8.68</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
@@ -17681,11 +17681,11 @@
       </c>
       <c r="G27" s="18" t="inlineStr">
         <is>
-          <t>p95 = 548ms, 0% errors</t>
+          <t>p95 = 865ms, 0% errors</t>
         </is>
       </c>
       <c r="H27" s="18" t="n">
-        <v>6.52</v>
+        <v>10.74</v>
       </c>
       <c r="I27" s="18" t="inlineStr">
         <is>
@@ -17731,11 +17731,11 @@
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>p95 = 421ms, 0% errors</t>
+          <t>p95 = 435ms, 0% errors</t>
         </is>
       </c>
       <c r="H28" s="17" t="n">
-        <v>8.74</v>
+        <v>9.07</v>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
@@ -17781,11 +17781,11 @@
       </c>
       <c r="G29" s="18" t="inlineStr">
         <is>
-          <t>p95 = 558ms, 0% errors</t>
+          <t>p95 = 410ms, 0% errors</t>
         </is>
       </c>
       <c r="H29" s="18" t="n">
-        <v>10.71</v>
+        <v>2.03</v>
       </c>
       <c r="I29" s="18" t="inlineStr">
         <is>
@@ -17831,11 +17831,11 @@
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>p95 = 774ms, 0% errors</t>
+          <t>p95 = 429ms, 0% errors</t>
         </is>
       </c>
       <c r="H30" s="17" t="n">
-        <v>8.369999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
@@ -17881,11 +17881,11 @@
       </c>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t>p95 = 645ms, 0% errors</t>
+          <t>p95 = 643ms, 0% errors</t>
         </is>
       </c>
       <c r="H31" s="18" t="n">
-        <v>4.18</v>
+        <v>6.92</v>
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
@@ -17931,11 +17931,11 @@
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>p95 = 534ms, 0% errors</t>
+          <t>p95 = 809ms, 0% errors</t>
         </is>
       </c>
       <c r="H32" s="17" t="n">
-        <v>2.66</v>
+        <v>10.11</v>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
@@ -17981,11 +17981,11 @@
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>p95 = 436ms, 0% errors</t>
+          <t>p95 = 763ms, 0% errors</t>
         </is>
       </c>
       <c r="H33" s="18" t="n">
-        <v>10.82</v>
+        <v>7.82</v>
       </c>
       <c r="I33" s="18" t="inlineStr">
         <is>
@@ -18031,11 +18031,11 @@
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t>p95 = 293ms, 0% errors</t>
+          <t>p95 = 549ms, 0% errors</t>
         </is>
       </c>
       <c r="H34" s="17" t="n">
-        <v>1.88</v>
+        <v>2.82</v>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
@@ -18081,11 +18081,11 @@
       </c>
       <c r="G35" s="18" t="inlineStr">
         <is>
-          <t>p95 = 784ms, 0% errors</t>
+          <t>p95 = 620ms, 0% errors</t>
         </is>
       </c>
       <c r="H35" s="18" t="n">
-        <v>6.54</v>
+        <v>8.56</v>
       </c>
       <c r="I35" s="18" t="inlineStr">
         <is>
@@ -18131,11 +18131,11 @@
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>p95 = 822ms, 0% errors</t>
+          <t>p95 = 542ms, 0% errors</t>
         </is>
       </c>
       <c r="H36" s="17" t="n">
-        <v>8.68</v>
+        <v>6.59</v>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
@@ -18181,11 +18181,11 @@
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
-          <t>p95 = 196ms, 0% errors</t>
+          <t>p95 = 466ms, 0% errors</t>
         </is>
       </c>
       <c r="H37" s="18" t="n">
-        <v>4.82</v>
+        <v>8.75</v>
       </c>
       <c r="I37" s="18" t="inlineStr">
         <is>
@@ -18231,11 +18231,11 @@
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>p95 = 656ms, 0% errors</t>
+          <t>p95 = 837ms, 0% errors</t>
         </is>
       </c>
       <c r="H38" s="17" t="n">
-        <v>11.69</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
@@ -18281,11 +18281,11 @@
       </c>
       <c r="G39" s="18" t="inlineStr">
         <is>
-          <t>p95 = 297ms, 0% errors</t>
+          <t>p95 = 346ms, 0% errors</t>
         </is>
       </c>
       <c r="H39" s="18" t="n">
-        <v>7.63</v>
+        <v>6.82</v>
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
@@ -18331,11 +18331,11 @@
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>p95 = 639ms, 0% errors</t>
+          <t>p95 = 598ms, 0% errors</t>
         </is>
       </c>
       <c r="H40" s="17" t="n">
-        <v>8.44</v>
+        <v>1.54</v>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
@@ -18381,11 +18381,11 @@
       </c>
       <c r="G41" s="18" t="inlineStr">
         <is>
-          <t>p95 = 883ms, 0% errors</t>
+          <t>p95 = 709ms, 0% errors</t>
         </is>
       </c>
       <c r="H41" s="18" t="n">
-        <v>4.09</v>
+        <v>10.97</v>
       </c>
       <c r="I41" s="18" t="inlineStr">
         <is>
@@ -18431,11 +18431,11 @@
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>p95 = 775ms, 0% errors</t>
+          <t>p95 = 185ms, 0% errors</t>
         </is>
       </c>
       <c r="H42" s="17" t="n">
-        <v>9.26</v>
+        <v>10.69</v>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
@@ -18481,11 +18481,11 @@
       </c>
       <c r="G43" s="18" t="inlineStr">
         <is>
-          <t>p95 = 571ms, 0% errors</t>
+          <t>p95 = 764ms, 0% errors</t>
         </is>
       </c>
       <c r="H43" s="18" t="n">
-        <v>4.73</v>
+        <v>3.9</v>
       </c>
       <c r="I43" s="18" t="inlineStr">
         <is>
@@ -18531,11 +18531,11 @@
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>p95 = 807ms, 0% errors</t>
+          <t>p95 = 214ms, 0% errors</t>
         </is>
       </c>
       <c r="H44" s="17" t="n">
-        <v>3.65</v>
+        <v>5.76</v>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
@@ -18581,11 +18581,11 @@
       </c>
       <c r="G45" s="18" t="inlineStr">
         <is>
-          <t>p95 = 207ms, 0% errors</t>
+          <t>p95 = 613ms, 0% errors</t>
         </is>
       </c>
       <c r="H45" s="18" t="n">
-        <v>3.96</v>
+        <v>4.43</v>
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
@@ -18631,11 +18631,11 @@
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>p95 = 858ms, 0% errors</t>
+          <t>p95 = 798ms, 0% errors</t>
         </is>
       </c>
       <c r="H46" s="17" t="n">
-        <v>4.43</v>
+        <v>6.11</v>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
@@ -18681,11 +18681,11 @@
       </c>
       <c r="G47" s="18" t="inlineStr">
         <is>
-          <t>p95 = 805ms, 0% errors</t>
+          <t>p95 = 729ms, 0% errors</t>
         </is>
       </c>
       <c r="H47" s="18" t="n">
-        <v>5.52</v>
+        <v>8.1</v>
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
@@ -18731,11 +18731,11 @@
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>p95 = 702ms, 0% errors</t>
+          <t>p95 = 458ms, 0% errors</t>
         </is>
       </c>
       <c r="H48" s="17" t="n">
-        <v>4.77</v>
+        <v>9.77</v>
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
@@ -18781,11 +18781,11 @@
       </c>
       <c r="G49" s="18" t="inlineStr">
         <is>
-          <t>p95 = 357ms, 0% errors</t>
+          <t>p95 = 294ms, 0% errors</t>
         </is>
       </c>
       <c r="H49" s="18" t="n">
-        <v>10.7</v>
+        <v>5.71</v>
       </c>
       <c r="I49" s="18" t="inlineStr">
         <is>
@@ -18831,11 +18831,11 @@
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>p95 = 321ms, 0% errors</t>
+          <t>p95 = 542ms, 0% errors</t>
         </is>
       </c>
       <c r="H50" s="17" t="n">
-        <v>10.33</v>
+        <v>2.15</v>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
@@ -18881,11 +18881,11 @@
       </c>
       <c r="G51" s="18" t="inlineStr">
         <is>
-          <t>p95 = 346ms, 0% errors</t>
+          <t>p95 = 456ms, 0% errors</t>
         </is>
       </c>
       <c r="H51" s="18" t="n">
-        <v>7.68</v>
+        <v>2.64</v>
       </c>
       <c r="I51" s="18" t="inlineStr">
         <is>
@@ -18931,11 +18931,11 @@
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>p95 = 187ms, 0% errors</t>
+          <t>p95 = 490ms, 0% errors</t>
         </is>
       </c>
       <c r="H52" s="17" t="n">
-        <v>6.84</v>
+        <v>11.68</v>
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
@@ -18981,11 +18981,11 @@
       </c>
       <c r="G53" s="18" t="inlineStr">
         <is>
-          <t>p95 = 740ms, 0% errors</t>
+          <t>p95 = 297ms, 0% errors</t>
         </is>
       </c>
       <c r="H53" s="18" t="n">
-        <v>8.16</v>
+        <v>7.34</v>
       </c>
       <c r="I53" s="18" t="inlineStr">
         <is>
@@ -19031,11 +19031,11 @@
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>p95 = 181ms, 0% errors</t>
+          <t>p95 = 356ms, 0% errors</t>
         </is>
       </c>
       <c r="H54" s="17" t="n">
-        <v>1.79</v>
+        <v>6.76</v>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
@@ -19081,11 +19081,11 @@
       </c>
       <c r="G55" s="18" t="inlineStr">
         <is>
-          <t>p95 = 604ms, 0% errors</t>
+          <t>p95 = 879ms, 0% errors</t>
         </is>
       </c>
       <c r="H55" s="18" t="n">
-        <v>2.88</v>
+        <v>11.46</v>
       </c>
       <c r="I55" s="18" t="inlineStr">
         <is>
@@ -19131,11 +19131,11 @@
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>p95 = 471ms, 0% errors</t>
+          <t>p95 = 622ms, 0% errors</t>
         </is>
       </c>
       <c r="H56" s="17" t="n">
-        <v>10.15</v>
+        <v>7.63</v>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
@@ -19181,11 +19181,11 @@
       </c>
       <c r="G57" s="18" t="inlineStr">
         <is>
-          <t>p95 = 833ms, 0% errors</t>
+          <t>p95 = 265ms, 0% errors</t>
         </is>
       </c>
       <c r="H57" s="18" t="n">
-        <v>11.87</v>
+        <v>4.99</v>
       </c>
       <c r="I57" s="18" t="inlineStr">
         <is>
@@ -19231,11 +19231,11 @@
       </c>
       <c r="G58" s="17" t="inlineStr">
         <is>
-          <t>p95 = 207ms, 0% errors</t>
+          <t>p95 = 704ms, 0% errors</t>
         </is>
       </c>
       <c r="H58" s="17" t="n">
-        <v>11.92</v>
+        <v>11.14</v>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
@@ -19281,11 +19281,11 @@
       </c>
       <c r="G59" s="18" t="inlineStr">
         <is>
-          <t>p95 = 285ms, 0% errors</t>
+          <t>p95 = 288ms, 0% errors</t>
         </is>
       </c>
       <c r="H59" s="18" t="n">
-        <v>5.42</v>
+        <v>4.17</v>
       </c>
       <c r="I59" s="18" t="inlineStr">
         <is>
@@ -19331,11 +19331,11 @@
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>p95 = 554ms, 0% errors</t>
+          <t>p95 = 882ms, 0% errors</t>
         </is>
       </c>
       <c r="H60" s="17" t="n">
-        <v>9.08</v>
+        <v>6.4</v>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
@@ -19381,11 +19381,11 @@
       </c>
       <c r="G61" s="18" t="inlineStr">
         <is>
-          <t>p95 = 466ms, 0% errors</t>
+          <t>p95 = 869ms, 0% errors</t>
         </is>
       </c>
       <c r="H61" s="18" t="n">
-        <v>5.73</v>
+        <v>11.16</v>
       </c>
       <c r="I61" s="18" t="inlineStr">
         <is>
@@ -19431,11 +19431,11 @@
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>p95 = 473ms, 0% errors</t>
+          <t>p95 = 675ms, 0% errors</t>
         </is>
       </c>
       <c r="H62" s="17" t="n">
-        <v>9</v>
+        <v>11.6</v>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
@@ -19481,11 +19481,11 @@
       </c>
       <c r="G63" s="18" t="inlineStr">
         <is>
-          <t>p95 = 312ms, 0% errors</t>
+          <t>p95 = 225ms, 0% errors</t>
         </is>
       </c>
       <c r="H63" s="18" t="n">
-        <v>10.08</v>
+        <v>5.26</v>
       </c>
       <c r="I63" s="18" t="inlineStr">
         <is>
@@ -19531,11 +19531,11 @@
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>p95 = 321ms, 0% errors</t>
+          <t>p95 = 301ms, 0% errors</t>
         </is>
       </c>
       <c r="H64" s="17" t="n">
-        <v>2.96</v>
+        <v>1.97</v>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
@@ -19581,11 +19581,11 @@
       </c>
       <c r="G65" s="18" t="inlineStr">
         <is>
-          <t>p95 = 341ms, 0% errors</t>
+          <t>p95 = 890ms, 0% errors</t>
         </is>
       </c>
       <c r="H65" s="18" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="I65" s="18" t="inlineStr">
         <is>
@@ -19631,11 +19631,11 @@
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>p95 = 415ms, 0% errors</t>
+          <t>p95 = 766ms, 0% errors</t>
         </is>
       </c>
       <c r="H66" s="17" t="n">
-        <v>8.640000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
@@ -19681,11 +19681,11 @@
       </c>
       <c r="G67" s="18" t="inlineStr">
         <is>
-          <t>p95 = 201ms, 0% errors</t>
+          <t>p95 = 882ms, 0% errors</t>
         </is>
       </c>
       <c r="H67" s="18" t="n">
-        <v>6.87</v>
+        <v>5.1</v>
       </c>
       <c r="I67" s="18" t="inlineStr">
         <is>
@@ -19731,11 +19731,11 @@
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>p95 = 788ms, 0% errors</t>
+          <t>p95 = 314ms, 0% errors</t>
         </is>
       </c>
       <c r="H68" s="17" t="n">
-        <v>4.06</v>
+        <v>5.55</v>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
@@ -19781,11 +19781,11 @@
       </c>
       <c r="G69" s="18" t="inlineStr">
         <is>
-          <t>p95 = 342ms, 0% errors</t>
+          <t>p95 = 517ms, 0% errors</t>
         </is>
       </c>
       <c r="H69" s="18" t="n">
-        <v>6.72</v>
+        <v>10.39</v>
       </c>
       <c r="I69" s="18" t="inlineStr">
         <is>
@@ -19831,11 +19831,11 @@
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>p95 = 329ms, 0% errors</t>
+          <t>p95 = 647ms, 0% errors</t>
         </is>
       </c>
       <c r="H70" s="17" t="n">
-        <v>8.199999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
@@ -19881,11 +19881,11 @@
       </c>
       <c r="G71" s="18" t="inlineStr">
         <is>
-          <t>p95 = 531ms, 0% errors</t>
+          <t>p95 = 556ms, 0% errors</t>
         </is>
       </c>
       <c r="H71" s="18" t="n">
-        <v>10.24</v>
+        <v>2.42</v>
       </c>
       <c r="I71" s="18" t="inlineStr">
         <is>
@@ -19931,11 +19931,11 @@
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>p95 = 683ms, 0% errors</t>
+          <t>p95 = 466ms, 0% errors</t>
         </is>
       </c>
       <c r="H72" s="17" t="n">
-        <v>8.1</v>
+        <v>7.69</v>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
@@ -19981,11 +19981,11 @@
       </c>
       <c r="G73" s="18" t="inlineStr">
         <is>
-          <t>p95 = 798ms, 0% errors</t>
+          <t>p95 = 396ms, 0% errors</t>
         </is>
       </c>
       <c r="H73" s="18" t="n">
-        <v>5.57</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I73" s="18" t="inlineStr">
         <is>
@@ -20031,11 +20031,11 @@
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>p95 = 686ms, 0% errors</t>
+          <t>p95 = 312ms, 0% errors</t>
         </is>
       </c>
       <c r="H74" s="17" t="n">
-        <v>3.02</v>
+        <v>11.68</v>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
@@ -20081,11 +20081,11 @@
       </c>
       <c r="G75" s="18" t="inlineStr">
         <is>
-          <t>p95 = 564ms, 0% errors</t>
+          <t>p95 = 852ms, 0% errors</t>
         </is>
       </c>
       <c r="H75" s="18" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="I75" s="18" t="inlineStr">
         <is>
@@ -20131,11 +20131,11 @@
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>p95 = 217ms, 0% errors</t>
+          <t>p95 = 633ms, 0% errors</t>
         </is>
       </c>
       <c r="H76" s="17" t="n">
-        <v>2.47</v>
+        <v>5.71</v>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
@@ -20181,11 +20181,11 @@
       </c>
       <c r="G77" s="18" t="inlineStr">
         <is>
-          <t>p95 = 767ms, 0% errors</t>
+          <t>p95 = 518ms, 0% errors</t>
         </is>
       </c>
       <c r="H77" s="18" t="n">
-        <v>5.48</v>
+        <v>4.5</v>
       </c>
       <c r="I77" s="18" t="inlineStr">
         <is>
@@ -20231,11 +20231,11 @@
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>p95 = 632ms, 0% errors</t>
+          <t>p95 = 440ms, 0% errors</t>
         </is>
       </c>
       <c r="H78" s="17" t="n">
-        <v>8.4</v>
+        <v>6.96</v>
       </c>
       <c r="I78" s="17" t="inlineStr">
         <is>
@@ -20281,11 +20281,11 @@
       </c>
       <c r="G79" s="18" t="inlineStr">
         <is>
-          <t>p95 = 594ms, 0% errors</t>
+          <t>p95 = 253ms, 0% errors</t>
         </is>
       </c>
       <c r="H79" s="18" t="n">
-        <v>2.58</v>
+        <v>4.36</v>
       </c>
       <c r="I79" s="18" t="inlineStr">
         <is>
@@ -20331,11 +20331,11 @@
       </c>
       <c r="G80" s="17" t="inlineStr">
         <is>
-          <t>p95 = 541ms, 0% errors</t>
+          <t>p95 = 780ms, 0% errors</t>
         </is>
       </c>
       <c r="H80" s="17" t="n">
-        <v>4.51</v>
+        <v>2.13</v>
       </c>
       <c r="I80" s="17" t="inlineStr">
         <is>
@@ -20381,11 +20381,11 @@
       </c>
       <c r="G81" s="18" t="inlineStr">
         <is>
-          <t>p95 = 598ms, 0% errors</t>
+          <t>p95 = 533ms, 0% errors</t>
         </is>
       </c>
       <c r="H81" s="18" t="n">
-        <v>5.01</v>
+        <v>11.51</v>
       </c>
       <c r="I81" s="18" t="inlineStr">
         <is>
@@ -20431,11 +20431,11 @@
       </c>
       <c r="G82" s="17" t="inlineStr">
         <is>
-          <t>p95 = 721ms, 0% errors</t>
+          <t>p95 = 189ms, 0% errors</t>
         </is>
       </c>
       <c r="H82" s="17" t="n">
-        <v>11.82</v>
+        <v>10.21</v>
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
@@ -20481,11 +20481,11 @@
       </c>
       <c r="G83" s="18" t="inlineStr">
         <is>
-          <t>p95 = 670ms, 0% errors</t>
+          <t>p95 = 262ms, 0% errors</t>
         </is>
       </c>
       <c r="H83" s="18" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="I83" s="18" t="inlineStr">
         <is>
@@ -20531,11 +20531,11 @@
       </c>
       <c r="G84" s="17" t="inlineStr">
         <is>
-          <t>p95 = 767ms, 0% errors</t>
+          <t>p95 = 774ms, 0% errors</t>
         </is>
       </c>
       <c r="H84" s="17" t="n">
-        <v>7.66</v>
+        <v>8.56</v>
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
@@ -20581,11 +20581,11 @@
       </c>
       <c r="G85" s="18" t="inlineStr">
         <is>
-          <t>p95 = 853ms, 0% errors</t>
+          <t>p95 = 574ms, 0% errors</t>
         </is>
       </c>
       <c r="H85" s="18" t="n">
-        <v>2.47</v>
+        <v>2.87</v>
       </c>
       <c r="I85" s="18" t="inlineStr">
         <is>
@@ -20631,11 +20631,11 @@
       </c>
       <c r="G86" s="17" t="inlineStr">
         <is>
-          <t>p95 = 250ms, 0% errors</t>
+          <t>p95 = 850ms, 0% errors</t>
         </is>
       </c>
       <c r="H86" s="17" t="n">
-        <v>2.47</v>
+        <v>2.96</v>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
@@ -20681,11 +20681,11 @@
       </c>
       <c r="G87" s="18" t="inlineStr">
         <is>
-          <t>p95 = 635ms, 0% errors</t>
+          <t>p95 = 708ms, 0% errors</t>
         </is>
       </c>
       <c r="H87" s="18" t="n">
-        <v>7.6</v>
+        <v>10.93</v>
       </c>
       <c r="I87" s="18" t="inlineStr">
         <is>
@@ -20731,11 +20731,11 @@
       </c>
       <c r="G88" s="17" t="inlineStr">
         <is>
-          <t>p95 = 601ms, 0% errors</t>
+          <t>p95 = 402ms, 0% errors</t>
         </is>
       </c>
       <c r="H88" s="17" t="n">
-        <v>4.5</v>
+        <v>8.1</v>
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
@@ -20781,11 +20781,11 @@
       </c>
       <c r="G89" s="18" t="inlineStr">
         <is>
-          <t>p95 = 358ms, 0% errors</t>
+          <t>p95 = 539ms, 0% errors</t>
         </is>
       </c>
       <c r="H89" s="18" t="n">
-        <v>11.32</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="I89" s="18" t="inlineStr">
         <is>
@@ -20831,11 +20831,11 @@
       </c>
       <c r="G90" s="17" t="inlineStr">
         <is>
-          <t>p95 = 433ms, 0% errors</t>
+          <t>p95 = 314ms, 0% errors</t>
         </is>
       </c>
       <c r="H90" s="17" t="n">
-        <v>4.84</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
@@ -20881,11 +20881,11 @@
       </c>
       <c r="G91" s="18" t="inlineStr">
         <is>
-          <t>p95 = 333ms, 0% errors</t>
+          <t>p95 = 394ms, 0% errors</t>
         </is>
       </c>
       <c r="H91" s="18" t="n">
-        <v>4.14</v>
+        <v>5.01</v>
       </c>
       <c r="I91" s="18" t="inlineStr">
         <is>
@@ -20931,11 +20931,11 @@
       </c>
       <c r="G92" s="17" t="inlineStr">
         <is>
-          <t>p95 = 241ms, 0% errors</t>
+          <t>p95 = 868ms, 0% errors</t>
         </is>
       </c>
       <c r="H92" s="17" t="n">
-        <v>3.35</v>
+        <v>9.94</v>
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
@@ -20981,11 +20981,11 @@
       </c>
       <c r="G93" s="18" t="inlineStr">
         <is>
-          <t>p95 = 515ms, 0% errors</t>
+          <t>p95 = 507ms, 0% errors</t>
         </is>
       </c>
       <c r="H93" s="18" t="n">
-        <v>11.42</v>
+        <v>8.1</v>
       </c>
       <c r="I93" s="18" t="inlineStr">
         <is>
@@ -21031,11 +21031,11 @@
       </c>
       <c r="G94" s="17" t="inlineStr">
         <is>
-          <t>p95 = 187ms, 0% errors</t>
+          <t>p95 = 370ms, 0% errors</t>
         </is>
       </c>
       <c r="H94" s="17" t="n">
-        <v>9.59</v>
+        <v>10.48</v>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
@@ -21081,11 +21081,11 @@
       </c>
       <c r="G95" s="18" t="inlineStr">
         <is>
-          <t>p95 = 597ms, 0% errors</t>
+          <t>p95 = 588ms, 0% errors</t>
         </is>
       </c>
       <c r="H95" s="18" t="n">
-        <v>7.83</v>
+        <v>4.81</v>
       </c>
       <c r="I95" s="18" t="inlineStr">
         <is>
@@ -21131,11 +21131,11 @@
       </c>
       <c r="G96" s="17" t="inlineStr">
         <is>
-          <t>p95 = 573ms, 0% errors</t>
+          <t>p95 = 516ms, 0% errors</t>
         </is>
       </c>
       <c r="H96" s="17" t="n">
-        <v>7.87</v>
+        <v>4.96</v>
       </c>
       <c r="I96" s="17" t="inlineStr">
         <is>
@@ -21181,11 +21181,11 @@
       </c>
       <c r="G97" s="18" t="inlineStr">
         <is>
-          <t>p95 = 682ms, 0% errors</t>
+          <t>p95 = 202ms, 0% errors</t>
         </is>
       </c>
       <c r="H97" s="18" t="n">
-        <v>5.59</v>
+        <v>5.39</v>
       </c>
       <c r="I97" s="18" t="inlineStr">
         <is>
@@ -21231,11 +21231,11 @@
       </c>
       <c r="G98" s="17" t="inlineStr">
         <is>
-          <t>p95 = 664ms, 0% errors</t>
+          <t>p95 = 678ms, 0% errors</t>
         </is>
       </c>
       <c r="H98" s="17" t="n">
-        <v>11.87</v>
+        <v>11.98</v>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
@@ -21281,11 +21281,11 @@
       </c>
       <c r="G99" s="18" t="inlineStr">
         <is>
-          <t>p95 = 874ms, 0% errors</t>
+          <t>p95 = 379ms, 0% errors</t>
         </is>
       </c>
       <c r="H99" s="18" t="n">
-        <v>9.41</v>
+        <v>7.25</v>
       </c>
       <c r="I99" s="18" t="inlineStr">
         <is>
@@ -21331,11 +21331,11 @@
       </c>
       <c r="G100" s="17" t="inlineStr">
         <is>
-          <t>p95 = 400ms, 0% errors</t>
+          <t>p95 = 783ms, 0% errors</t>
         </is>
       </c>
       <c r="H100" s="17" t="n">
-        <v>9</v>
+        <v>2.51</v>
       </c>
       <c r="I100" s="17" t="inlineStr">
         <is>
@@ -21381,11 +21381,11 @@
       </c>
       <c r="G101" s="18" t="inlineStr">
         <is>
-          <t>p95 = 393ms, 0% errors</t>
+          <t>p95 = 428ms, 0% errors</t>
         </is>
       </c>
       <c r="H101" s="18" t="n">
-        <v>2.31</v>
+        <v>6.59</v>
       </c>
       <c r="I101" s="18" t="inlineStr">
         <is>
@@ -21431,11 +21431,11 @@
       </c>
       <c r="G102" s="17" t="inlineStr">
         <is>
-          <t>p95 = 355ms, 0% errors</t>
+          <t>p95 = 674ms, 0% errors</t>
         </is>
       </c>
       <c r="H102" s="17" t="n">
-        <v>10.66</v>
+        <v>4.32</v>
       </c>
       <c r="I102" s="17" t="inlineStr">
         <is>
@@ -21481,11 +21481,11 @@
       </c>
       <c r="G103" s="18" t="inlineStr">
         <is>
-          <t>p95 = 382ms, 0% errors</t>
+          <t>p95 = 766ms, 0% errors</t>
         </is>
       </c>
       <c r="H103" s="18" t="n">
-        <v>2.93</v>
+        <v>9.1</v>
       </c>
       <c r="I103" s="18" t="inlineStr">
         <is>
@@ -21531,11 +21531,11 @@
       </c>
       <c r="G104" s="17" t="inlineStr">
         <is>
-          <t>p95 = 600ms, 0% errors</t>
+          <t>p95 = 838ms, 0% errors</t>
         </is>
       </c>
       <c r="H104" s="17" t="n">
-        <v>10.76</v>
+        <v>4.44</v>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
@@ -21581,11 +21581,11 @@
       </c>
       <c r="G105" s="18" t="inlineStr">
         <is>
-          <t>p95 = 628ms, 0% errors</t>
+          <t>p95 = 517ms, 0% errors</t>
         </is>
       </c>
       <c r="H105" s="18" t="n">
-        <v>2.9</v>
+        <v>8.65</v>
       </c>
       <c r="I105" s="18" t="inlineStr">
         <is>
@@ -21631,11 +21631,11 @@
       </c>
       <c r="G106" s="17" t="inlineStr">
         <is>
-          <t>p95 = 656ms, 0% errors</t>
+          <t>p95 = 563ms, 0% errors</t>
         </is>
       </c>
       <c r="H106" s="17" t="n">
-        <v>11.52</v>
+        <v>8.83</v>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
@@ -21681,11 +21681,11 @@
       </c>
       <c r="G107" s="18" t="inlineStr">
         <is>
-          <t>p95 = 516ms, 0% errors</t>
+          <t>p95 = 361ms, 0% errors</t>
         </is>
       </c>
       <c r="H107" s="18" t="n">
-        <v>11.66</v>
+        <v>1.68</v>
       </c>
       <c r="I107" s="18" t="inlineStr">
         <is>
@@ -21731,11 +21731,11 @@
       </c>
       <c r="G108" s="17" t="inlineStr">
         <is>
-          <t>p95 = 267ms, 0% errors</t>
+          <t>p95 = 399ms, 0% errors</t>
         </is>
       </c>
       <c r="H108" s="17" t="n">
-        <v>8.75</v>
+        <v>4.7</v>
       </c>
       <c r="I108" s="17" t="inlineStr">
         <is>
@@ -21781,11 +21781,11 @@
       </c>
       <c r="G109" s="18" t="inlineStr">
         <is>
-          <t>p95 = 374ms, 0% errors</t>
+          <t>p95 = 370ms, 0% errors</t>
         </is>
       </c>
       <c r="H109" s="18" t="n">
-        <v>8.15</v>
+        <v>7.78</v>
       </c>
       <c r="I109" s="18" t="inlineStr">
         <is>
@@ -21831,11 +21831,11 @@
       </c>
       <c r="G110" s="17" t="inlineStr">
         <is>
-          <t>p95 = 498ms, 0% errors</t>
+          <t>p95 = 534ms, 0% errors</t>
         </is>
       </c>
       <c r="H110" s="17" t="n">
-        <v>2.69</v>
+        <v>11.17</v>
       </c>
       <c r="I110" s="17" t="inlineStr">
         <is>
@@ -21881,11 +21881,11 @@
       </c>
       <c r="G111" s="18" t="inlineStr">
         <is>
-          <t>p95 = 564ms, 0% errors</t>
+          <t>p95 = 493ms, 0% errors</t>
         </is>
       </c>
       <c r="H111" s="18" t="n">
-        <v>7.12</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="I111" s="18" t="inlineStr">
         <is>
@@ -21931,11 +21931,11 @@
       </c>
       <c r="G112" s="17" t="inlineStr">
         <is>
-          <t>p95 = 822ms, 0% errors</t>
+          <t>p95 = 777ms, 0% errors</t>
         </is>
       </c>
       <c r="H112" s="17" t="n">
-        <v>5.63</v>
+        <v>5.75</v>
       </c>
       <c r="I112" s="17" t="inlineStr">
         <is>
@@ -21981,11 +21981,11 @@
       </c>
       <c r="G113" s="18" t="inlineStr">
         <is>
-          <t>p95 = 508ms, 0% errors</t>
+          <t>p95 = 473ms, 0% errors</t>
         </is>
       </c>
       <c r="H113" s="18" t="n">
-        <v>6.34</v>
+        <v>6.29</v>
       </c>
       <c r="I113" s="18" t="inlineStr">
         <is>
@@ -22031,11 +22031,11 @@
       </c>
       <c r="G114" s="17" t="inlineStr">
         <is>
-          <t>p95 = 397ms, 0% errors</t>
+          <t>p95 = 234ms, 0% errors</t>
         </is>
       </c>
       <c r="H114" s="17" t="n">
-        <v>3.89</v>
+        <v>9.56</v>
       </c>
       <c r="I114" s="17" t="inlineStr">
         <is>
@@ -22081,11 +22081,11 @@
       </c>
       <c r="G115" s="18" t="inlineStr">
         <is>
-          <t>p95 = 201ms, 0% errors</t>
+          <t>p95 = 571ms, 0% errors</t>
         </is>
       </c>
       <c r="H115" s="18" t="n">
-        <v>6.62</v>
+        <v>3.37</v>
       </c>
       <c r="I115" s="18" t="inlineStr">
         <is>
@@ -22131,11 +22131,11 @@
       </c>
       <c r="G116" s="17" t="inlineStr">
         <is>
-          <t>p95 = 704ms, 0% errors</t>
+          <t>p95 = 723ms, 0% errors</t>
         </is>
       </c>
       <c r="H116" s="17" t="n">
-        <v>6.25</v>
+        <v>4.58</v>
       </c>
       <c r="I116" s="17" t="inlineStr">
         <is>
@@ -22181,11 +22181,11 @@
       </c>
       <c r="G117" s="18" t="inlineStr">
         <is>
-          <t>p95 = 562ms, 0% errors</t>
+          <t>p95 = 687ms, 0% errors</t>
         </is>
       </c>
       <c r="H117" s="18" t="n">
-        <v>2.95</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I117" s="18" t="inlineStr">
         <is>
@@ -22231,11 +22231,11 @@
       </c>
       <c r="G118" s="17" t="inlineStr">
         <is>
-          <t>p95 = 519ms, 0% errors</t>
+          <t>p95 = 637ms, 0% errors</t>
         </is>
       </c>
       <c r="H118" s="17" t="n">
-        <v>6.07</v>
+        <v>5.77</v>
       </c>
       <c r="I118" s="17" t="inlineStr">
         <is>
@@ -22281,11 +22281,11 @@
       </c>
       <c r="G119" s="18" t="inlineStr">
         <is>
-          <t>p95 = 580ms, 0% errors</t>
+          <t>p95 = 599ms, 0% errors</t>
         </is>
       </c>
       <c r="H119" s="18" t="n">
-        <v>11.78</v>
+        <v>6.68</v>
       </c>
       <c r="I119" s="18" t="inlineStr">
         <is>
@@ -22331,11 +22331,11 @@
       </c>
       <c r="G120" s="17" t="inlineStr">
         <is>
-          <t>p95 = 864ms, 0% errors</t>
+          <t>p95 = 737ms, 0% errors</t>
         </is>
       </c>
       <c r="H120" s="17" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="I120" s="17" t="inlineStr">
         <is>
@@ -22381,11 +22381,11 @@
       </c>
       <c r="G121" s="18" t="inlineStr">
         <is>
-          <t>p95 = 820ms, 0% errors</t>
+          <t>p95 = 817ms, 0% errors</t>
         </is>
       </c>
       <c r="H121" s="18" t="n">
-        <v>3.07</v>
+        <v>11.9</v>
       </c>
       <c r="I121" s="18" t="inlineStr">
         <is>
@@ -22431,11 +22431,11 @@
       </c>
       <c r="G122" s="17" t="inlineStr">
         <is>
-          <t>p95 = 763ms, 0% errors</t>
+          <t>p95 = 386ms, 0% errors</t>
         </is>
       </c>
       <c r="H122" s="17" t="n">
-        <v>1.71</v>
+        <v>3.89</v>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
@@ -22481,11 +22481,11 @@
       </c>
       <c r="G123" s="18" t="inlineStr">
         <is>
-          <t>p95 = 805ms, 0% errors</t>
+          <t>p95 = 346ms, 0% errors</t>
         </is>
       </c>
       <c r="H123" s="18" t="n">
-        <v>11.39</v>
+        <v>4.37</v>
       </c>
       <c r="I123" s="18" t="inlineStr">
         <is>
@@ -22531,11 +22531,11 @@
       </c>
       <c r="G124" s="17" t="inlineStr">
         <is>
-          <t>p95 = 590ms, 0% errors</t>
+          <t>p95 = 360ms, 0% errors</t>
         </is>
       </c>
       <c r="H124" s="17" t="n">
-        <v>5.35</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="I124" s="17" t="inlineStr">
         <is>
@@ -22581,11 +22581,11 @@
       </c>
       <c r="G125" s="18" t="inlineStr">
         <is>
-          <t>p95 = 875ms, 0% errors</t>
+          <t>p95 = 310ms, 0% errors</t>
         </is>
       </c>
       <c r="H125" s="18" t="n">
-        <v>4.04</v>
+        <v>9.82</v>
       </c>
       <c r="I125" s="18" t="inlineStr">
         <is>
@@ -22631,11 +22631,11 @@
       </c>
       <c r="G126" s="17" t="inlineStr">
         <is>
-          <t>p95 = 552ms, 0% errors</t>
+          <t>p95 = 565ms, 0% errors</t>
         </is>
       </c>
       <c r="H126" s="17" t="n">
-        <v>3.65</v>
+        <v>6.83</v>
       </c>
       <c r="I126" s="17" t="inlineStr">
         <is>
@@ -22681,11 +22681,11 @@
       </c>
       <c r="G127" s="18" t="inlineStr">
         <is>
-          <t>p95 = 668ms, 0% errors</t>
+          <t>p95 = 716ms, 0% errors</t>
         </is>
       </c>
       <c r="H127" s="18" t="n">
-        <v>2.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I127" s="18" t="inlineStr">
         <is>
@@ -22731,11 +22731,11 @@
       </c>
       <c r="G128" s="17" t="inlineStr">
         <is>
-          <t>p95 = 626ms, 0% errors</t>
+          <t>p95 = 802ms, 0% errors</t>
         </is>
       </c>
       <c r="H128" s="17" t="n">
-        <v>7.69</v>
+        <v>5.44</v>
       </c>
       <c r="I128" s="17" t="inlineStr">
         <is>
@@ -22781,11 +22781,11 @@
       </c>
       <c r="G129" s="18" t="inlineStr">
         <is>
-          <t>p95 = 726ms, 0% errors</t>
+          <t>p95 = 548ms, 0% errors</t>
         </is>
       </c>
       <c r="H129" s="18" t="n">
-        <v>10.91</v>
+        <v>8.51</v>
       </c>
       <c r="I129" s="18" t="inlineStr">
         <is>
@@ -22831,11 +22831,11 @@
       </c>
       <c r="G130" s="17" t="inlineStr">
         <is>
-          <t>p95 = 691ms, 0% errors</t>
+          <t>p95 = 349ms, 0% errors</t>
         </is>
       </c>
       <c r="H130" s="17" t="n">
-        <v>5.81</v>
+        <v>2.31</v>
       </c>
       <c r="I130" s="17" t="inlineStr">
         <is>
@@ -22881,11 +22881,11 @@
       </c>
       <c r="G131" s="18" t="inlineStr">
         <is>
-          <t>p95 = 570ms, 0% errors</t>
+          <t>p95 = 647ms, 0% errors</t>
         </is>
       </c>
       <c r="H131" s="18" t="n">
-        <v>1.59</v>
+        <v>5.51</v>
       </c>
       <c r="I131" s="18" t="inlineStr">
         <is>
@@ -22931,11 +22931,11 @@
       </c>
       <c r="G132" s="17" t="inlineStr">
         <is>
-          <t>p95 = 698ms, 0% errors</t>
+          <t>p95 = 425ms, 0% errors</t>
         </is>
       </c>
       <c r="H132" s="17" t="n">
-        <v>9.67</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="I132" s="17" t="inlineStr">
         <is>
@@ -22981,11 +22981,11 @@
       </c>
       <c r="G133" s="18" t="inlineStr">
         <is>
-          <t>p95 = 279ms, 0% errors</t>
+          <t>p95 = 694ms, 0% errors</t>
         </is>
       </c>
       <c r="H133" s="18" t="n">
-        <v>9.699999999999999</v>
+        <v>4.73</v>
       </c>
       <c r="I133" s="18" t="inlineStr">
         <is>
@@ -23031,11 +23031,11 @@
       </c>
       <c r="G134" s="17" t="inlineStr">
         <is>
-          <t>p95 = 253ms, 0% errors</t>
+          <t>p95 = 871ms, 0% errors</t>
         </is>
       </c>
       <c r="H134" s="17" t="n">
-        <v>7.03</v>
+        <v>8.6</v>
       </c>
       <c r="I134" s="17" t="inlineStr">
         <is>
@@ -23081,11 +23081,11 @@
       </c>
       <c r="G135" s="18" t="inlineStr">
         <is>
-          <t>p95 = 215ms, 0% errors</t>
+          <t>p95 = 327ms, 0% errors</t>
         </is>
       </c>
       <c r="H135" s="18" t="n">
-        <v>11.35</v>
+        <v>2.12</v>
       </c>
       <c r="I135" s="18" t="inlineStr">
         <is>
@@ -23131,11 +23131,11 @@
       </c>
       <c r="G136" s="17" t="inlineStr">
         <is>
-          <t>p95 = 542ms, 0% errors</t>
+          <t>p95 = 391ms, 0% errors</t>
         </is>
       </c>
       <c r="H136" s="17" t="n">
-        <v>10.95</v>
+        <v>3.25</v>
       </c>
       <c r="I136" s="17" t="inlineStr">
         <is>
@@ -23181,11 +23181,11 @@
       </c>
       <c r="G137" s="18" t="inlineStr">
         <is>
-          <t>p95 = 884ms, 0% errors</t>
+          <t>p95 = 222ms, 0% errors</t>
         </is>
       </c>
       <c r="H137" s="18" t="n">
-        <v>5.02</v>
+        <v>8.24</v>
       </c>
       <c r="I137" s="18" t="inlineStr">
         <is>
@@ -23231,11 +23231,11 @@
       </c>
       <c r="G138" s="17" t="inlineStr">
         <is>
-          <t>p95 = 209ms, 0% errors</t>
+          <t>p95 = 787ms, 0% errors</t>
         </is>
       </c>
       <c r="H138" s="17" t="n">
-        <v>7</v>
+        <v>11.67</v>
       </c>
       <c r="I138" s="17" t="inlineStr">
         <is>
@@ -23281,11 +23281,11 @@
       </c>
       <c r="G139" s="18" t="inlineStr">
         <is>
-          <t>p95 = 541ms, 0% errors</t>
+          <t>p95 = 194ms, 0% errors</t>
         </is>
       </c>
       <c r="H139" s="18" t="n">
-        <v>6.34</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I139" s="18" t="inlineStr">
         <is>
@@ -23331,11 +23331,11 @@
       </c>
       <c r="G140" s="17" t="inlineStr">
         <is>
-          <t>p95 = 449ms, 0% errors</t>
+          <t>p95 = 612ms, 0% errors</t>
         </is>
       </c>
       <c r="H140" s="17" t="n">
-        <v>5.77</v>
+        <v>3.87</v>
       </c>
       <c r="I140" s="17" t="inlineStr">
         <is>
@@ -23381,11 +23381,11 @@
       </c>
       <c r="G141" s="18" t="inlineStr">
         <is>
-          <t>p95 = 527ms, 0% errors</t>
+          <t>p95 = 319ms, 0% errors</t>
         </is>
       </c>
       <c r="H141" s="18" t="n">
-        <v>5.46</v>
+        <v>7.1</v>
       </c>
       <c r="I141" s="18" t="inlineStr">
         <is>
@@ -23431,11 +23431,11 @@
       </c>
       <c r="G142" s="17" t="inlineStr">
         <is>
-          <t>p95 = 562ms, 0% errors</t>
+          <t>p95 = 571ms, 0% errors</t>
         </is>
       </c>
       <c r="H142" s="17" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="I142" s="17" t="inlineStr">
         <is>
@@ -23481,11 +23481,11 @@
       </c>
       <c r="G143" s="18" t="inlineStr">
         <is>
-          <t>p95 = 713ms, 0% errors</t>
+          <t>p95 = 276ms, 0% errors</t>
         </is>
       </c>
       <c r="H143" s="18" t="n">
-        <v>7.71</v>
+        <v>5.33</v>
       </c>
       <c r="I143" s="18" t="inlineStr">
         <is>
@@ -23531,11 +23531,11 @@
       </c>
       <c r="G144" s="17" t="inlineStr">
         <is>
-          <t>p95 = 519ms, 0% errors</t>
+          <t>p95 = 705ms, 0% errors</t>
         </is>
       </c>
       <c r="H144" s="17" t="n">
-        <v>1.77</v>
+        <v>7.11</v>
       </c>
       <c r="I144" s="17" t="inlineStr">
         <is>
@@ -23581,11 +23581,11 @@
       </c>
       <c r="G145" s="18" t="inlineStr">
         <is>
-          <t>p95 = 867ms, 0% errors</t>
+          <t>p95 = 591ms, 0% errors</t>
         </is>
       </c>
       <c r="H145" s="18" t="n">
-        <v>6.23</v>
+        <v>3.26</v>
       </c>
       <c r="I145" s="18" t="inlineStr">
         <is>
@@ -23631,11 +23631,11 @@
       </c>
       <c r="G146" s="17" t="inlineStr">
         <is>
-          <t>p95 = 850ms, 0% errors</t>
+          <t>p95 = 855ms, 0% errors</t>
         </is>
       </c>
       <c r="H146" s="17" t="n">
-        <v>2.02</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I146" s="17" t="inlineStr">
         <is>
@@ -23681,11 +23681,11 @@
       </c>
       <c r="G147" s="18" t="inlineStr">
         <is>
-          <t>p95 = 595ms, 0% errors</t>
+          <t>p95 = 868ms, 0% errors</t>
         </is>
       </c>
       <c r="H147" s="18" t="n">
-        <v>5.19</v>
+        <v>7.14</v>
       </c>
       <c r="I147" s="18" t="inlineStr">
         <is>
@@ -23731,11 +23731,11 @@
       </c>
       <c r="G148" s="17" t="inlineStr">
         <is>
-          <t>p95 = 297ms, 0% errors</t>
+          <t>p95 = 192ms, 0% errors</t>
         </is>
       </c>
       <c r="H148" s="17" t="n">
-        <v>3.76</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="I148" s="17" t="inlineStr">
         <is>
@@ -23781,11 +23781,11 @@
       </c>
       <c r="G149" s="18" t="inlineStr">
         <is>
-          <t>p95 = 340ms, 0% errors</t>
+          <t>p95 = 324ms, 0% errors</t>
         </is>
       </c>
       <c r="H149" s="18" t="n">
-        <v>6.36</v>
+        <v>2.26</v>
       </c>
       <c r="I149" s="18" t="inlineStr">
         <is>
@@ -23831,11 +23831,11 @@
       </c>
       <c r="G150" s="17" t="inlineStr">
         <is>
-          <t>p95 = 599ms, 0% errors</t>
+          <t>p95 = 666ms, 0% errors</t>
         </is>
       </c>
       <c r="H150" s="17" t="n">
-        <v>9.630000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="I150" s="17" t="inlineStr">
         <is>
@@ -23881,11 +23881,11 @@
       </c>
       <c r="G151" s="18" t="inlineStr">
         <is>
-          <t>p95 = 216ms, 0% errors</t>
+          <t>p95 = 450ms, 0% errors</t>
         </is>
       </c>
       <c r="H151" s="18" t="n">
-        <v>4.65</v>
+        <v>3.57</v>
       </c>
       <c r="I151" s="18" t="inlineStr">
         <is>
@@ -23931,11 +23931,11 @@
       </c>
       <c r="G152" s="17" t="inlineStr">
         <is>
-          <t>p95 = 717ms, 0% errors</t>
+          <t>p95 = 472ms, 0% errors</t>
         </is>
       </c>
       <c r="H152" s="17" t="n">
-        <v>4.52</v>
+        <v>3.79</v>
       </c>
       <c r="I152" s="17" t="inlineStr">
         <is>
@@ -23981,11 +23981,11 @@
       </c>
       <c r="G153" s="18" t="inlineStr">
         <is>
-          <t>p95 = 326ms, 0% errors</t>
+          <t>p95 = 443ms, 0% errors</t>
         </is>
       </c>
       <c r="H153" s="18" t="n">
-        <v>6.69</v>
+        <v>7.17</v>
       </c>
       <c r="I153" s="18" t="inlineStr">
         <is>
@@ -24031,11 +24031,11 @@
       </c>
       <c r="G154" s="17" t="inlineStr">
         <is>
-          <t>p95 = 656ms, 0% errors</t>
+          <t>p95 = 835ms, 0% errors</t>
         </is>
       </c>
       <c r="H154" s="17" t="n">
-        <v>3.41</v>
+        <v>1.81</v>
       </c>
       <c r="I154" s="17" t="inlineStr">
         <is>
@@ -24081,11 +24081,11 @@
       </c>
       <c r="G155" s="18" t="inlineStr">
         <is>
-          <t>p95 = 665ms, 0% errors</t>
+          <t>p95 = 197ms, 0% errors</t>
         </is>
       </c>
       <c r="H155" s="18" t="n">
-        <v>9.17</v>
+        <v>10.54</v>
       </c>
       <c r="I155" s="18" t="inlineStr">
         <is>
@@ -24131,11 +24131,11 @@
       </c>
       <c r="G156" s="17" t="inlineStr">
         <is>
-          <t>p95 = 649ms, 0% errors</t>
+          <t>p95 = 183ms, 0% errors</t>
         </is>
       </c>
       <c r="H156" s="17" t="n">
-        <v>9.539999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="I156" s="17" t="inlineStr">
         <is>
@@ -24181,11 +24181,11 @@
       </c>
       <c r="G157" s="18" t="inlineStr">
         <is>
-          <t>p95 = 579ms, 0% errors</t>
+          <t>p95 = 763ms, 0% errors</t>
         </is>
       </c>
       <c r="H157" s="18" t="n">
-        <v>3.94</v>
+        <v>4.46</v>
       </c>
       <c r="I157" s="18" t="inlineStr">
         <is>
@@ -24231,11 +24231,11 @@
       </c>
       <c r="G158" s="17" t="inlineStr">
         <is>
-          <t>p95 = 632ms, 0% errors</t>
+          <t>p95 = 858ms, 0% errors</t>
         </is>
       </c>
       <c r="H158" s="17" t="n">
-        <v>4.29</v>
+        <v>10.52</v>
       </c>
       <c r="I158" s="17" t="inlineStr">
         <is>
@@ -24281,11 +24281,11 @@
       </c>
       <c r="G159" s="18" t="inlineStr">
         <is>
-          <t>p95 = 394ms, 0% errors</t>
+          <t>p95 = 376ms, 0% errors</t>
         </is>
       </c>
       <c r="H159" s="18" t="n">
-        <v>6.97</v>
+        <v>4.93</v>
       </c>
       <c r="I159" s="18" t="inlineStr">
         <is>
@@ -24331,11 +24331,11 @@
       </c>
       <c r="G160" s="17" t="inlineStr">
         <is>
-          <t>p95 = 195ms, 0% errors</t>
+          <t>p95 = 792ms, 0% errors</t>
         </is>
       </c>
       <c r="H160" s="17" t="n">
-        <v>4.8</v>
+        <v>10.82</v>
       </c>
       <c r="I160" s="17" t="inlineStr">
         <is>
@@ -24381,11 +24381,11 @@
       </c>
       <c r="G161" s="18" t="inlineStr">
         <is>
-          <t>p95 = 823ms, 0% errors</t>
+          <t>p95 = 828ms, 0% errors</t>
         </is>
       </c>
       <c r="H161" s="18" t="n">
-        <v>3.61</v>
+        <v>11.64</v>
       </c>
       <c r="I161" s="18" t="inlineStr">
         <is>
@@ -24431,11 +24431,11 @@
       </c>
       <c r="G162" s="17" t="inlineStr">
         <is>
-          <t>p95 = 608ms, 0% errors</t>
+          <t>p95 = 550ms, 0% errors</t>
         </is>
       </c>
       <c r="H162" s="17" t="n">
-        <v>11.11</v>
+        <v>5.89</v>
       </c>
       <c r="I162" s="17" t="inlineStr">
         <is>
@@ -24481,11 +24481,11 @@
       </c>
       <c r="G163" s="18" t="inlineStr">
         <is>
-          <t>p95 = 518ms, 0% errors</t>
+          <t>p95 = 492ms, 0% errors</t>
         </is>
       </c>
       <c r="H163" s="18" t="n">
-        <v>9.58</v>
+        <v>7.22</v>
       </c>
       <c r="I163" s="18" t="inlineStr">
         <is>
@@ -24531,11 +24531,11 @@
       </c>
       <c r="G164" s="17" t="inlineStr">
         <is>
-          <t>p95 = 832ms, 0% errors</t>
+          <t>p95 = 573ms, 0% errors</t>
         </is>
       </c>
       <c r="H164" s="17" t="n">
-        <v>8.390000000000001</v>
+        <v>2.29</v>
       </c>
       <c r="I164" s="17" t="inlineStr">
         <is>
@@ -24581,11 +24581,11 @@
       </c>
       <c r="G165" s="18" t="inlineStr">
         <is>
-          <t>p95 = 665ms, 0% errors</t>
+          <t>p95 = 887ms, 0% errors</t>
         </is>
       </c>
       <c r="H165" s="18" t="n">
-        <v>5.25</v>
+        <v>1.91</v>
       </c>
       <c r="I165" s="18" t="inlineStr">
         <is>
@@ -24631,11 +24631,11 @@
       </c>
       <c r="G166" s="17" t="inlineStr">
         <is>
-          <t>p95 = 816ms, 0% errors</t>
+          <t>p95 = 674ms, 0% errors</t>
         </is>
       </c>
       <c r="H166" s="17" t="n">
-        <v>6.59</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I166" s="17" t="inlineStr">
         <is>
@@ -24681,11 +24681,11 @@
       </c>
       <c r="G167" s="18" t="inlineStr">
         <is>
-          <t>p95 = 312ms, 0% errors</t>
+          <t>p95 = 189ms, 0% errors</t>
         </is>
       </c>
       <c r="H167" s="18" t="n">
-        <v>8.06</v>
+        <v>7.13</v>
       </c>
       <c r="I167" s="18" t="inlineStr">
         <is>
@@ -24731,11 +24731,11 @@
       </c>
       <c r="G168" s="17" t="inlineStr">
         <is>
-          <t>p95 = 377ms, 0% errors</t>
+          <t>p95 = 609ms, 0% errors</t>
         </is>
       </c>
       <c r="H168" s="17" t="n">
-        <v>3.69</v>
+        <v>10.79</v>
       </c>
       <c r="I168" s="17" t="inlineStr">
         <is>
@@ -24781,11 +24781,11 @@
       </c>
       <c r="G169" s="18" t="inlineStr">
         <is>
-          <t>p95 = 435ms, 0% errors</t>
+          <t>p95 = 627ms, 0% errors</t>
         </is>
       </c>
       <c r="H169" s="18" t="n">
-        <v>5.75</v>
+        <v>5.92</v>
       </c>
       <c r="I169" s="18" t="inlineStr">
         <is>
@@ -24831,11 +24831,11 @@
       </c>
       <c r="G170" s="17" t="inlineStr">
         <is>
-          <t>p95 = 267ms, 0% errors</t>
+          <t>p95 = 531ms, 0% errors</t>
         </is>
       </c>
       <c r="H170" s="17" t="n">
-        <v>10.05</v>
+        <v>3.23</v>
       </c>
       <c r="I170" s="17" t="inlineStr">
         <is>
@@ -24881,11 +24881,11 @@
       </c>
       <c r="G171" s="18" t="inlineStr">
         <is>
-          <t>p95 = 214ms, 0% errors</t>
+          <t>p95 = 816ms, 0% errors</t>
         </is>
       </c>
       <c r="H171" s="18" t="n">
-        <v>5.8</v>
+        <v>7.64</v>
       </c>
       <c r="I171" s="18" t="inlineStr">
         <is>
@@ -24931,11 +24931,11 @@
       </c>
       <c r="G172" s="17" t="inlineStr">
         <is>
-          <t>p95 = 337ms, 0% errors</t>
+          <t>p95 = 583ms, 0% errors</t>
         </is>
       </c>
       <c r="H172" s="17" t="n">
-        <v>3.62</v>
+        <v>6.96</v>
       </c>
       <c r="I172" s="17" t="inlineStr">
         <is>
@@ -24981,11 +24981,11 @@
       </c>
       <c r="G173" s="18" t="inlineStr">
         <is>
-          <t>p95 = 506ms, 0% errors</t>
+          <t>p95 = 735ms, 0% errors</t>
         </is>
       </c>
       <c r="H173" s="18" t="n">
-        <v>10.8</v>
+        <v>5.43</v>
       </c>
       <c r="I173" s="18" t="inlineStr">
         <is>
@@ -25031,11 +25031,11 @@
       </c>
       <c r="G174" s="17" t="inlineStr">
         <is>
-          <t>p95 = 723ms, 0% errors</t>
+          <t>p95 = 809ms, 0% errors</t>
         </is>
       </c>
       <c r="H174" s="17" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="I174" s="17" t="inlineStr">
         <is>
@@ -25081,11 +25081,11 @@
       </c>
       <c r="G175" s="18" t="inlineStr">
         <is>
-          <t>p95 = 686ms, 0% errors</t>
+          <t>p95 = 191ms, 0% errors</t>
         </is>
       </c>
       <c r="H175" s="18" t="n">
-        <v>3.5</v>
+        <v>8.17</v>
       </c>
       <c r="I175" s="18" t="inlineStr">
         <is>
@@ -25131,11 +25131,11 @@
       </c>
       <c r="G176" s="17" t="inlineStr">
         <is>
-          <t>p95 = 351ms, 0% errors</t>
+          <t>p95 = 358ms, 0% errors</t>
         </is>
       </c>
       <c r="H176" s="17" t="n">
-        <v>8.76</v>
+        <v>6.01</v>
       </c>
       <c r="I176" s="17" t="inlineStr">
         <is>
@@ -25181,11 +25181,11 @@
       </c>
       <c r="G177" s="18" t="inlineStr">
         <is>
-          <t>p95 = 589ms, 0% errors</t>
+          <t>p95 = 735ms, 0% errors</t>
         </is>
       </c>
       <c r="H177" s="18" t="n">
-        <v>2.2</v>
+        <v>11.01</v>
       </c>
       <c r="I177" s="18" t="inlineStr">
         <is>
@@ -25231,11 +25231,11 @@
       </c>
       <c r="G178" s="17" t="inlineStr">
         <is>
-          <t>p95 = 340ms, 0% errors</t>
+          <t>p95 = 478ms, 0% errors</t>
         </is>
       </c>
       <c r="H178" s="17" t="n">
-        <v>10.44</v>
+        <v>5.58</v>
       </c>
       <c r="I178" s="17" t="inlineStr">
         <is>
@@ -25281,11 +25281,11 @@
       </c>
       <c r="G179" s="18" t="inlineStr">
         <is>
-          <t>p95 = 247ms, 0% errors</t>
+          <t>p95 = 397ms, 0% errors</t>
         </is>
       </c>
       <c r="H179" s="18" t="n">
-        <v>4.86</v>
+        <v>2.73</v>
       </c>
       <c r="I179" s="18" t="inlineStr">
         <is>
@@ -25331,11 +25331,11 @@
       </c>
       <c r="G180" s="17" t="inlineStr">
         <is>
-          <t>p95 = 214ms, 0% errors</t>
+          <t>p95 = 256ms, 0% errors</t>
         </is>
       </c>
       <c r="H180" s="17" t="n">
-        <v>3.73</v>
+        <v>7.9</v>
       </c>
       <c r="I180" s="17" t="inlineStr">
         <is>
@@ -25381,11 +25381,11 @@
       </c>
       <c r="G181" s="18" t="inlineStr">
         <is>
-          <t>p95 = 375ms, 0% errors</t>
+          <t>p95 = 558ms, 0% errors</t>
         </is>
       </c>
       <c r="H181" s="18" t="n">
-        <v>2.21</v>
+        <v>6.28</v>
       </c>
       <c r="I181" s="18" t="inlineStr">
         <is>
@@ -25431,11 +25431,11 @@
       </c>
       <c r="G182" s="17" t="inlineStr">
         <is>
-          <t>p95 = 225ms, 0% errors</t>
+          <t>p95 = 575ms, 0% errors</t>
         </is>
       </c>
       <c r="H182" s="17" t="n">
-        <v>5.69</v>
+        <v>10.05</v>
       </c>
       <c r="I182" s="17" t="inlineStr">
         <is>
@@ -25481,11 +25481,11 @@
       </c>
       <c r="G183" s="18" t="inlineStr">
         <is>
-          <t>p95 = 653ms, 0% errors</t>
+          <t>p95 = 876ms, 0% errors</t>
         </is>
       </c>
       <c r="H183" s="18" t="n">
-        <v>9.59</v>
+        <v>11.98</v>
       </c>
       <c r="I183" s="18" t="inlineStr">
         <is>
@@ -25531,11 +25531,11 @@
       </c>
       <c r="G184" s="17" t="inlineStr">
         <is>
-          <t>p95 = 244ms, 0% errors</t>
+          <t>p95 = 570ms, 0% errors</t>
         </is>
       </c>
       <c r="H184" s="17" t="n">
-        <v>10.02</v>
+        <v>10.15</v>
       </c>
       <c r="I184" s="17" t="inlineStr">
         <is>
@@ -25581,11 +25581,11 @@
       </c>
       <c r="G185" s="18" t="inlineStr">
         <is>
-          <t>p95 = 425ms, 0% errors</t>
+          <t>p95 = 232ms, 0% errors</t>
         </is>
       </c>
       <c r="H185" s="18" t="n">
-        <v>2.74</v>
+        <v>10.33</v>
       </c>
       <c r="I185" s="18" t="inlineStr">
         <is>
@@ -25631,11 +25631,11 @@
       </c>
       <c r="G186" s="17" t="inlineStr">
         <is>
-          <t>p95 = 421ms, 0% errors</t>
+          <t>p95 = 665ms, 0% errors</t>
         </is>
       </c>
       <c r="H186" s="17" t="n">
-        <v>2.83</v>
+        <v>5.04</v>
       </c>
       <c r="I186" s="17" t="inlineStr">
         <is>
@@ -25681,11 +25681,11 @@
       </c>
       <c r="G187" s="18" t="inlineStr">
         <is>
-          <t>p95 = 505ms, 0% errors</t>
+          <t>p95 = 337ms, 0% errors</t>
         </is>
       </c>
       <c r="H187" s="18" t="n">
-        <v>6.33</v>
+        <v>4.57</v>
       </c>
       <c r="I187" s="18" t="inlineStr">
         <is>
@@ -25731,11 +25731,11 @@
       </c>
       <c r="G188" s="17" t="inlineStr">
         <is>
-          <t>p95 = 805ms, 0% errors</t>
+          <t>p95 = 363ms, 0% errors</t>
         </is>
       </c>
       <c r="H188" s="17" t="n">
-        <v>8.42</v>
+        <v>11.27</v>
       </c>
       <c r="I188" s="17" t="inlineStr">
         <is>
@@ -25781,11 +25781,11 @@
       </c>
       <c r="G189" s="18" t="inlineStr">
         <is>
-          <t>p95 = 479ms, 0% errors</t>
+          <t>p95 = 296ms, 0% errors</t>
         </is>
       </c>
       <c r="H189" s="18" t="n">
-        <v>10.64</v>
+        <v>4.31</v>
       </c>
       <c r="I189" s="18" t="inlineStr">
         <is>
@@ -25831,11 +25831,11 @@
       </c>
       <c r="G190" s="17" t="inlineStr">
         <is>
-          <t>p95 = 777ms, 0% errors</t>
+          <t>p95 = 201ms, 0% errors</t>
         </is>
       </c>
       <c r="H190" s="17" t="n">
-        <v>2.38</v>
+        <v>5.44</v>
       </c>
       <c r="I190" s="17" t="inlineStr">
         <is>
@@ -25881,11 +25881,11 @@
       </c>
       <c r="G191" s="18" t="inlineStr">
         <is>
-          <t>p95 = 789ms, 0% errors</t>
+          <t>p95 = 259ms, 0% errors</t>
         </is>
       </c>
       <c r="H191" s="18" t="n">
-        <v>10.5</v>
+        <v>4.65</v>
       </c>
       <c r="I191" s="18" t="inlineStr">
         <is>
@@ -25931,11 +25931,11 @@
       </c>
       <c r="G192" s="17" t="inlineStr">
         <is>
-          <t>p95 = 259ms, 0% errors</t>
+          <t>p95 = 564ms, 0% errors</t>
         </is>
       </c>
       <c r="H192" s="17" t="n">
-        <v>11.16</v>
+        <v>4.89</v>
       </c>
       <c r="I192" s="17" t="inlineStr">
         <is>
@@ -25981,11 +25981,11 @@
       </c>
       <c r="G193" s="18" t="inlineStr">
         <is>
-          <t>p95 = 742ms, 0% errors</t>
+          <t>p95 = 259ms, 0% errors</t>
         </is>
       </c>
       <c r="H193" s="18" t="n">
-        <v>4.55</v>
+        <v>11.55</v>
       </c>
       <c r="I193" s="18" t="inlineStr">
         <is>
@@ -26031,11 +26031,11 @@
       </c>
       <c r="G194" s="17" t="inlineStr">
         <is>
-          <t>p95 = 407ms, 0% errors</t>
+          <t>p95 = 665ms, 0% errors</t>
         </is>
       </c>
       <c r="H194" s="17" t="n">
-        <v>4.16</v>
+        <v>7.46</v>
       </c>
       <c r="I194" s="17" t="inlineStr">
         <is>
@@ -26081,11 +26081,11 @@
       </c>
       <c r="G195" s="18" t="inlineStr">
         <is>
-          <t>p95 = 396ms, 0% errors</t>
+          <t>p95 = 556ms, 0% errors</t>
         </is>
       </c>
       <c r="H195" s="18" t="n">
-        <v>6.04</v>
+        <v>2.56</v>
       </c>
       <c r="I195" s="18" t="inlineStr">
         <is>
@@ -26131,11 +26131,11 @@
       </c>
       <c r="G196" s="17" t="inlineStr">
         <is>
-          <t>p95 = 288ms, 0% errors</t>
+          <t>p95 = 766ms, 0% errors</t>
         </is>
       </c>
       <c r="H196" s="17" t="n">
-        <v>11.58</v>
+        <v>11.08</v>
       </c>
       <c r="I196" s="17" t="inlineStr">
         <is>
@@ -26181,11 +26181,11 @@
       </c>
       <c r="G197" s="18" t="inlineStr">
         <is>
-          <t>p95 = 285ms, 0% errors</t>
+          <t>p95 = 802ms, 0% errors</t>
         </is>
       </c>
       <c r="H197" s="18" t="n">
-        <v>7.2</v>
+        <v>5.19</v>
       </c>
       <c r="I197" s="18" t="inlineStr">
         <is>
@@ -26231,11 +26231,11 @@
       </c>
       <c r="G198" s="17" t="inlineStr">
         <is>
-          <t>p95 = 702ms, 0% errors</t>
+          <t>p95 = 404ms, 0% errors</t>
         </is>
       </c>
       <c r="H198" s="17" t="n">
-        <v>2.32</v>
+        <v>4.91</v>
       </c>
       <c r="I198" s="17" t="inlineStr">
         <is>
@@ -26281,11 +26281,11 @@
       </c>
       <c r="G199" s="18" t="inlineStr">
         <is>
-          <t>p95 = 569ms, 0% errors</t>
+          <t>p95 = 724ms, 0% errors</t>
         </is>
       </c>
       <c r="H199" s="18" t="n">
-        <v>2.32</v>
+        <v>7.74</v>
       </c>
       <c r="I199" s="18" t="inlineStr">
         <is>
@@ -26331,11 +26331,11 @@
       </c>
       <c r="G200" s="17" t="inlineStr">
         <is>
-          <t>p95 = 853ms, 0% errors</t>
+          <t>p95 = 518ms, 0% errors</t>
         </is>
       </c>
       <c r="H200" s="17" t="n">
-        <v>8.949999999999999</v>
+        <v>6.24</v>
       </c>
       <c r="I200" s="17" t="inlineStr">
         <is>
@@ -26381,11 +26381,11 @@
       </c>
       <c r="G201" s="18" t="inlineStr">
         <is>
-          <t>p95 = 700ms, 0% errors</t>
+          <t>p95 = 226ms, 0% errors</t>
         </is>
       </c>
       <c r="H201" s="18" t="n">
-        <v>11.04</v>
+        <v>9.9</v>
       </c>
       <c r="I201" s="18" t="inlineStr">
         <is>
@@ -26431,11 +26431,11 @@
       </c>
       <c r="G202" s="17" t="inlineStr">
         <is>
-          <t>p95 = 582ms, 0% errors</t>
+          <t>p95 = 444ms, 0% errors</t>
         </is>
       </c>
       <c r="H202" s="17" t="n">
-        <v>7.42</v>
+        <v>8.44</v>
       </c>
       <c r="I202" s="17" t="inlineStr">
         <is>
@@ -26481,11 +26481,11 @@
       </c>
       <c r="G203" s="18" t="inlineStr">
         <is>
-          <t>p95 = 843ms, 0% errors</t>
+          <t>p95 = 734ms, 0% errors</t>
         </is>
       </c>
       <c r="H203" s="18" t="n">
-        <v>6.86</v>
+        <v>7.31</v>
       </c>
       <c r="I203" s="18" t="inlineStr">
         <is>
@@ -26531,11 +26531,11 @@
       </c>
       <c r="G204" s="17" t="inlineStr">
         <is>
-          <t>p95 = 571ms, 0% errors</t>
+          <t>p95 = 726ms, 0% errors</t>
         </is>
       </c>
       <c r="H204" s="17" t="n">
-        <v>6.42</v>
+        <v>2.54</v>
       </c>
       <c r="I204" s="17" t="inlineStr">
         <is>
@@ -26581,11 +26581,11 @@
       </c>
       <c r="G205" s="18" t="inlineStr">
         <is>
-          <t>p95 = 492ms, 0% errors</t>
+          <t>p95 = 722ms, 0% errors</t>
         </is>
       </c>
       <c r="H205" s="18" t="n">
-        <v>11.6</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="I205" s="18" t="inlineStr">
         <is>
@@ -26631,11 +26631,11 @@
       </c>
       <c r="G206" s="17" t="inlineStr">
         <is>
-          <t>p95 = 282ms, 0% errors</t>
+          <t>p95 = 446ms, 0% errors</t>
         </is>
       </c>
       <c r="H206" s="17" t="n">
-        <v>5.54</v>
+        <v>3.1</v>
       </c>
       <c r="I206" s="17" t="inlineStr">
         <is>
@@ -26681,11 +26681,11 @@
       </c>
       <c r="G207" s="18" t="inlineStr">
         <is>
-          <t>p95 = 716ms, 0% errors</t>
+          <t>p95 = 827ms, 0% errors</t>
         </is>
       </c>
       <c r="H207" s="18" t="n">
-        <v>8.94</v>
+        <v>8.07</v>
       </c>
       <c r="I207" s="18" t="inlineStr">
         <is>
@@ -26731,11 +26731,11 @@
       </c>
       <c r="G208" s="17" t="inlineStr">
         <is>
-          <t>p95 = 750ms, 0% errors</t>
+          <t>p95 = 846ms, 0% errors</t>
         </is>
       </c>
       <c r="H208" s="17" t="n">
-        <v>3.46</v>
+        <v>7.37</v>
       </c>
       <c r="I208" s="17" t="inlineStr">
         <is>
@@ -26781,11 +26781,11 @@
       </c>
       <c r="G209" s="18" t="inlineStr">
         <is>
-          <t>p95 = 582ms, 0% errors</t>
+          <t>p95 = 327ms, 0% errors</t>
         </is>
       </c>
       <c r="H209" s="18" t="n">
-        <v>11.52</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="I209" s="18" t="inlineStr">
         <is>
@@ -26831,11 +26831,11 @@
       </c>
       <c r="G210" s="17" t="inlineStr">
         <is>
-          <t>p95 = 822ms, 0% errors</t>
+          <t>p95 = 418ms, 0% errors</t>
         </is>
       </c>
       <c r="H210" s="17" t="n">
-        <v>5.77</v>
+        <v>3.3</v>
       </c>
       <c r="I210" s="17" t="inlineStr">
         <is>
@@ -26881,11 +26881,11 @@
       </c>
       <c r="G211" s="18" t="inlineStr">
         <is>
-          <t>p95 = 446ms, 0% errors</t>
+          <t>p95 = 509ms, 0% errors</t>
         </is>
       </c>
       <c r="H211" s="18" t="n">
-        <v>1.81</v>
+        <v>7.68</v>
       </c>
       <c r="I211" s="18" t="inlineStr">
         <is>
@@ -26931,11 +26931,11 @@
       </c>
       <c r="G212" s="17" t="inlineStr">
         <is>
-          <t>p95 = 540ms, 0% errors</t>
+          <t>p95 = 816ms, 0% errors</t>
         </is>
       </c>
       <c r="H212" s="17" t="n">
-        <v>4.96</v>
+        <v>3.87</v>
       </c>
       <c r="I212" s="17" t="inlineStr">
         <is>
@@ -26981,11 +26981,11 @@
       </c>
       <c r="G213" s="18" t="inlineStr">
         <is>
-          <t>p95 = 485ms, 0% errors</t>
+          <t>p95 = 185ms, 0% errors</t>
         </is>
       </c>
       <c r="H213" s="18" t="n">
-        <v>8.41</v>
+        <v>11.55</v>
       </c>
       <c r="I213" s="18" t="inlineStr">
         <is>
@@ -27031,11 +27031,11 @@
       </c>
       <c r="G214" s="17" t="inlineStr">
         <is>
-          <t>p95 = 624ms, 0% errors</t>
+          <t>p95 = 546ms, 0% errors</t>
         </is>
       </c>
       <c r="H214" s="17" t="n">
-        <v>4.9</v>
+        <v>3.93</v>
       </c>
       <c r="I214" s="17" t="inlineStr">
         <is>
@@ -27081,11 +27081,11 @@
       </c>
       <c r="G215" s="18" t="inlineStr">
         <is>
-          <t>p95 = 865ms, 0% errors</t>
+          <t>p95 = 761ms, 0% errors</t>
         </is>
       </c>
       <c r="H215" s="18" t="n">
-        <v>9.199999999999999</v>
+        <v>5.24</v>
       </c>
       <c r="I215" s="18" t="inlineStr">
         <is>
@@ -27131,11 +27131,11 @@
       </c>
       <c r="G216" s="17" t="inlineStr">
         <is>
-          <t>p95 = 467ms, 0% errors</t>
+          <t>p95 = 263ms, 0% errors</t>
         </is>
       </c>
       <c r="H216" s="17" t="n">
-        <v>7.16</v>
+        <v>2.57</v>
       </c>
       <c r="I216" s="17" t="inlineStr">
         <is>
@@ -27181,11 +27181,11 @@
       </c>
       <c r="G217" s="18" t="inlineStr">
         <is>
-          <t>p95 = 720ms, 0% errors</t>
+          <t>p95 = 185ms, 0% errors</t>
         </is>
       </c>
       <c r="H217" s="18" t="n">
-        <v>5.37</v>
+        <v>9.57</v>
       </c>
       <c r="I217" s="18" t="inlineStr">
         <is>
@@ -27231,11 +27231,11 @@
       </c>
       <c r="G218" s="17" t="inlineStr">
         <is>
-          <t>p95 = 251ms, 0% errors</t>
+          <t>p95 = 616ms, 0% errors</t>
         </is>
       </c>
       <c r="H218" s="17" t="n">
-        <v>8.31</v>
+        <v>9.32</v>
       </c>
       <c r="I218" s="17" t="inlineStr">
         <is>
@@ -27281,11 +27281,11 @@
       </c>
       <c r="G219" s="18" t="inlineStr">
         <is>
-          <t>p95 = 572ms, 0% errors</t>
+          <t>p95 = 368ms, 0% errors</t>
         </is>
       </c>
       <c r="H219" s="18" t="n">
-        <v>11.19</v>
+        <v>8.24</v>
       </c>
       <c r="I219" s="18" t="inlineStr">
         <is>
@@ -27331,11 +27331,11 @@
       </c>
       <c r="G220" s="17" t="inlineStr">
         <is>
-          <t>p95 = 638ms, 0% errors</t>
+          <t>p95 = 636ms, 0% errors</t>
         </is>
       </c>
       <c r="H220" s="17" t="n">
-        <v>9.19</v>
+        <v>2.33</v>
       </c>
       <c r="I220" s="17" t="inlineStr">
         <is>
@@ -27381,11 +27381,11 @@
       </c>
       <c r="G221" s="18" t="inlineStr">
         <is>
-          <t>p95 = 887ms, 0% errors</t>
+          <t>p95 = 438ms, 0% errors</t>
         </is>
       </c>
       <c r="H221" s="18" t="n">
-        <v>11.08</v>
+        <v>11.98</v>
       </c>
       <c r="I221" s="18" t="inlineStr">
         <is>
@@ -27431,11 +27431,11 @@
       </c>
       <c r="G222" s="17" t="inlineStr">
         <is>
-          <t>p95 = 569ms, 0% errors</t>
+          <t>p95 = 854ms, 0% errors</t>
         </is>
       </c>
       <c r="H222" s="17" t="n">
-        <v>7.37</v>
+        <v>9.65</v>
       </c>
       <c r="I222" s="17" t="inlineStr">
         <is>
@@ -27481,11 +27481,11 @@
       </c>
       <c r="G223" s="18" t="inlineStr">
         <is>
-          <t>p95 = 429ms, 0% errors</t>
+          <t>p95 = 747ms, 0% errors</t>
         </is>
       </c>
       <c r="H223" s="18" t="n">
-        <v>11.53</v>
+        <v>4.26</v>
       </c>
       <c r="I223" s="18" t="inlineStr">
         <is>
@@ -27531,11 +27531,11 @@
       </c>
       <c r="G224" s="17" t="inlineStr">
         <is>
-          <t>p95 = 469ms, 0% errors</t>
+          <t>p95 = 694ms, 0% errors</t>
         </is>
       </c>
       <c r="H224" s="17" t="n">
-        <v>10.72</v>
+        <v>3.55</v>
       </c>
       <c r="I224" s="17" t="inlineStr">
         <is>
@@ -27581,11 +27581,11 @@
       </c>
       <c r="G225" s="18" t="inlineStr">
         <is>
-          <t>p95 = 402ms, 0% errors</t>
+          <t>p95 = 445ms, 0% errors</t>
         </is>
       </c>
       <c r="H225" s="18" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="I225" s="18" t="inlineStr">
         <is>
@@ -27631,11 +27631,11 @@
       </c>
       <c r="G226" s="17" t="inlineStr">
         <is>
-          <t>p95 = 445ms, 0% errors</t>
+          <t>p95 = 588ms, 0% errors</t>
         </is>
       </c>
       <c r="H226" s="17" t="n">
-        <v>3.19</v>
+        <v>1.95</v>
       </c>
       <c r="I226" s="17" t="inlineStr">
         <is>
@@ -27681,11 +27681,11 @@
       </c>
       <c r="G227" s="18" t="inlineStr">
         <is>
-          <t>p95 = 738ms, 0% errors</t>
+          <t>p95 = 670ms, 0% errors</t>
         </is>
       </c>
       <c r="H227" s="18" t="n">
-        <v>2.14</v>
+        <v>7.64</v>
       </c>
       <c r="I227" s="18" t="inlineStr">
         <is>
@@ -27731,11 +27731,11 @@
       </c>
       <c r="G228" s="17" t="inlineStr">
         <is>
-          <t>p95 = 842ms, 0% errors</t>
+          <t>p95 = 492ms, 0% errors</t>
         </is>
       </c>
       <c r="H228" s="17" t="n">
-        <v>1.64</v>
+        <v>7.51</v>
       </c>
       <c r="I228" s="17" t="inlineStr">
         <is>
@@ -27781,11 +27781,11 @@
       </c>
       <c r="G229" s="18" t="inlineStr">
         <is>
-          <t>p95 = 573ms, 0% errors</t>
+          <t>p95 = 553ms, 0% errors</t>
         </is>
       </c>
       <c r="H229" s="18" t="n">
-        <v>5.79</v>
+        <v>6.43</v>
       </c>
       <c r="I229" s="18" t="inlineStr">
         <is>
@@ -27831,11 +27831,11 @@
       </c>
       <c r="G230" s="17" t="inlineStr">
         <is>
-          <t>p95 = 456ms, 0% errors</t>
+          <t>p95 = 508ms, 0% errors</t>
         </is>
       </c>
       <c r="H230" s="17" t="n">
-        <v>9.24</v>
+        <v>11.41</v>
       </c>
       <c r="I230" s="17" t="inlineStr">
         <is>
@@ -27881,11 +27881,11 @@
       </c>
       <c r="G231" s="18" t="inlineStr">
         <is>
-          <t>p95 = 325ms, 0% errors</t>
+          <t>p95 = 239ms, 0% errors</t>
         </is>
       </c>
       <c r="H231" s="18" t="n">
-        <v>9.279999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="I231" s="18" t="inlineStr">
         <is>
@@ -27931,11 +27931,11 @@
       </c>
       <c r="G232" s="17" t="inlineStr">
         <is>
-          <t>p95 = 546ms, 0% errors</t>
+          <t>p95 = 844ms, 0% errors</t>
         </is>
       </c>
       <c r="H232" s="17" t="n">
-        <v>10.28</v>
+        <v>8.16</v>
       </c>
       <c r="I232" s="17" t="inlineStr">
         <is>
@@ -27981,11 +27981,11 @@
       </c>
       <c r="G233" s="18" t="inlineStr">
         <is>
-          <t>p95 = 737ms, 0% errors</t>
+          <t>p95 = 568ms, 0% errors</t>
         </is>
       </c>
       <c r="H233" s="18" t="n">
-        <v>2.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I233" s="18" t="inlineStr">
         <is>
@@ -28031,11 +28031,11 @@
       </c>
       <c r="G234" s="17" t="inlineStr">
         <is>
-          <t>p95 = 624ms, 0% errors</t>
+          <t>p95 = 658ms, 0% errors</t>
         </is>
       </c>
       <c r="H234" s="17" t="n">
-        <v>8.970000000000001</v>
+        <v>6.19</v>
       </c>
       <c r="I234" s="17" t="inlineStr">
         <is>
@@ -28081,11 +28081,11 @@
       </c>
       <c r="G235" s="18" t="inlineStr">
         <is>
-          <t>p95 = 743ms, 0% errors</t>
+          <t>p95 = 744ms, 0% errors</t>
         </is>
       </c>
       <c r="H235" s="18" t="n">
-        <v>9.630000000000001</v>
+        <v>6.59</v>
       </c>
       <c r="I235" s="18" t="inlineStr">
         <is>
@@ -28131,11 +28131,11 @@
       </c>
       <c r="G236" s="17" t="inlineStr">
         <is>
-          <t>p95 = 234ms, 0% errors</t>
+          <t>p95 = 477ms, 0% errors</t>
         </is>
       </c>
       <c r="H236" s="17" t="n">
-        <v>6.32</v>
+        <v>4.82</v>
       </c>
       <c r="I236" s="17" t="inlineStr">
         <is>
@@ -28181,11 +28181,11 @@
       </c>
       <c r="G237" s="18" t="inlineStr">
         <is>
-          <t>p95 = 450ms, 0% errors</t>
+          <t>p95 = 252ms, 0% errors</t>
         </is>
       </c>
       <c r="H237" s="18" t="n">
-        <v>5.03</v>
+        <v>10.22</v>
       </c>
       <c r="I237" s="18" t="inlineStr">
         <is>
@@ -28231,11 +28231,11 @@
       </c>
       <c r="G238" s="17" t="inlineStr">
         <is>
-          <t>p95 = 258ms, 0% errors</t>
+          <t>p95 = 259ms, 0% errors</t>
         </is>
       </c>
       <c r="H238" s="17" t="n">
-        <v>4.41</v>
+        <v>8.06</v>
       </c>
       <c r="I238" s="17" t="inlineStr">
         <is>
@@ -28281,11 +28281,11 @@
       </c>
       <c r="G239" s="18" t="inlineStr">
         <is>
-          <t>p95 = 612ms, 0% errors</t>
+          <t>p95 = 521ms, 0% errors</t>
         </is>
       </c>
       <c r="H239" s="18" t="n">
-        <v>6.99</v>
+        <v>4.96</v>
       </c>
       <c r="I239" s="18" t="inlineStr">
         <is>
@@ -28331,11 +28331,11 @@
       </c>
       <c r="G240" s="17" t="inlineStr">
         <is>
-          <t>p95 = 618ms, 0% errors</t>
+          <t>p95 = 540ms, 0% errors</t>
         </is>
       </c>
       <c r="H240" s="17" t="n">
-        <v>2.49</v>
+        <v>11.25</v>
       </c>
       <c r="I240" s="17" t="inlineStr">
         <is>
@@ -28381,11 +28381,11 @@
       </c>
       <c r="G241" s="18" t="inlineStr">
         <is>
-          <t>p95 = 608ms, 0% errors</t>
+          <t>p95 = 238ms, 0% errors</t>
         </is>
       </c>
       <c r="H241" s="18" t="n">
-        <v>9.56</v>
+        <v>8.08</v>
       </c>
       <c r="I241" s="18" t="inlineStr">
         <is>
@@ -28431,11 +28431,11 @@
       </c>
       <c r="G242" s="17" t="inlineStr">
         <is>
-          <t>p95 = 828ms, 0% errors</t>
+          <t>p95 = 842ms, 0% errors</t>
         </is>
       </c>
       <c r="H242" s="17" t="n">
-        <v>4.79</v>
+        <v>6.38</v>
       </c>
       <c r="I242" s="17" t="inlineStr">
         <is>
@@ -28481,11 +28481,11 @@
       </c>
       <c r="G243" s="18" t="inlineStr">
         <is>
-          <t>p95 = 890ms, 0% errors</t>
+          <t>p95 = 277ms, 0% errors</t>
         </is>
       </c>
       <c r="H243" s="18" t="n">
-        <v>7.14</v>
+        <v>5.27</v>
       </c>
       <c r="I243" s="18" t="inlineStr">
         <is>
@@ -28531,11 +28531,11 @@
       </c>
       <c r="G244" s="17" t="inlineStr">
         <is>
-          <t>p95 = 420ms, 0% errors</t>
+          <t>p95 = 789ms, 0% errors</t>
         </is>
       </c>
       <c r="H244" s="17" t="n">
-        <v>10.96</v>
+        <v>2.24</v>
       </c>
       <c r="I244" s="17" t="inlineStr">
         <is>
@@ -28581,11 +28581,11 @@
       </c>
       <c r="G245" s="18" t="inlineStr">
         <is>
-          <t>p95 = 301ms, 0% errors</t>
+          <t>p95 = 217ms, 0% errors</t>
         </is>
       </c>
       <c r="H245" s="18" t="n">
-        <v>6.52</v>
+        <v>11.98</v>
       </c>
       <c r="I245" s="18" t="inlineStr">
         <is>
@@ -28631,11 +28631,11 @@
       </c>
       <c r="G246" s="17" t="inlineStr">
         <is>
-          <t>p95 = 560ms, 0% errors</t>
+          <t>p95 = 876ms, 0% errors</t>
         </is>
       </c>
       <c r="H246" s="17" t="n">
-        <v>9.960000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="I246" s="17" t="inlineStr">
         <is>
@@ -28681,11 +28681,11 @@
       </c>
       <c r="G247" s="18" t="inlineStr">
         <is>
-          <t>p95 = 559ms, 0% errors</t>
+          <t>p95 = 551ms, 0% errors</t>
         </is>
       </c>
       <c r="H247" s="18" t="n">
-        <v>11.1</v>
+        <v>9.56</v>
       </c>
       <c r="I247" s="18" t="inlineStr">
         <is>
@@ -28731,11 +28731,11 @@
       </c>
       <c r="G248" s="17" t="inlineStr">
         <is>
-          <t>p95 = 348ms, 0% errors</t>
+          <t>p95 = 886ms, 0% errors</t>
         </is>
       </c>
       <c r="H248" s="17" t="n">
-        <v>1.67</v>
+        <v>10.35</v>
       </c>
       <c r="I248" s="17" t="inlineStr">
         <is>
@@ -28781,11 +28781,11 @@
       </c>
       <c r="G249" s="18" t="inlineStr">
         <is>
-          <t>p95 = 817ms, 0% errors</t>
+          <t>p95 = 446ms, 0% errors</t>
         </is>
       </c>
       <c r="H249" s="18" t="n">
-        <v>11.82</v>
+        <v>7.24</v>
       </c>
       <c r="I249" s="18" t="inlineStr">
         <is>
@@ -28831,11 +28831,11 @@
       </c>
       <c r="G250" s="17" t="inlineStr">
         <is>
-          <t>p95 = 853ms, 0% errors</t>
+          <t>p95 = 556ms, 0% errors</t>
         </is>
       </c>
       <c r="H250" s="17" t="n">
-        <v>2.55</v>
+        <v>4.51</v>
       </c>
       <c r="I250" s="17" t="inlineStr">
         <is>
@@ -28881,11 +28881,11 @@
       </c>
       <c r="G251" s="18" t="inlineStr">
         <is>
-          <t>p95 = 502ms, 0% errors</t>
+          <t>p95 = 715ms, 0% errors</t>
         </is>
       </c>
       <c r="H251" s="18" t="n">
-        <v>8.09</v>
+        <v>11.1</v>
       </c>
       <c r="I251" s="18" t="inlineStr">
         <is>
@@ -28931,11 +28931,11 @@
       </c>
       <c r="G252" s="17" t="inlineStr">
         <is>
-          <t>p95 = 352ms, 0% errors</t>
+          <t>p95 = 357ms, 0% errors</t>
         </is>
       </c>
       <c r="H252" s="17" t="n">
-        <v>6.87</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I252" s="17" t="inlineStr">
         <is>
@@ -28981,11 +28981,11 @@
       </c>
       <c r="G253" s="18" t="inlineStr">
         <is>
-          <t>p95 = 853ms, 0% errors</t>
+          <t>p95 = 537ms, 0% errors</t>
         </is>
       </c>
       <c r="H253" s="18" t="n">
-        <v>4.01</v>
+        <v>5.11</v>
       </c>
       <c r="I253" s="18" t="inlineStr">
         <is>
@@ -29031,11 +29031,11 @@
       </c>
       <c r="G254" s="17" t="inlineStr">
         <is>
-          <t>p95 = 886ms, 0% errors</t>
+          <t>p95 = 722ms, 0% errors</t>
         </is>
       </c>
       <c r="H254" s="17" t="n">
-        <v>10.96</v>
+        <v>10.57</v>
       </c>
       <c r="I254" s="17" t="inlineStr">
         <is>
@@ -29081,11 +29081,11 @@
       </c>
       <c r="G255" s="18" t="inlineStr">
         <is>
-          <t>p95 = 854ms, 0% errors</t>
+          <t>p95 = 843ms, 0% errors</t>
         </is>
       </c>
       <c r="H255" s="18" t="n">
-        <v>9.800000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="I255" s="18" t="inlineStr">
         <is>
@@ -29131,11 +29131,11 @@
       </c>
       <c r="G256" s="17" t="inlineStr">
         <is>
-          <t>p95 = 318ms, 0% errors</t>
+          <t>p95 = 831ms, 0% errors</t>
         </is>
       </c>
       <c r="H256" s="17" t="n">
-        <v>7.15</v>
+        <v>2.29</v>
       </c>
       <c r="I256" s="17" t="inlineStr">
         <is>
@@ -29181,11 +29181,11 @@
       </c>
       <c r="G257" s="18" t="inlineStr">
         <is>
-          <t>p95 = 471ms, 0% errors</t>
+          <t>p95 = 727ms, 0% errors</t>
         </is>
       </c>
       <c r="H257" s="18" t="n">
-        <v>3.01</v>
+        <v>11.78</v>
       </c>
       <c r="I257" s="18" t="inlineStr">
         <is>
@@ -29231,11 +29231,11 @@
       </c>
       <c r="G258" s="17" t="inlineStr">
         <is>
-          <t>p95 = 560ms, 0% errors</t>
+          <t>p95 = 402ms, 0% errors</t>
         </is>
       </c>
       <c r="H258" s="17" t="n">
-        <v>2.2</v>
+        <v>11.14</v>
       </c>
       <c r="I258" s="17" t="inlineStr">
         <is>
@@ -29281,11 +29281,11 @@
       </c>
       <c r="G259" s="18" t="inlineStr">
         <is>
-          <t>p95 = 381ms, 0% errors</t>
+          <t>p95 = 343ms, 0% errors</t>
         </is>
       </c>
       <c r="H259" s="18" t="n">
-        <v>5.85</v>
+        <v>9.66</v>
       </c>
       <c r="I259" s="18" t="inlineStr">
         <is>
@@ -29331,11 +29331,11 @@
       </c>
       <c r="G260" s="17" t="inlineStr">
         <is>
-          <t>p95 = 374ms, 0% errors</t>
+          <t>p95 = 242ms, 0% errors</t>
         </is>
       </c>
       <c r="H260" s="17" t="n">
-        <v>3.92</v>
+        <v>6.27</v>
       </c>
       <c r="I260" s="17" t="inlineStr">
         <is>
@@ -29381,11 +29381,11 @@
       </c>
       <c r="G261" s="18" t="inlineStr">
         <is>
-          <t>p95 = 450ms, 0% errors</t>
+          <t>p95 = 447ms, 0% errors</t>
         </is>
       </c>
       <c r="H261" s="18" t="n">
-        <v>10.44</v>
+        <v>9.99</v>
       </c>
       <c r="I261" s="18" t="inlineStr">
         <is>
@@ -29431,11 +29431,11 @@
       </c>
       <c r="G262" s="17" t="inlineStr">
         <is>
-          <t>p95 = 752ms, 0% errors</t>
+          <t>p95 = 354ms, 0% errors</t>
         </is>
       </c>
       <c r="H262" s="17" t="n">
-        <v>4.63</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I262" s="17" t="inlineStr">
         <is>
@@ -29481,11 +29481,11 @@
       </c>
       <c r="G263" s="18" t="inlineStr">
         <is>
-          <t>p95 = 190ms, 0% errors</t>
+          <t>p95 = 569ms, 0% errors</t>
         </is>
       </c>
       <c r="H263" s="18" t="n">
-        <v>5.05</v>
+        <v>9.09</v>
       </c>
       <c r="I263" s="18" t="inlineStr">
         <is>
@@ -29531,11 +29531,11 @@
       </c>
       <c r="G264" s="17" t="inlineStr">
         <is>
-          <t>p95 = 211ms, 0% errors</t>
+          <t>p95 = 188ms, 0% errors</t>
         </is>
       </c>
       <c r="H264" s="17" t="n">
-        <v>6.63</v>
+        <v>4.46</v>
       </c>
       <c r="I264" s="17" t="inlineStr">
         <is>
@@ -29581,11 +29581,11 @@
       </c>
       <c r="G265" s="18" t="inlineStr">
         <is>
-          <t>p95 = 346ms, 0% errors</t>
+          <t>p95 = 519ms, 0% errors</t>
         </is>
       </c>
       <c r="H265" s="18" t="n">
-        <v>3.79</v>
+        <v>3.24</v>
       </c>
       <c r="I265" s="18" t="inlineStr">
         <is>
@@ -29631,11 +29631,11 @@
       </c>
       <c r="G266" s="17" t="inlineStr">
         <is>
-          <t>p95 = 501ms, 0% errors</t>
+          <t>p95 = 186ms, 0% errors</t>
         </is>
       </c>
       <c r="H266" s="17" t="n">
-        <v>6.81</v>
+        <v>4.96</v>
       </c>
       <c r="I266" s="17" t="inlineStr">
         <is>
@@ -29681,11 +29681,11 @@
       </c>
       <c r="G267" s="18" t="inlineStr">
         <is>
-          <t>p95 = 256ms, 0% errors</t>
+          <t>p95 = 231ms, 0% errors</t>
         </is>
       </c>
       <c r="H267" s="18" t="n">
-        <v>3.67</v>
+        <v>10.55</v>
       </c>
       <c r="I267" s="18" t="inlineStr">
         <is>
@@ -29731,11 +29731,11 @@
       </c>
       <c r="G268" s="17" t="inlineStr">
         <is>
-          <t>p95 = 781ms, 0% errors</t>
+          <t>p95 = 316ms, 0% errors</t>
         </is>
       </c>
       <c r="H268" s="17" t="n">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="I268" s="17" t="inlineStr">
         <is>
@@ -29781,11 +29781,11 @@
       </c>
       <c r="G269" s="18" t="inlineStr">
         <is>
-          <t>p95 = 766ms, 0% errors</t>
+          <t>p95 = 205ms, 0% errors</t>
         </is>
       </c>
       <c r="H269" s="18" t="n">
-        <v>9.380000000000001</v>
+        <v>10.15</v>
       </c>
       <c r="I269" s="18" t="inlineStr">
         <is>
@@ -29831,11 +29831,11 @@
       </c>
       <c r="G270" s="17" t="inlineStr">
         <is>
-          <t>p95 = 261ms, 0% errors</t>
+          <t>p95 = 237ms, 0% errors</t>
         </is>
       </c>
       <c r="H270" s="17" t="n">
-        <v>10.47</v>
+        <v>3.63</v>
       </c>
       <c r="I270" s="17" t="inlineStr">
         <is>
@@ -29881,11 +29881,11 @@
       </c>
       <c r="G271" s="18" t="inlineStr">
         <is>
-          <t>p95 = 457ms, 0% errors</t>
+          <t>p95 = 630ms, 0% errors</t>
         </is>
       </c>
       <c r="H271" s="18" t="n">
-        <v>8.58</v>
+        <v>10.94</v>
       </c>
       <c r="I271" s="18" t="inlineStr">
         <is>
@@ -29931,11 +29931,11 @@
       </c>
       <c r="G272" s="17" t="inlineStr">
         <is>
-          <t>p95 = 853ms, 0% errors</t>
+          <t>p95 = 310ms, 0% errors</t>
         </is>
       </c>
       <c r="H272" s="17" t="n">
-        <v>11.02</v>
+        <v>8.9</v>
       </c>
       <c r="I272" s="17" t="inlineStr">
         <is>
@@ -29981,11 +29981,11 @@
       </c>
       <c r="G273" s="18" t="inlineStr">
         <is>
-          <t>p95 = 383ms, 0% errors</t>
+          <t>p95 = 272ms, 0% errors</t>
         </is>
       </c>
       <c r="H273" s="18" t="n">
-        <v>3.6</v>
+        <v>4.69</v>
       </c>
       <c r="I273" s="18" t="inlineStr">
         <is>
@@ -30031,11 +30031,11 @@
       </c>
       <c r="G274" s="17" t="inlineStr">
         <is>
-          <t>p95 = 857ms, 0% errors</t>
+          <t>p95 = 480ms, 0% errors</t>
         </is>
       </c>
       <c r="H274" s="17" t="n">
-        <v>6.28</v>
+        <v>4.13</v>
       </c>
       <c r="I274" s="17" t="inlineStr">
         <is>
@@ -30081,11 +30081,11 @@
       </c>
       <c r="G275" s="18" t="inlineStr">
         <is>
-          <t>p95 = 337ms, 0% errors</t>
+          <t>p95 = 766ms, 0% errors</t>
         </is>
       </c>
       <c r="H275" s="18" t="n">
-        <v>11.55</v>
+        <v>5.47</v>
       </c>
       <c r="I275" s="18" t="inlineStr">
         <is>
@@ -30131,11 +30131,11 @@
       </c>
       <c r="G276" s="17" t="inlineStr">
         <is>
-          <t>p95 = 750ms, 0% errors</t>
+          <t>p95 = 365ms, 0% errors</t>
         </is>
       </c>
       <c r="H276" s="17" t="n">
-        <v>10.48</v>
+        <v>11.05</v>
       </c>
       <c r="I276" s="17" t="inlineStr">
         <is>
@@ -30181,11 +30181,11 @@
       </c>
       <c r="G277" s="18" t="inlineStr">
         <is>
-          <t>p95 = 498ms, 0% errors</t>
+          <t>p95 = 350ms, 0% errors</t>
         </is>
       </c>
       <c r="H277" s="18" t="n">
-        <v>8.300000000000001</v>
+        <v>2.66</v>
       </c>
       <c r="I277" s="18" t="inlineStr">
         <is>
@@ -30231,11 +30231,11 @@
       </c>
       <c r="G278" s="17" t="inlineStr">
         <is>
-          <t>p95 = 236ms, 0% errors</t>
+          <t>p95 = 403ms, 0% errors</t>
         </is>
       </c>
       <c r="H278" s="17" t="n">
-        <v>3.79</v>
+        <v>10.14</v>
       </c>
       <c r="I278" s="17" t="inlineStr">
         <is>
@@ -30281,11 +30281,11 @@
       </c>
       <c r="G279" s="18" t="inlineStr">
         <is>
-          <t>p95 = 383ms, 0% errors</t>
+          <t>p95 = 180ms, 0% errors</t>
         </is>
       </c>
       <c r="H279" s="18" t="n">
-        <v>4.7</v>
+        <v>11.41</v>
       </c>
       <c r="I279" s="18" t="inlineStr">
         <is>
@@ -30331,11 +30331,11 @@
       </c>
       <c r="G280" s="17" t="inlineStr">
         <is>
-          <t>p95 = 547ms, 0% errors</t>
+          <t>p95 = 464ms, 0% errors</t>
         </is>
       </c>
       <c r="H280" s="17" t="n">
-        <v>6.4</v>
+        <v>4.18</v>
       </c>
       <c r="I280" s="17" t="inlineStr">
         <is>
@@ -30381,11 +30381,11 @@
       </c>
       <c r="G281" s="18" t="inlineStr">
         <is>
-          <t>p95 = 821ms, 0% errors</t>
+          <t>p95 = 467ms, 0% errors</t>
         </is>
       </c>
       <c r="H281" s="18" t="n">
-        <v>2.79</v>
+        <v>7.08</v>
       </c>
       <c r="I281" s="18" t="inlineStr">
         <is>
@@ -30431,11 +30431,11 @@
       </c>
       <c r="G282" s="17" t="inlineStr">
         <is>
-          <t>p95 = 319ms, 0% errors</t>
+          <t>p95 = 875ms, 0% errors</t>
         </is>
       </c>
       <c r="H282" s="17" t="n">
-        <v>5.71</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="I282" s="17" t="inlineStr">
         <is>
@@ -30481,11 +30481,11 @@
       </c>
       <c r="G283" s="18" t="inlineStr">
         <is>
-          <t>p95 = 803ms, 0% errors</t>
+          <t>p95 = 494ms, 0% errors</t>
         </is>
       </c>
       <c r="H283" s="18" t="n">
-        <v>9.369999999999999</v>
+        <v>4.07</v>
       </c>
       <c r="I283" s="18" t="inlineStr">
         <is>
@@ -30531,11 +30531,11 @@
       </c>
       <c r="G284" s="17" t="inlineStr">
         <is>
-          <t>p95 = 667ms, 0% errors</t>
+          <t>p95 = 740ms, 0% errors</t>
         </is>
       </c>
       <c r="H284" s="17" t="n">
-        <v>10.52</v>
+        <v>10.57</v>
       </c>
       <c r="I284" s="17" t="inlineStr">
         <is>
@@ -30581,11 +30581,11 @@
       </c>
       <c r="G285" s="18" t="inlineStr">
         <is>
-          <t>p95 = 790ms, 0% errors</t>
+          <t>p95 = 417ms, 0% errors</t>
         </is>
       </c>
       <c r="H285" s="18" t="n">
-        <v>2.42</v>
+        <v>3.29</v>
       </c>
       <c r="I285" s="18" t="inlineStr">
         <is>
@@ -30631,11 +30631,11 @@
       </c>
       <c r="G286" s="17" t="inlineStr">
         <is>
-          <t>p95 = 842ms, 0% errors</t>
+          <t>p95 = 515ms, 0% errors</t>
         </is>
       </c>
       <c r="H286" s="17" t="n">
-        <v>4.01</v>
+        <v>3.76</v>
       </c>
       <c r="I286" s="17" t="inlineStr">
         <is>
@@ -30681,11 +30681,11 @@
       </c>
       <c r="G287" s="18" t="inlineStr">
         <is>
-          <t>p95 = 454ms, 0% errors</t>
+          <t>p95 = 843ms, 0% errors</t>
         </is>
       </c>
       <c r="H287" s="18" t="n">
-        <v>1.94</v>
+        <v>2.94</v>
       </c>
       <c r="I287" s="18" t="inlineStr">
         <is>
@@ -30731,11 +30731,11 @@
       </c>
       <c r="G288" s="17" t="inlineStr">
         <is>
-          <t>p95 = 456ms, 0% errors</t>
+          <t>p95 = 784ms, 0% errors</t>
         </is>
       </c>
       <c r="H288" s="17" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="I288" s="17" t="inlineStr">
         <is>
@@ -30781,11 +30781,11 @@
       </c>
       <c r="G289" s="18" t="inlineStr">
         <is>
-          <t>p95 = 554ms, 0% errors</t>
+          <t>p95 = 478ms, 0% errors</t>
         </is>
       </c>
       <c r="H289" s="18" t="n">
-        <v>11.56</v>
+        <v>8.08</v>
       </c>
       <c r="I289" s="18" t="inlineStr">
         <is>
@@ -30831,11 +30831,11 @@
       </c>
       <c r="G290" s="17" t="inlineStr">
         <is>
-          <t>p95 = 740ms, 0% errors</t>
+          <t>p95 = 526ms, 0% errors</t>
         </is>
       </c>
       <c r="H290" s="17" t="n">
-        <v>10.7</v>
+        <v>9.82</v>
       </c>
       <c r="I290" s="17" t="inlineStr">
         <is>
@@ -30881,11 +30881,11 @@
       </c>
       <c r="G291" s="18" t="inlineStr">
         <is>
-          <t>p95 = 498ms, 0% errors</t>
+          <t>p95 = 546ms, 0% errors</t>
         </is>
       </c>
       <c r="H291" s="18" t="n">
-        <v>1.57</v>
+        <v>3.93</v>
       </c>
       <c r="I291" s="18" t="inlineStr">
         <is>
@@ -30931,11 +30931,11 @@
       </c>
       <c r="G292" s="17" t="inlineStr">
         <is>
-          <t>p95 = 610ms, 0% errors</t>
+          <t>p95 = 775ms, 0% errors</t>
         </is>
       </c>
       <c r="H292" s="17" t="n">
-        <v>5.12</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="I292" s="17" t="inlineStr">
         <is>
@@ -30981,11 +30981,11 @@
       </c>
       <c r="G293" s="18" t="inlineStr">
         <is>
-          <t>p95 = 380ms, 0% errors</t>
+          <t>p95 = 592ms, 0% errors</t>
         </is>
       </c>
       <c r="H293" s="18" t="n">
-        <v>5.1</v>
+        <v>11.09</v>
       </c>
       <c r="I293" s="18" t="inlineStr">
         <is>
@@ -31031,11 +31031,11 @@
       </c>
       <c r="G294" s="17" t="inlineStr">
         <is>
-          <t>p95 = 850ms, 0% errors</t>
+          <t>p95 = 676ms, 0% errors</t>
         </is>
       </c>
       <c r="H294" s="17" t="n">
-        <v>6.63</v>
+        <v>11.41</v>
       </c>
       <c r="I294" s="17" t="inlineStr">
         <is>
@@ -31081,11 +31081,11 @@
       </c>
       <c r="G295" s="18" t="inlineStr">
         <is>
-          <t>p95 = 540ms, 0% errors</t>
+          <t>p95 = 491ms, 0% errors</t>
         </is>
       </c>
       <c r="H295" s="18" t="n">
-        <v>5.45</v>
+        <v>6.7</v>
       </c>
       <c r="I295" s="18" t="inlineStr">
         <is>
@@ -31131,11 +31131,11 @@
       </c>
       <c r="G296" s="17" t="inlineStr">
         <is>
-          <t>p95 = 510ms, 0% errors</t>
+          <t>p95 = 486ms, 0% errors</t>
         </is>
       </c>
       <c r="H296" s="17" t="n">
-        <v>10.66</v>
+        <v>6.1</v>
       </c>
       <c r="I296" s="17" t="inlineStr">
         <is>
@@ -31181,11 +31181,11 @@
       </c>
       <c r="G297" s="18" t="inlineStr">
         <is>
-          <t>p95 = 628ms, 0% errors</t>
+          <t>p95 = 412ms, 0% errors</t>
         </is>
       </c>
       <c r="H297" s="18" t="n">
-        <v>5.98</v>
+        <v>3.24</v>
       </c>
       <c r="I297" s="18" t="inlineStr">
         <is>
@@ -31231,11 +31231,11 @@
       </c>
       <c r="G298" s="17" t="inlineStr">
         <is>
-          <t>p95 = 619ms, 0% errors</t>
+          <t>p95 = 392ms, 0% errors</t>
         </is>
       </c>
       <c r="H298" s="17" t="n">
-        <v>4.35</v>
+        <v>2.72</v>
       </c>
       <c r="I298" s="17" t="inlineStr">
         <is>
@@ -31281,11 +31281,11 @@
       </c>
       <c r="G299" s="18" t="inlineStr">
         <is>
-          <t>p95 = 711ms, 0% errors</t>
+          <t>p95 = 476ms, 0% errors</t>
         </is>
       </c>
       <c r="H299" s="18" t="n">
-        <v>6.01</v>
+        <v>5.8</v>
       </c>
       <c r="I299" s="18" t="inlineStr">
         <is>
@@ -31331,11 +31331,11 @@
       </c>
       <c r="G300" s="17" t="inlineStr">
         <is>
-          <t>p95 = 509ms, 0% errors</t>
+          <t>p95 = 263ms, 0% errors</t>
         </is>
       </c>
       <c r="H300" s="17" t="n">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
       <c r="I300" s="17" t="inlineStr">
         <is>
@@ -31381,11 +31381,11 @@
       </c>
       <c r="G301" s="18" t="inlineStr">
         <is>
-          <t>p95 = 366ms, 0% errors</t>
+          <t>p95 = 584ms, 0% errors</t>
         </is>
       </c>
       <c r="H301" s="18" t="n">
-        <v>5.22</v>
+        <v>2.58</v>
       </c>
       <c r="I301" s="18" t="inlineStr">
         <is>
@@ -31431,11 +31431,11 @@
       </c>
       <c r="G302" s="17" t="inlineStr">
         <is>
-          <t>p95 = 525ms, 0% errors</t>
+          <t>p95 = 602ms, 0% errors</t>
         </is>
       </c>
       <c r="H302" s="17" t="n">
-        <v>11.03</v>
+        <v>10.36</v>
       </c>
       <c r="I302" s="17" t="inlineStr">
         <is>
@@ -31481,11 +31481,11 @@
       </c>
       <c r="G303" s="18" t="inlineStr">
         <is>
-          <t>p95 = 549ms, 0% errors</t>
+          <t>p95 = 748ms, 0% errors</t>
         </is>
       </c>
       <c r="H303" s="18" t="n">
-        <v>7</v>
+        <v>11.26</v>
       </c>
       <c r="I303" s="18" t="inlineStr">
         <is>
@@ -31531,11 +31531,11 @@
       </c>
       <c r="G304" s="17" t="inlineStr">
         <is>
-          <t>p95 = 454ms, 0% errors</t>
+          <t>p95 = 453ms, 0% errors</t>
         </is>
       </c>
       <c r="H304" s="17" t="n">
-        <v>2.68</v>
+        <v>7.94</v>
       </c>
       <c r="I304" s="17" t="inlineStr">
         <is>
@@ -31581,11 +31581,11 @@
       </c>
       <c r="G305" s="18" t="inlineStr">
         <is>
-          <t>p95 = 770ms, 0% errors</t>
+          <t>p95 = 698ms, 0% errors</t>
         </is>
       </c>
       <c r="H305" s="18" t="n">
-        <v>8.130000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="I305" s="18" t="inlineStr">
         <is>
@@ -31631,11 +31631,11 @@
       </c>
       <c r="G306" s="17" t="inlineStr">
         <is>
-          <t>p95 = 605ms, 0% errors</t>
+          <t>p95 = 471ms, 0% errors</t>
         </is>
       </c>
       <c r="H306" s="17" t="n">
-        <v>7.95</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="I306" s="17" t="inlineStr">
         <is>
@@ -31681,11 +31681,11 @@
       </c>
       <c r="G307" s="18" t="inlineStr">
         <is>
-          <t>p95 = 309ms, 0% errors</t>
+          <t>p95 = 329ms, 0% errors</t>
         </is>
       </c>
       <c r="H307" s="18" t="n">
-        <v>5.02</v>
+        <v>9.44</v>
       </c>
       <c r="I307" s="18" t="inlineStr">
         <is>
@@ -31731,11 +31731,11 @@
       </c>
       <c r="G308" s="17" t="inlineStr">
         <is>
-          <t>p95 = 343ms, 0% errors</t>
+          <t>p95 = 313ms, 0% errors</t>
         </is>
       </c>
       <c r="H308" s="17" t="n">
-        <v>10</v>
+        <v>4.38</v>
       </c>
       <c r="I308" s="17" t="inlineStr">
         <is>
@@ -31781,11 +31781,11 @@
       </c>
       <c r="G309" s="18" t="inlineStr">
         <is>
-          <t>p95 = 875ms, 0% errors</t>
+          <t>p95 = 718ms, 0% errors</t>
         </is>
       </c>
       <c r="H309" s="18" t="n">
-        <v>9.48</v>
+        <v>8.23</v>
       </c>
       <c r="I309" s="18" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         </is>
       </c>
       <c r="E2" s="17" t="n">
-        <v>6.07</v>
+        <v>7.15</v>
       </c>
       <c r="F2" s="17" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         </is>
       </c>
       <c r="E3" s="18" t="n">
-        <v>11.69</v>
+        <v>6.26</v>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
